--- a/research/traditional_assets/database/data/ireland/ireland_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_publishing_newspapers.xlsx
@@ -650,10 +650,10 @@
         <v>-0.2549658091826766</v>
       </c>
       <c r="X2">
-        <v>0.1377363473057364</v>
+        <v>0.1376934121251494</v>
       </c>
       <c r="Y2">
-        <v>-0.3927021564884131</v>
+        <v>-0.392659221307826</v>
       </c>
       <c r="Z2">
         <v>16.06701481080389</v>
@@ -662,10 +662,10 @@
         <v>1.259719207545411</v>
       </c>
       <c r="AB2">
-        <v>0.1022207015791208</v>
+        <v>0.1021986430814967</v>
       </c>
       <c r="AC2">
-        <v>1.15749850596629</v>
+        <v>1.157520564463914</v>
       </c>
       <c r="AD2">
         <v>1631.5</v>
@@ -787,10 +787,10 @@
         <v>-0.2549658091826766</v>
       </c>
       <c r="X3">
-        <v>0.1377363473057364</v>
+        <v>0.1376934121251494</v>
       </c>
       <c r="Y3">
-        <v>-0.3927021564884131</v>
+        <v>-0.392659221307826</v>
       </c>
       <c r="Z3">
         <v>16.06701481080389</v>
@@ -799,10 +799,10 @@
         <v>1.259719207545411</v>
       </c>
       <c r="AB3">
-        <v>0.1022207015791208</v>
+        <v>0.1021986430814967</v>
       </c>
       <c r="AC3">
-        <v>1.15749850596629</v>
+        <v>1.157520564463914</v>
       </c>
       <c r="AD3">
         <v>1631.5</v>
@@ -1139,7 +1139,7 @@
         <v>2.74672131147541</v>
       </c>
       <c r="F2">
-        <v>13.1419023439981</v>
+        <v>13.4690675323309</v>
       </c>
       <c r="G2">
         <v>4.71903867686752</v>
@@ -1157,13 +1157,13 @@
         <v>1804</v>
       </c>
       <c r="L2">
-        <v>3236.85494213346</v>
+        <v>3246.49260044196</v>
       </c>
       <c r="M2">
         <v>3358.34819329067</v>
       </c>
       <c r="N2">
-        <v>3645.67065305996</v>
+        <v>3655.30831136847</v>
       </c>
       <c r="O2">
         <v>1707.34819329067</v>
@@ -1172,16 +1172,16 @@
         <v>561.815710926507</v>
       </c>
       <c r="Q2">
-        <v>0.102220701579121</v>
+        <v>0.102198643081497</v>
       </c>
       <c r="R2">
-        <v>0.0958254117589105</v>
+        <v>0.09560639551172551</v>
       </c>
       <c r="S2">
         <v>0.0646945395797173</v>
       </c>
       <c r="T2">
-        <v>0.0504320395797173</v>
+        <v>0.0492070395797173</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.137736347305736</v>
+        <v>0.137693412125149</v>
       </c>
       <c r="X2">
-        <v>0.104471768364471</v>
+        <v>0.104444368070203</v>
       </c>
       <c r="Y2">
         <v>1.7911736434372</v>
@@ -1236,7 +1236,7 @@
         <v>1804</v>
       </c>
       <c r="AK2">
-        <v>0.05132743418963755</v>
+        <v>0.05130346377183671</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1421,13 +1421,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.09609008716954667</v>
+        <v>0.09606660120303137</v>
       </c>
       <c r="C2">
-        <v>3785.807731176</v>
+        <v>3785.88280440116</v>
       </c>
       <c r="D2">
-        <v>3632.807731176</v>
+        <v>3632.88280440116</v>
       </c>
       <c r="E2">
         <v>-1707.348193290669</v>
@@ -1472,19 +1472,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.09609008716954667</v>
+        <v>0.09606660120303137</v>
       </c>
       <c r="T2">
         <v>0.9797896186226994</v>
       </c>
       <c r="U2">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V2">
         <v>0.125</v>
       </c>
       <c r="W2">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1503,13 +1503,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.09607354495638193</v>
+        <v>0.09603783834732474</v>
       </c>
       <c r="C3">
-        <v>3751.495522061305</v>
+        <v>3752.162852136417</v>
       </c>
       <c r="D3">
-        <v>3633.609003994212</v>
+        <v>3634.276334069324</v>
       </c>
       <c r="E3">
         <v>-1672.234711357762</v>
@@ -1536,37 +1536,37 @@
         <v>425.55</v>
       </c>
       <c r="M3">
-        <v>2.023822297853759</v>
+        <v>1.97466342314769</v>
       </c>
       <c r="N3">
-        <v>423.5261777021462</v>
+        <v>423.5753365768523</v>
       </c>
       <c r="O3">
-        <v>52.94077221276828</v>
+        <v>52.94691707210654</v>
       </c>
       <c r="P3">
-        <v>370.585405489378</v>
+        <v>370.6284195047458</v>
       </c>
       <c r="Q3">
-        <v>397.285405489378</v>
+        <v>397.3284195047457</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.09653457026321692</v>
+        <v>0.09651087671871472</v>
       </c>
       <c r="T3">
         <v>0.9884493753529506</v>
       </c>
       <c r="U3">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V3">
         <v>0.125</v>
       </c>
       <c r="W3">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>210.2704375039701</v>
+        <v>215.5050805172948</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1585,13 +1585,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.09605700274321717</v>
+        <v>0.09600907549161812</v>
       </c>
       <c r="C4">
-        <v>3717.183666491208</v>
+        <v>3718.443969363989</v>
       </c>
       <c r="D4">
-        <v>3634.410630357021</v>
+        <v>3635.670933229802</v>
       </c>
       <c r="E4">
         <v>-1637.121229424855</v>
@@ -1618,37 +1618,37 @@
         <v>425.55</v>
       </c>
       <c r="M4">
-        <v>4.047644595707519</v>
+        <v>3.949326846295381</v>
       </c>
       <c r="N4">
-        <v>421.5023554042925</v>
+        <v>421.6006731537046</v>
       </c>
       <c r="O4">
-        <v>52.68779442553656</v>
+        <v>52.70008414421308</v>
       </c>
       <c r="P4">
-        <v>368.8145609787559</v>
+        <v>368.9005890094916</v>
       </c>
       <c r="Q4">
-        <v>395.5145609787559</v>
+        <v>395.6005890094916</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.09698812444043145</v>
+        <v>0.09696421908165692</v>
       </c>
       <c r="T4">
         <v>0.9972858618123904</v>
       </c>
       <c r="U4">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V4">
         <v>0.125</v>
       </c>
       <c r="W4">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>105.135218751985</v>
+        <v>107.7525402586474</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1667,13 +1667,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.0960404605300524</v>
+        <v>0.09598031263591153</v>
       </c>
       <c r="C5">
-        <v>3682.872164699751</v>
+        <v>3684.726157315552</v>
       </c>
       <c r="D5">
-        <v>3635.21261049847</v>
+        <v>3637.066603114272</v>
       </c>
       <c r="E5">
         <v>-1602.007747491949</v>
@@ -1700,37 +1700,37 @@
         <v>425.55</v>
       </c>
       <c r="M5">
-        <v>6.071466893561279</v>
+        <v>5.923990269443071</v>
       </c>
       <c r="N5">
-        <v>419.4785331064387</v>
+        <v>419.6260097305569</v>
       </c>
       <c r="O5">
-        <v>52.43481663830484</v>
+        <v>52.45325121631961</v>
       </c>
       <c r="P5">
-        <v>367.0437164681339</v>
+        <v>367.1727585142373</v>
       </c>
       <c r="Q5">
-        <v>393.7437164681339</v>
+        <v>393.8727585142373</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.09745103025016585</v>
+        <v>0.09742690870981444</v>
       </c>
       <c r="T5">
         <v>1.006304543868932</v>
       </c>
       <c r="U5">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V5">
         <v>0.125</v>
       </c>
       <c r="W5">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>70.09014583465667</v>
+        <v>71.83502683909826</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1749,13 +1749,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.09602391831688763</v>
+        <v>0.0959515497802049</v>
       </c>
       <c r="C6">
-        <v>3648.561016921182</v>
+        <v>3651.00941722468</v>
       </c>
       <c r="D6">
-        <v>3636.014944652808</v>
+        <v>3638.463344956307</v>
       </c>
       <c r="E6">
         <v>-1566.894265559042</v>
@@ -1782,37 +1782,37 @@
         <v>425.55</v>
       </c>
       <c r="M6">
-        <v>8.095289191415038</v>
+        <v>7.898653692590761</v>
       </c>
       <c r="N6">
-        <v>417.454710808585</v>
+        <v>417.6513463074093</v>
       </c>
       <c r="O6">
-        <v>52.18183885107312</v>
+        <v>52.20641828842616</v>
       </c>
       <c r="P6">
-        <v>365.2728719575119</v>
+        <v>365.4449280189831</v>
       </c>
       <c r="Q6">
-        <v>391.9728719575119</v>
+        <v>392.1449280189831</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.09792357993093639</v>
+        <v>0.09789923770522521</v>
       </c>
       <c r="T6">
         <v>1.015511115134985</v>
       </c>
       <c r="U6">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V6">
         <v>0.125</v>
       </c>
       <c r="W6">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>52.56760937599252</v>
+        <v>53.87627012932371</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1831,13 +1831,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.09600737610372287</v>
+        <v>0.09592278692449828</v>
       </c>
       <c r="C7">
-        <v>3614.250223389957</v>
+        <v>3617.293750326835</v>
       </c>
       <c r="D7">
-        <v>3636.81763305449</v>
+        <v>3639.861159991369</v>
       </c>
       <c r="E7">
         <v>-1531.780783626135</v>
@@ -1864,37 +1864,37 @@
         <v>425.55</v>
       </c>
       <c r="M7">
-        <v>10.1191114892688</v>
+        <v>9.873317115738452</v>
       </c>
       <c r="N7">
-        <v>415.4308885107312</v>
+        <v>415.6766828842615</v>
       </c>
       <c r="O7">
-        <v>51.9288610638414</v>
+        <v>51.95958536053269</v>
       </c>
       <c r="P7">
-        <v>363.5020274468898</v>
+        <v>363.7170975237289</v>
       </c>
       <c r="Q7">
-        <v>390.2020274468898</v>
+        <v>390.4170975237288</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.09840607802603896</v>
+        <v>0.09838151046896045</v>
       </c>
       <c r="T7">
         <v>1.024911508954008</v>
       </c>
       <c r="U7">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V7">
         <v>0.125</v>
       </c>
       <c r="W7">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>42.05408750079401</v>
+        <v>43.10101610345896</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1913,13 +1913,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.09599083389055811</v>
+        <v>0.09589402406879168</v>
       </c>
       <c r="C8">
-        <v>3579.939784340741</v>
+        <v>3583.579157859382</v>
       </c>
       <c r="D8">
-        <v>3637.620675938181</v>
+        <v>3641.260049456822</v>
       </c>
       <c r="E8">
         <v>-1496.667301693228</v>
@@ -1946,37 +1946,37 @@
         <v>425.55</v>
       </c>
       <c r="M8">
-        <v>12.14293378712256</v>
+        <v>11.84798053888614</v>
       </c>
       <c r="N8">
-        <v>413.4070662128775</v>
+        <v>413.7020194611139</v>
       </c>
       <c r="O8">
-        <v>51.67588327660968</v>
+        <v>51.71275243263923</v>
       </c>
       <c r="P8">
-        <v>361.7311829362678</v>
+        <v>361.9892670284746</v>
       </c>
       <c r="Q8">
-        <v>388.4311829362678</v>
+        <v>388.6892670284746</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.0988988420380586</v>
+        <v>0.09887404435532834</v>
       </c>
       <c r="T8">
         <v>1.034511911152159</v>
       </c>
       <c r="U8">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V8">
         <v>0.125</v>
       </c>
       <c r="W8">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.04507291732834</v>
+        <v>35.91751341954914</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1995,13 +1995,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.09597429167739337</v>
+        <v>0.09586526121308506</v>
       </c>
       <c r="C9">
-        <v>3545.629700008402</v>
+        <v>3549.865641061589</v>
       </c>
       <c r="D9">
-        <v>3638.424073538749</v>
+        <v>3642.660014591936</v>
       </c>
       <c r="E9">
         <v>-1461.553819760322</v>
@@ -2028,37 +2028,37 @@
         <v>425.55</v>
       </c>
       <c r="M9">
-        <v>14.16675608497632</v>
+        <v>13.82264396203383</v>
       </c>
       <c r="N9">
-        <v>411.3832439150237</v>
+        <v>411.7273560379662</v>
       </c>
       <c r="O9">
-        <v>51.42290548937796</v>
+        <v>51.46591950474577</v>
       </c>
       <c r="P9">
-        <v>359.9603384256457</v>
+        <v>360.2614365332204</v>
       </c>
       <c r="Q9">
-        <v>386.6603384256457</v>
+        <v>386.9614365332204</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.09940220312560555</v>
+        <v>0.09937717036828478</v>
       </c>
       <c r="T9">
         <v>1.044318773612635</v>
       </c>
       <c r="U9">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V9">
         <v>0.125</v>
       </c>
       <c r="W9">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.03863392913857</v>
+        <v>30.78644007389926</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2077,13 +2077,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.09595774946422859</v>
+        <v>0.09583649835737845</v>
       </c>
       <c r="C10">
-        <v>3511.319970628022</v>
+        <v>3516.15320117463</v>
       </c>
       <c r="D10">
-        <v>3639.227826091275</v>
+        <v>3644.061056637884</v>
       </c>
       <c r="E10">
         <v>-1426.440337827415</v>
@@ -2110,37 +2110,37 @@
         <v>425.55</v>
       </c>
       <c r="M10">
-        <v>16.19057838283008</v>
+        <v>15.79730738518152</v>
       </c>
       <c r="N10">
-        <v>409.3594216171699</v>
+        <v>409.7526926148185</v>
       </c>
       <c r="O10">
-        <v>51.16992770214624</v>
+        <v>51.21908657685231</v>
       </c>
       <c r="P10">
-        <v>358.1894939150237</v>
+        <v>358.5336060379662</v>
       </c>
       <c r="Q10">
-        <v>384.8894939150236</v>
+        <v>385.2336060379662</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.09991650684549044</v>
+        <v>0.09989123390326202</v>
       </c>
       <c r="T10">
         <v>1.054338828735296</v>
       </c>
       <c r="U10">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V10">
         <v>0.125</v>
       </c>
       <c r="W10">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.28380468799626</v>
+        <v>26.93813506466185</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2159,13 +2159,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.09594120725106385</v>
+        <v>0.09580773550167182</v>
       </c>
       <c r="C11">
-        <v>3477.010596434883</v>
+        <v>3482.441839441591</v>
       </c>
       <c r="D11">
-        <v>3640.031933831043</v>
+        <v>3645.463176837751</v>
       </c>
       <c r="E11">
         <v>-1391.326855894509</v>
@@ -2192,37 +2192,37 @@
         <v>425.55</v>
       </c>
       <c r="M11">
-        <v>18.21440068068383</v>
+        <v>17.77197080832921</v>
       </c>
       <c r="N11">
-        <v>407.3355993193162</v>
+        <v>407.7780291916708</v>
       </c>
       <c r="O11">
-        <v>50.91694991491453</v>
+        <v>50.97225364895885</v>
       </c>
       <c r="P11">
-        <v>356.4186494044017</v>
+        <v>356.805775542712</v>
       </c>
       <c r="Q11">
-        <v>383.1186494044017</v>
+        <v>383.5057755427119</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1004421139438344</v>
+        <v>0.1004165955379091</v>
       </c>
       <c r="T11">
         <v>1.064579104849664</v>
       </c>
       <c r="U11">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V11">
         <v>0.125</v>
       </c>
       <c r="W11">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.36338194488556</v>
+        <v>23.94500894636609</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2241,13 +2241,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.09592466503789909</v>
+        <v>0.09577897264596522</v>
       </c>
       <c r="C12">
-        <v>3442.70157766448</v>
+        <v>3448.731557107466</v>
       </c>
       <c r="D12">
-        <v>3640.836396993547</v>
+        <v>3646.866376436533</v>
       </c>
       <c r="E12">
         <v>-1356.213373961602</v>
@@ -2274,37 +2274,37 @@
         <v>425.55</v>
       </c>
       <c r="M12">
-        <v>20.2382229785376</v>
+        <v>19.7466342314769</v>
       </c>
       <c r="N12">
-        <v>405.3117770214624</v>
+        <v>405.8033657685231</v>
       </c>
       <c r="O12">
-        <v>50.6639721276828</v>
+        <v>50.72542072106539</v>
       </c>
       <c r="P12">
-        <v>354.6478048937796</v>
+        <v>355.0779450474577</v>
       </c>
       <c r="Q12">
-        <v>381.3478048937796</v>
+        <v>381.7779450474577</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1009794011999193</v>
+        <v>0.1009536318755483</v>
       </c>
       <c r="T12">
         <v>1.075046942655462</v>
       </c>
       <c r="U12">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V12">
         <v>0.125</v>
       </c>
       <c r="W12">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.02704375039701</v>
+        <v>21.55050805172948</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2323,13 +2323,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.09590812282473432</v>
+        <v>0.09575020979025861</v>
       </c>
       <c r="C13">
-        <v>3408.392914552517</v>
+        <v>3415.022355419174</v>
       </c>
       <c r="D13">
-        <v>3641.641215814491</v>
+        <v>3648.270656681148</v>
       </c>
       <c r="E13">
         <v>-1321.099892028695</v>
@@ -2356,37 +2356,37 @@
         <v>425.55</v>
       </c>
       <c r="M13">
-        <v>22.26204527639135</v>
+        <v>21.72129765462459</v>
       </c>
       <c r="N13">
-        <v>403.2879547236087</v>
+        <v>403.8287023453754</v>
       </c>
       <c r="O13">
-        <v>50.41099434045108</v>
+        <v>50.47858779317193</v>
       </c>
       <c r="P13">
-        <v>352.8769603831576</v>
+        <v>353.3501145522035</v>
       </c>
       <c r="Q13">
-        <v>379.5769603831575</v>
+        <v>380.0501145522035</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1015287623269274</v>
+        <v>0.101502736445494</v>
       </c>
       <c r="T13">
         <v>1.085750012771503</v>
       </c>
       <c r="U13">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V13">
         <v>0.125</v>
       </c>
       <c r="W13">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.11549431854273</v>
+        <v>19.59137095611771</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2405,13 +2405,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.09589158061156956</v>
+        <v>0.09572144693455198</v>
       </c>
       <c r="C14">
-        <v>3374.084607334903</v>
+        <v>3381.314235625553</v>
       </c>
       <c r="D14">
-        <v>3642.446390529783</v>
+        <v>3649.676018820434</v>
       </c>
       <c r="E14">
         <v>-1285.986410095788</v>
@@ -2438,37 +2438,37 @@
         <v>425.55</v>
       </c>
       <c r="M14">
-        <v>24.28586757424512</v>
+        <v>23.69596107777229</v>
       </c>
       <c r="N14">
-        <v>401.2641324257549</v>
+        <v>401.8540389222277</v>
       </c>
       <c r="O14">
-        <v>50.15801655321936</v>
+        <v>50.23175486527847</v>
       </c>
       <c r="P14">
-        <v>351.1061158725356</v>
+        <v>351.6222840569493</v>
       </c>
       <c r="Q14">
-        <v>377.8061158725355</v>
+        <v>378.3222840569493</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1020906089340949</v>
+        <v>0.1020643206647567</v>
       </c>
       <c r="T14">
         <v>1.09669633448109</v>
       </c>
       <c r="U14">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V14">
         <v>0.125</v>
       </c>
       <c r="W14">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.52253645866417</v>
+        <v>17.95875670977457</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2487,13 +2487,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.0958750383984048</v>
+        <v>0.09569268407884537</v>
       </c>
       <c r="C15">
-        <v>3339.776656247757</v>
+        <v>3347.607198977364</v>
       </c>
       <c r="D15">
-        <v>3643.251921375544</v>
+        <v>3651.082464105151</v>
       </c>
       <c r="E15">
         <v>-1250.872928162882</v>
@@ -2520,37 +2520,37 @@
         <v>425.55</v>
       </c>
       <c r="M15">
-        <v>26.30968987209888</v>
+        <v>25.67062450091997</v>
       </c>
       <c r="N15">
-        <v>399.2403101279011</v>
+        <v>399.87937549908</v>
       </c>
       <c r="O15">
-        <v>49.90503876598764</v>
+        <v>49.984921937385</v>
       </c>
       <c r="P15">
-        <v>349.3352713619135</v>
+        <v>349.894453561695</v>
       </c>
       <c r="Q15">
-        <v>376.0352713619135</v>
+        <v>376.594453561695</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1026653715552202</v>
+        <v>0.1026388148660714</v>
       </c>
       <c r="T15">
         <v>1.107894295770208</v>
       </c>
       <c r="U15">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V15">
         <v>0.125</v>
       </c>
       <c r="W15">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.17464903876693</v>
+        <v>16.57731388594576</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2569,13 +2569,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.09585849618524003</v>
+        <v>0.09566392122313874</v>
       </c>
       <c r="C16">
-        <v>3305.469061527408</v>
+        <v>3313.901246727298</v>
       </c>
       <c r="D16">
-        <v>3644.057808588101</v>
+        <v>3652.489993787992</v>
       </c>
       <c r="E16">
         <v>-1215.759446229975</v>
@@ -2602,37 +2602,37 @@
         <v>425.55</v>
       </c>
       <c r="M16">
-        <v>28.33351216995264</v>
+        <v>27.64528792406767</v>
       </c>
       <c r="N16">
-        <v>397.2164878300474</v>
+        <v>397.9047120759324</v>
       </c>
       <c r="O16">
-        <v>49.65206097875592</v>
+        <v>49.73808900949155</v>
       </c>
       <c r="P16">
-        <v>347.5644268512914</v>
+        <v>348.1666230664408</v>
       </c>
       <c r="Q16">
-        <v>374.2644268512914</v>
+        <v>374.8666230664408</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1032535007489298</v>
+        <v>0.1032266693976492</v>
       </c>
       <c r="T16">
         <v>1.119352674763723</v>
       </c>
       <c r="U16">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V16">
         <v>0.125</v>
       </c>
       <c r="W16">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.01931696456929</v>
+        <v>15.39322003694963</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2651,13 +2651,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.09584195397207528</v>
+        <v>0.09563515836743214</v>
       </c>
       <c r="C17">
-        <v>3271.161823410392</v>
+        <v>3280.196380129978</v>
       </c>
       <c r="D17">
-        <v>3644.864052403992</v>
+        <v>3653.898609123578</v>
       </c>
       <c r="E17">
         <v>-1180.645964297068</v>
@@ -2684,37 +2684,37 @@
         <v>425.55</v>
       </c>
       <c r="M17">
-        <v>30.3573344678064</v>
+        <v>29.61995134721536</v>
       </c>
       <c r="N17">
-        <v>395.1926655321936</v>
+        <v>395.9300486527846</v>
       </c>
       <c r="O17">
-        <v>49.3990831915242</v>
+        <v>49.49125608159808</v>
       </c>
       <c r="P17">
-        <v>345.7935823406694</v>
+        <v>346.4387925711866</v>
       </c>
       <c r="Q17">
-        <v>372.4935823406694</v>
+        <v>373.1387925711866</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.103855468276609</v>
+        <v>0.1038283558005583</v>
       </c>
       <c r="T17">
         <v>1.131080662674734</v>
       </c>
       <c r="U17">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V17">
         <v>0.125</v>
       </c>
       <c r="W17">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.01802916693133</v>
+        <v>14.36700536781965</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2733,13 +2733,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.09582541175891053</v>
+        <v>0.09560639551172552</v>
       </c>
       <c r="C18">
-        <v>3236.854942133456</v>
+        <v>3246.492600441964</v>
       </c>
       <c r="D18">
-        <v>3645.670653059963</v>
+        <v>3655.308311368471</v>
       </c>
       <c r="E18">
         <v>-1145.532482364162</v>
@@ -2766,37 +2766,37 @@
         <v>425.55</v>
       </c>
       <c r="M18">
-        <v>32.38115676566015</v>
+        <v>31.59461477036304</v>
       </c>
       <c r="N18">
-        <v>393.1688432343399</v>
+        <v>393.955385229637</v>
       </c>
       <c r="O18">
-        <v>49.14610540429248</v>
+        <v>49.24442315370462</v>
       </c>
       <c r="P18">
-        <v>344.0227378300474</v>
+        <v>344.7109620759323</v>
       </c>
       <c r="Q18">
-        <v>370.7227378300474</v>
+        <v>371.4109620759323</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1044717683644711</v>
+        <v>0.1044443680702033</v>
       </c>
       <c r="T18">
         <v>1.143087888393149</v>
       </c>
       <c r="U18">
-        <v>0.0576366166625341</v>
+        <v>0.0562366166625341</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.05043203957971733</v>
+        <v>0.04920703957971734</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.14190234399813</v>
+        <v>13.46906753233093</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2815,13 +2815,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.09597249454574575</v>
+        <v>0.09580075765601889</v>
       </c>
       <c r="C19">
-        <v>3194.58218246704</v>
+        <v>3201.87429985764</v>
       </c>
       <c r="D19">
-        <v>3638.511375326454</v>
+        <v>3645.803492717054</v>
       </c>
       <c r="E19">
         <v>-1110.419000431255</v>
@@ -2848,37 +2848,37 @@
         <v>425.55</v>
       </c>
       <c r="M19">
-        <v>35.06160117565927</v>
+        <v>34.46467198279986</v>
       </c>
       <c r="N19">
-        <v>390.4883988243407</v>
+        <v>391.0853280172001</v>
       </c>
       <c r="O19">
-        <v>48.81104985304259</v>
+        <v>48.88566600215002</v>
       </c>
       <c r="P19">
-        <v>341.6773489712981</v>
+        <v>342.1996620150501</v>
       </c>
       <c r="Q19">
-        <v>368.3773489712981</v>
+        <v>368.8996620150501</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.10510291905686</v>
+        <v>0.1050752240089963</v>
       </c>
       <c r="T19">
         <v>1.155384444851768</v>
       </c>
       <c r="U19">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V19">
         <v>0.125</v>
       </c>
       <c r="W19">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.13720953210284</v>
+        <v>12.34742637946409</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2897,13 +2897,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.095965577332581</v>
+        <v>0.09578511980031229</v>
       </c>
       <c r="C20">
-        <v>3159.804766811896</v>
+        <v>3167.523721177221</v>
       </c>
       <c r="D20">
-        <v>3638.847441604216</v>
+        <v>3646.566395969541</v>
       </c>
       <c r="E20">
         <v>-1075.305518498348</v>
@@ -2930,37 +2930,37 @@
         <v>425.55</v>
       </c>
       <c r="M20">
-        <v>37.12404830363922</v>
+        <v>36.4920056288469</v>
       </c>
       <c r="N20">
-        <v>388.4259516963608</v>
+        <v>389.0579943711531</v>
       </c>
       <c r="O20">
-        <v>48.5532439620451</v>
+        <v>48.63224929639414</v>
       </c>
       <c r="P20">
-        <v>339.8727077343157</v>
+        <v>340.4257450747589</v>
       </c>
       <c r="Q20">
-        <v>366.5727077343157</v>
+        <v>367.1257450747589</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1057494636685755</v>
+        <v>0.1057214666780039</v>
       </c>
       <c r="T20">
         <v>1.167980917321572</v>
       </c>
       <c r="U20">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V20">
         <v>0.125</v>
       </c>
       <c r="W20">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.46292011365269</v>
+        <v>11.66145824727165</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2979,13 +2979,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.09595866011941623</v>
+        <v>0.09576948194460567</v>
       </c>
       <c r="C21">
-        <v>3125.027413243118</v>
+        <v>3133.173461846536</v>
       </c>
       <c r="D21">
-        <v>3639.183569968345</v>
+        <v>3647.329618571763</v>
       </c>
       <c r="E21">
         <v>-1040.192036565441</v>
@@ -3012,37 +3012,37 @@
         <v>425.55</v>
       </c>
       <c r="M21">
-        <v>39.18649543161919</v>
+        <v>38.51933927489396</v>
       </c>
       <c r="N21">
-        <v>386.3635045683808</v>
+        <v>387.030660725106</v>
       </c>
       <c r="O21">
-        <v>48.29543807104761</v>
+        <v>48.37883259063825</v>
       </c>
       <c r="P21">
-        <v>338.0680664973332</v>
+        <v>338.6518281344678</v>
       </c>
       <c r="Q21">
-        <v>364.7680664973332</v>
+        <v>365.3518281344678</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1064119723447777</v>
+        <v>0.1063836659561227</v>
       </c>
       <c r="T21">
         <v>1.180888413802976</v>
       </c>
       <c r="U21">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V21">
         <v>0.125</v>
       </c>
       <c r="W21">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.8596085287236</v>
+        <v>11.04769728688892</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3061,13 +3061,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.09595174290625148</v>
+        <v>0.09575384408889905</v>
       </c>
       <c r="C22">
-        <v>3090.250121777912</v>
+        <v>3098.823522066148</v>
       </c>
       <c r="D22">
-        <v>3639.519760436046</v>
+        <v>3648.093160724282</v>
       </c>
       <c r="E22">
         <v>-1005.078554632535</v>
@@ -3094,37 +3094,37 @@
         <v>425.55</v>
       </c>
       <c r="M22">
-        <v>41.24894255959914</v>
+        <v>40.54667292094101</v>
       </c>
       <c r="N22">
-        <v>384.3010574404009</v>
+        <v>385.003327079059</v>
       </c>
       <c r="O22">
-        <v>48.03763218005011</v>
+        <v>48.12541588488237</v>
       </c>
       <c r="P22">
-        <v>336.2634252603508</v>
+        <v>336.8779111941766</v>
       </c>
       <c r="Q22">
-        <v>362.9634252603508</v>
+        <v>363.5779111941766</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.107091043737885</v>
+        <v>0.1070624202161945</v>
       </c>
       <c r="T22">
         <v>1.194118597696415</v>
       </c>
       <c r="U22">
-        <v>0.0587366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V22">
         <v>0.125</v>
       </c>
       <c r="W22">
-        <v>0.05139453957971733</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.31662810228742</v>
+        <v>10.49531242254448</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3143,13 +3143,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.09634907569308673</v>
+        <v>0.09573820623319244</v>
       </c>
       <c r="C23">
-        <v>3035.925625964164</v>
+        <v>3064.473902036782</v>
       </c>
       <c r="D23">
-        <v>3620.308746555205</v>
+        <v>3648.857022627823</v>
       </c>
       <c r="E23">
         <v>-969.9650726996282</v>
@@ -3176,45 +3176,45 @@
         <v>425.55</v>
       </c>
       <c r="M23">
-        <v>44.93363255287938</v>
+        <v>42.57400656698805</v>
       </c>
       <c r="N23">
-        <v>380.6163674471206</v>
+        <v>382.975993433012</v>
       </c>
       <c r="O23">
-        <v>47.57704593089008</v>
+        <v>47.8719991791265</v>
       </c>
       <c r="P23">
-        <v>333.0393215162305</v>
+        <v>335.1039942538855</v>
       </c>
       <c r="Q23">
-        <v>359.7393215162305</v>
+        <v>361.8039942538855</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1077873068118305</v>
+        <v>0.10775835812842</v>
       </c>
       <c r="T23">
         <v>1.207683722954245</v>
       </c>
       <c r="U23">
-        <v>0.0609366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05331953957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.470634262636095</v>
+        <v>9.995535640518554</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3225,13 +3225,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.09636140847992197</v>
+        <v>0.09604981837748582</v>
       </c>
       <c r="C24">
-        <v>3000.219099251362</v>
+        <v>3014.199181978634</v>
       </c>
       <c r="D24">
-        <v>3619.715701775309</v>
+        <v>3633.695784502582</v>
       </c>
       <c r="E24">
         <v>-934.8515907667215</v>
@@ -3258,37 +3258,37 @@
         <v>425.55</v>
       </c>
       <c r="M24">
-        <v>47.07332934111173</v>
+        <v>45.91458443732581</v>
       </c>
       <c r="N24">
-        <v>378.4766706588883</v>
+        <v>379.6354155626742</v>
       </c>
       <c r="O24">
-        <v>47.30958383236104</v>
+        <v>47.45442694533428</v>
       </c>
       <c r="P24">
-        <v>331.1670868265272</v>
+        <v>332.1809886173399</v>
       </c>
       <c r="Q24">
-        <v>357.8670868265272</v>
+        <v>358.8809886173399</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1085014227851079</v>
+        <v>0.1084721406024974</v>
       </c>
       <c r="T24">
         <v>1.221596671936635</v>
       </c>
       <c r="U24">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V24">
         <v>0.125</v>
       </c>
       <c r="W24">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.040150887061726</v>
+        <v>9.268296886817804</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3307,13 +3307,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.09637374126675721</v>
+        <v>0.09604905552177921</v>
       </c>
       <c r="C25">
-        <v>2964.512766800724</v>
+        <v>2979.122662332305</v>
       </c>
       <c r="D25">
-        <v>3619.122851257579</v>
+        <v>3633.732746789159</v>
       </c>
       <c r="E25">
         <v>-899.7381088338147</v>
@@ -3340,37 +3340,37 @@
         <v>425.55</v>
       </c>
       <c r="M25">
-        <v>49.21302612934409</v>
+        <v>48.00161100265881</v>
       </c>
       <c r="N25">
-        <v>376.3369738706559</v>
+        <v>377.5483889973412</v>
       </c>
       <c r="O25">
-        <v>47.04212173383199</v>
+        <v>47.19354862466765</v>
       </c>
       <c r="P25">
-        <v>329.2948521368239</v>
+        <v>330.3548403726736</v>
       </c>
       <c r="Q25">
-        <v>355.9948521368239</v>
+        <v>357.0548403726735</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1092340872252237</v>
+        <v>0.1092044628810964</v>
       </c>
       <c r="T25">
         <v>1.235870996217268</v>
       </c>
       <c r="U25">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V25">
         <v>0.125</v>
       </c>
       <c r="W25">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.647100848493825</v>
+        <v>8.865327456956159</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3389,13 +3389,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.09638607405359245</v>
+        <v>0.09604829266607258</v>
       </c>
       <c r="C26">
-        <v>2928.806628516817</v>
+        <v>2944.046143437952</v>
       </c>
       <c r="D26">
-        <v>3618.530194906577</v>
+        <v>3633.769709827713</v>
       </c>
       <c r="E26">
         <v>-864.6246269009081</v>
@@ -3422,37 +3422,37 @@
         <v>425.55</v>
       </c>
       <c r="M26">
-        <v>51.35272291757644</v>
+        <v>50.0886375679918</v>
       </c>
       <c r="N26">
-        <v>374.1972770824236</v>
+        <v>375.4613624320082</v>
       </c>
       <c r="O26">
-        <v>46.77465963530295</v>
+        <v>46.93267030400103</v>
       </c>
       <c r="P26">
-        <v>327.4226174471206</v>
+        <v>328.5286921280072</v>
       </c>
       <c r="Q26">
-        <v>354.1226174471206</v>
+        <v>355.2286921280072</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1099860323085004</v>
+        <v>0.1099560567986058</v>
       </c>
       <c r="T26">
         <v>1.250520960610551</v>
       </c>
       <c r="U26">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V26">
         <v>0.125</v>
       </c>
       <c r="W26">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.286804979806581</v>
+        <v>8.495938812916322</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3471,13 +3471,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.09639840684042766</v>
+        <v>0.09604752981036596</v>
       </c>
       <c r="C27">
-        <v>2893.100684304268</v>
+        <v>2908.969625295596</v>
       </c>
       <c r="D27">
-        <v>3617.937732626935</v>
+        <v>3633.806673618263</v>
       </c>
       <c r="E27">
         <v>-829.5111449680014</v>
@@ -3504,37 +3504,37 @@
         <v>425.55</v>
       </c>
       <c r="M27">
-        <v>53.49241970580879</v>
+        <v>52.17566413332479</v>
       </c>
       <c r="N27">
-        <v>372.0575802941912</v>
+        <v>373.3743358666752</v>
       </c>
       <c r="O27">
-        <v>46.5071975367739</v>
+        <v>46.6717919833344</v>
       </c>
       <c r="P27">
-        <v>325.5503827574173</v>
+        <v>326.7025438833408</v>
       </c>
       <c r="Q27">
-        <v>352.2503827574173</v>
+        <v>353.4025438833408</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1107580292606644</v>
+        <v>0.1107276932205822</v>
       </c>
       <c r="T27">
         <v>1.265561590720987</v>
       </c>
       <c r="U27">
-        <v>0.0609366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V27">
         <v>0.125</v>
       </c>
       <c r="W27">
-        <v>0.05331953957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>7.955332780614318</v>
+        <v>8.156101260399666</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3553,13 +3553,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.09675198962726293</v>
+        <v>0.09604676695465936</v>
       </c>
       <c r="C28">
-        <v>2841.083353485816</v>
+        <v>2873.893107905261</v>
       </c>
       <c r="D28">
-        <v>3601.03388374139</v>
+        <v>3633.843638160835</v>
       </c>
       <c r="E28">
         <v>-794.3976630350948</v>
@@ -3586,45 +3586,45 @@
         <v>425.55</v>
       </c>
       <c r="M28">
-        <v>57.00154228942451</v>
+        <v>54.26269069865778</v>
       </c>
       <c r="N28">
-        <v>368.5484577105755</v>
+        <v>371.2873093013422</v>
       </c>
       <c r="O28">
-        <v>46.06855721382194</v>
+        <v>46.41091366266778</v>
       </c>
       <c r="P28">
-        <v>322.4799004967536</v>
+        <v>324.8763956386745</v>
       </c>
       <c r="Q28">
-        <v>349.1799004967536</v>
+        <v>351.5763956386745</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1115508909953195</v>
+        <v>0.1115201846809903</v>
       </c>
       <c r="T28">
         <v>1.281008724347921</v>
       </c>
       <c r="U28">
-        <v>0.0624366166625341</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05463203957971734</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.465587471989373</v>
+        <v>7.842405058076603</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3635,13 +3635,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.09677744741409816</v>
+        <v>0.09623500409895275</v>
       </c>
       <c r="C29">
-        <v>2804.758896542377</v>
+        <v>2829.681248829607</v>
       </c>
       <c r="D29">
-        <v>3599.822908730858</v>
+        <v>3624.745261018088</v>
       </c>
       <c r="E29">
         <v>-759.284181102188</v>
@@ -3668,37 +3668,37 @@
         <v>425.55</v>
       </c>
       <c r="M29">
-        <v>59.19390930055622</v>
+        <v>57.10816847374156</v>
       </c>
       <c r="N29">
-        <v>366.3560906994438</v>
+        <v>368.4418315262585</v>
       </c>
       <c r="O29">
-        <v>45.79451133743047</v>
+        <v>46.05522894078231</v>
       </c>
       <c r="P29">
-        <v>320.5615793620133</v>
+        <v>322.3866025854762</v>
       </c>
       <c r="Q29">
-        <v>347.2615793620133</v>
+        <v>349.0866025854762</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1123654749692801</v>
+        <v>0.1123343882362042</v>
       </c>
       <c r="T29">
         <v>1.29687906711532</v>
       </c>
       <c r="U29">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V29">
         <v>0.125</v>
       </c>
       <c r="W29">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.189084232286062</v>
+        <v>7.45164853598253</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3717,13 +3717,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.09680290520093339</v>
+        <v>0.09624124124324612</v>
       </c>
       <c r="C30">
-        <v>2768.435253791496</v>
+        <v>2794.267076452096</v>
       </c>
       <c r="D30">
-        <v>3598.612747912883</v>
+        <v>3624.444570573484</v>
       </c>
       <c r="E30">
         <v>-724.1706991692813</v>
@@ -3750,37 +3750,37 @@
         <v>425.55</v>
       </c>
       <c r="M30">
-        <v>61.38627631168793</v>
+        <v>59.22328582462088</v>
       </c>
       <c r="N30">
-        <v>364.1637236883121</v>
+        <v>366.3267141753792</v>
       </c>
       <c r="O30">
-        <v>45.52046546103901</v>
+        <v>45.79083927192239</v>
       </c>
       <c r="P30">
-        <v>318.6432582272731</v>
+        <v>320.5358749034568</v>
       </c>
       <c r="Q30">
-        <v>345.3432582272731</v>
+        <v>347.2358749034568</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1132026862758508</v>
+        <v>0.1131712085568407</v>
       </c>
       <c r="T30">
         <v>1.313190252737368</v>
       </c>
       <c r="U30">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V30">
         <v>0.125</v>
       </c>
       <c r="W30">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.932331223990132</v>
+        <v>7.185518231126012</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3799,13 +3799,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.09682836298776865</v>
+        <v>0.09624747838753951</v>
       </c>
       <c r="C31">
-        <v>2732.112424412318</v>
+        <v>2758.852953957949</v>
       </c>
       <c r="D31">
-        <v>3597.403400466612</v>
+        <v>3624.143930012243</v>
       </c>
       <c r="E31">
         <v>-689.0572172363748</v>
@@ -3832,37 +3832,37 @@
         <v>425.55</v>
       </c>
       <c r="M31">
-        <v>63.57864332281964</v>
+        <v>61.33840317550019</v>
       </c>
       <c r="N31">
-        <v>361.9713566771804</v>
+        <v>364.2115968244998</v>
       </c>
       <c r="O31">
-        <v>45.24641958464755</v>
+        <v>45.52644960306247</v>
       </c>
       <c r="P31">
-        <v>316.7249370925329</v>
+        <v>318.6851472214373</v>
       </c>
       <c r="Q31">
-        <v>343.4249370925328</v>
+        <v>345.3851472214373</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1140634809995079</v>
+        <v>0.1140316012808753</v>
       </c>
       <c r="T31">
         <v>1.329960908376939</v>
       </c>
       <c r="U31">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V31">
         <v>0.125</v>
       </c>
       <c r="W31">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.693285319714611</v>
+        <v>6.937741740397529</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3881,13 +3881,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.09685382077460387</v>
+        <v>0.09625371553183287</v>
       </c>
       <c r="C32">
-        <v>2695.7904075851</v>
+        <v>2723.438881334755</v>
       </c>
       <c r="D32">
-        <v>3596.1948655723</v>
+        <v>3623.843339321956</v>
       </c>
       <c r="E32">
         <v>-653.943735303468</v>
@@ -3914,37 +3914,37 @@
         <v>425.55</v>
       </c>
       <c r="M32">
-        <v>65.77101033395135</v>
+        <v>63.45352052637951</v>
       </c>
       <c r="N32">
-        <v>359.7789896660487</v>
+        <v>362.0964794736205</v>
       </c>
       <c r="O32">
-        <v>44.97237370825609</v>
+        <v>45.26205993420256</v>
       </c>
       <c r="P32">
-        <v>314.8066159577926</v>
+        <v>316.8344195394179</v>
       </c>
       <c r="Q32">
-        <v>341.5066159577926</v>
+        <v>343.5344195394179</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1149488698581267</v>
+        <v>0.1149165766541681</v>
       </c>
       <c r="T32">
         <v>1.347210725606212</v>
       </c>
       <c r="U32">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V32">
         <v>0.125</v>
       </c>
       <c r="W32">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.470175809057457</v>
+        <v>6.706483682384278</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3963,13 +3963,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.09687927856143913</v>
+        <v>0.09625995267612628</v>
       </c>
       <c r="C33">
-        <v>2659.469202491191</v>
+        <v>2688.024858570103</v>
       </c>
       <c r="D33">
-        <v>3594.987142411298</v>
+        <v>3623.54279849021</v>
       </c>
       <c r="E33">
         <v>-618.8302533705612</v>
@@ -3996,37 +3996,37 @@
         <v>425.55</v>
       </c>
       <c r="M33">
-        <v>67.96337734508307</v>
+        <v>65.56863787725884</v>
       </c>
       <c r="N33">
-        <v>357.5866226549169</v>
+        <v>359.9813621227412</v>
       </c>
       <c r="O33">
-        <v>44.69832783186462</v>
+        <v>44.99767026534265</v>
       </c>
       <c r="P33">
-        <v>312.8882948230523</v>
+        <v>314.9836918573985</v>
       </c>
       <c r="Q33">
-        <v>339.5882948230523</v>
+        <v>341.6836918573985</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1158599221619228</v>
+        <v>0.1158272034875564</v>
       </c>
       <c r="T33">
         <v>1.364960537537782</v>
       </c>
       <c r="U33">
-        <v>0.0624366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V33">
         <v>0.125</v>
       </c>
       <c r="W33">
-        <v>0.05463203957971734</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.261460460378182</v>
+        <v>6.490145499081558</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4045,13 +4045,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.09729673634827435</v>
+        <v>0.09626618982041966</v>
       </c>
       <c r="C34">
-        <v>2604.666508497319</v>
+        <v>2652.610885651591</v>
       </c>
       <c r="D34">
-        <v>3575.297930350333</v>
+        <v>3623.242307504605</v>
       </c>
       <c r="E34">
         <v>-583.7167714376546</v>
@@ -4078,45 +4078,45 @@
         <v>425.55</v>
       </c>
       <c r="M34">
-        <v>71.728828346809</v>
+        <v>67.68375522813814</v>
       </c>
       <c r="N34">
-        <v>353.821171653191</v>
+        <v>357.8662447718619</v>
       </c>
       <c r="O34">
-        <v>44.22764645664888</v>
+        <v>44.73328059648274</v>
       </c>
       <c r="P34">
-        <v>309.5935251965421</v>
+        <v>313.1329641753791</v>
       </c>
       <c r="Q34">
-        <v>336.2935251965421</v>
+        <v>339.8329641753791</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.116797770121713</v>
+        <v>0.1167646134631031</v>
       </c>
       <c r="T34">
         <v>1.383232402761458</v>
       </c>
       <c r="U34">
-        <v>0.0638366166625341</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.05585703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y34">
-        <v>5.932761064246932</v>
+        <v>6.287328452235261</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4127,13 +4127,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.09733444413510961</v>
+        <v>0.09656117696471303</v>
       </c>
       <c r="C35">
-        <v>2567.785170456083</v>
+        <v>2603.342310681721</v>
       </c>
       <c r="D35">
-        <v>3573.530074242003</v>
+        <v>3609.087214467642</v>
       </c>
       <c r="E35">
         <v>-548.6032895047479</v>
@@ -4160,37 +4160,37 @@
         <v>425.55</v>
       </c>
       <c r="M35">
-        <v>73.97035423264678</v>
+        <v>70.95761748280339</v>
       </c>
       <c r="N35">
-        <v>351.5796457673532</v>
+        <v>354.5923825171966</v>
       </c>
       <c r="O35">
-        <v>43.94745572091915</v>
+        <v>44.32404781464957</v>
       </c>
       <c r="P35">
-        <v>307.6321900464341</v>
+        <v>310.268334702547</v>
       </c>
       <c r="Q35">
-        <v>334.3321900464341</v>
+        <v>336.968334702547</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1177636135429894</v>
+        <v>0.1177300058259796</v>
       </c>
       <c r="T35">
         <v>1.402049696797781</v>
       </c>
       <c r="U35">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V35">
         <v>0.125</v>
       </c>
       <c r="W35">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.752980425936418</v>
+        <v>5.9972419466188</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4209,13 +4209,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.09737215192194483</v>
+        <v>0.09657616410900642</v>
       </c>
       <c r="C36">
-        <v>2530.90557983321</v>
+        <v>2567.512615529953</v>
       </c>
       <c r="D36">
-        <v>3571.763965552038</v>
+        <v>3608.371001248781</v>
       </c>
       <c r="E36">
         <v>-513.4898075718411</v>
@@ -4242,37 +4242,37 @@
         <v>425.55</v>
       </c>
       <c r="M36">
-        <v>76.21188011848456</v>
+        <v>73.10784831561561</v>
       </c>
       <c r="N36">
-        <v>349.3381198815155</v>
+        <v>352.4421516843844</v>
       </c>
       <c r="O36">
-        <v>43.66726498518943</v>
+        <v>44.05526896054805</v>
       </c>
       <c r="P36">
-        <v>305.670854896326</v>
+        <v>308.3868827238363</v>
       </c>
       <c r="Q36">
-        <v>332.370854896326</v>
+        <v>335.0868827238363</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1187587249467287</v>
+        <v>0.1187246525028826</v>
       </c>
       <c r="T36">
         <v>1.421437211865507</v>
       </c>
       <c r="U36">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V36">
         <v>0.125</v>
       </c>
       <c r="W36">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.583775119291229</v>
+        <v>5.8208524776006</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4291,13 +4291,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.09740985970878008</v>
+        <v>0.09659115125329981</v>
       </c>
       <c r="C37">
-        <v>2494.027734039154</v>
+        <v>2531.683204582789</v>
       </c>
       <c r="D37">
-        <v>3569.999601690889</v>
+        <v>3607.655072234523</v>
       </c>
       <c r="E37">
         <v>-478.3763256389343</v>
@@ -4324,37 +4324,37 @@
         <v>425.55</v>
       </c>
       <c r="M37">
-        <v>78.45340600432235</v>
+        <v>75.25807914842784</v>
       </c>
       <c r="N37">
-        <v>347.0965939956777</v>
+        <v>350.2919208515722</v>
       </c>
       <c r="O37">
-        <v>43.38707424945971</v>
+        <v>43.78649010644652</v>
       </c>
       <c r="P37">
-        <v>303.7095197462179</v>
+        <v>306.5054307451256</v>
       </c>
       <c r="Q37">
-        <v>330.4095197462179</v>
+        <v>333.2054307451256</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1197844551628908</v>
+        <v>0.1197499036929212</v>
       </c>
       <c r="T37">
         <v>1.441421265858394</v>
       </c>
       <c r="U37">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V37">
         <v>0.125</v>
       </c>
       <c r="W37">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.42423868731148</v>
+        <v>5.654542406812012</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4373,13 +4373,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.09744756749561533</v>
+        <v>0.09660613839759319</v>
       </c>
       <c r="C38">
-        <v>2457.151630489484</v>
+        <v>2495.854077671097</v>
       </c>
       <c r="D38">
-        <v>3568.236980074125</v>
+        <v>3606.939427255738</v>
       </c>
       <c r="E38">
         <v>-443.262843706028</v>
@@ -4406,37 +4406,37 @@
         <v>425.55</v>
       </c>
       <c r="M38">
-        <v>80.69493189016011</v>
+        <v>77.40830998124005</v>
       </c>
       <c r="N38">
-        <v>344.8550681098399</v>
+        <v>348.14169001876</v>
       </c>
       <c r="O38">
-        <v>43.10688351372999</v>
+        <v>43.51771125234499</v>
       </c>
       <c r="P38">
-        <v>301.7481845961099</v>
+        <v>304.623978766415</v>
       </c>
       <c r="Q38">
-        <v>328.4481845961099</v>
+        <v>331.3239787664149</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1208422394483079</v>
+        <v>0.1208071939826484</v>
       </c>
       <c r="T38">
         <v>1.462029821538559</v>
       </c>
       <c r="U38">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V38">
         <v>0.125</v>
       </c>
       <c r="W38">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.273565390441718</v>
+        <v>5.497471784400568</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4455,13 +4455,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.09748527528245057</v>
+        <v>0.09662112554188658</v>
       </c>
       <c r="C39">
-        <v>2420.27726660487</v>
+        <v>2460.025234625878</v>
       </c>
       <c r="D39">
-        <v>3566.476098122417</v>
+        <v>3606.224066143425</v>
       </c>
       <c r="E39">
         <v>-408.1493617731212</v>
@@ -4488,37 +4488,37 @@
         <v>425.55</v>
       </c>
       <c r="M39">
-        <v>82.93645777599789</v>
+        <v>79.55854081405228</v>
       </c>
       <c r="N39">
-        <v>342.6135422240021</v>
+        <v>345.9914591859477</v>
       </c>
       <c r="O39">
-        <v>42.82669277800026</v>
+        <v>43.24893239824347</v>
       </c>
       <c r="P39">
-        <v>299.7868494460018</v>
+        <v>302.7425267877043</v>
       </c>
       <c r="Q39">
-        <v>326.4868494460018</v>
+        <v>329.4425267877043</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1219336041872304</v>
+        <v>0.121898049043478</v>
       </c>
       <c r="T39">
         <v>1.483292617081587</v>
       </c>
       <c r="U39">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V39">
         <v>0.125</v>
       </c>
       <c r="W39">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.131036596105455</v>
+        <v>5.348891465903255</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4537,13 +4537,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.09752298306928579</v>
+        <v>0.09663611268617996</v>
       </c>
       <c r="C40">
-        <v>2383.404639811071</v>
+        <v>2424.196675278268</v>
       </c>
       <c r="D40">
-        <v>3564.716953261525</v>
+        <v>3605.508988728723</v>
       </c>
       <c r="E40">
         <v>-373.0358798402144</v>
@@ -4570,37 +4570,37 @@
         <v>425.55</v>
       </c>
       <c r="M40">
-        <v>85.17798366183568</v>
+        <v>81.70877164686451</v>
       </c>
       <c r="N40">
-        <v>340.3720163381643</v>
+        <v>343.8412283531355</v>
       </c>
       <c r="O40">
-        <v>42.54650204227054</v>
+        <v>42.98015354414194</v>
       </c>
       <c r="P40">
-        <v>297.8255142958938</v>
+        <v>300.8610748089936</v>
       </c>
       <c r="Q40">
-        <v>324.5255142958937</v>
+        <v>327.5610748089936</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1230601742403116</v>
+        <v>0.1230240929772377</v>
       </c>
       <c r="T40">
         <v>1.505241309255034</v>
       </c>
       <c r="U40">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V40">
         <v>0.125</v>
       </c>
       <c r="W40">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.996009317260574</v>
+        <v>5.208131164168958</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4619,13 +4619,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.09756069085612104</v>
+        <v>0.09665109983047335</v>
       </c>
       <c r="C41">
-        <v>2346.533747538922</v>
+        <v>2388.36839945954</v>
       </c>
       <c r="D41">
-        <v>3562.959542922283</v>
+        <v>3604.794194842902</v>
       </c>
       <c r="E41">
         <v>-337.9223979073076</v>
@@ -4652,37 +4652,37 @@
         <v>425.55</v>
       </c>
       <c r="M41">
-        <v>87.41950954767347</v>
+        <v>83.85900247967673</v>
       </c>
       <c r="N41">
-        <v>338.1304904523265</v>
+        <v>341.6909975203233</v>
       </c>
       <c r="O41">
-        <v>42.26631130654081</v>
+        <v>42.71137469004041</v>
       </c>
       <c r="P41">
-        <v>295.8641791457857</v>
+        <v>298.9796228302828</v>
       </c>
       <c r="Q41">
-        <v>322.5641791457857</v>
+        <v>325.6796228302828</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1242236810164447</v>
+        <v>0.1241870563842354</v>
       </c>
       <c r="T41">
         <v>1.52790963068007</v>
       </c>
       <c r="U41">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V41">
         <v>0.125</v>
       </c>
       <c r="W41">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.867906514253892</v>
+        <v>5.074589339446677</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4701,13 +4701,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09759839864295627</v>
+        <v>0.09666608697476675</v>
       </c>
       <c r="C42">
-        <v>2309.664587224323</v>
+        <v>2352.540407001095</v>
       </c>
       <c r="D42">
-        <v>3561.203864540591</v>
+        <v>3604.079684317363</v>
       </c>
       <c r="E42">
         <v>-302.8089159744011</v>
@@ -4734,37 +4734,37 @@
         <v>425.55</v>
       </c>
       <c r="M42">
-        <v>89.66103543351124</v>
+        <v>86.00923331248894</v>
       </c>
       <c r="N42">
-        <v>335.8889645664888</v>
+        <v>339.5407666875111</v>
       </c>
       <c r="O42">
-        <v>41.9861205708111</v>
+        <v>42.44259583593888</v>
       </c>
       <c r="P42">
-        <v>293.9028439956777</v>
+        <v>297.0981708515721</v>
       </c>
       <c r="Q42">
-        <v>320.6028439956777</v>
+        <v>323.7981708515721</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1254259713517822</v>
+        <v>0.125388785238133</v>
       </c>
       <c r="T42">
         <v>1.551333562819274</v>
       </c>
       <c r="U42">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V42">
         <v>0.125</v>
       </c>
       <c r="W42">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.746208851397546</v>
+        <v>4.947724605960511</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4783,13 +4783,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09763610642979152</v>
+        <v>0.09668107411906011</v>
       </c>
       <c r="C43">
-        <v>2272.797156308226</v>
+        <v>2316.712697734476</v>
       </c>
       <c r="D43">
-        <v>3559.4499155574</v>
+        <v>3603.365456983651</v>
       </c>
       <c r="E43">
         <v>-267.6954340414943</v>
@@ -4816,37 +4816,37 @@
         <v>425.55</v>
       </c>
       <c r="M43">
-        <v>91.90256131934903</v>
+        <v>88.15946414530117</v>
       </c>
       <c r="N43">
-        <v>333.647438680651</v>
+        <v>337.3905358546988</v>
       </c>
       <c r="O43">
-        <v>41.70592983508137</v>
+        <v>42.17381698183735</v>
       </c>
       <c r="P43">
-        <v>291.9415088455696</v>
+        <v>295.2167188728615</v>
       </c>
       <c r="Q43">
-        <v>318.6415088455696</v>
+        <v>321.9167188728615</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1266690172917075</v>
+        <v>0.1266312506633492</v>
       </c>
       <c r="T43">
         <v>1.575551526556417</v>
       </c>
       <c r="U43">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V43">
         <v>0.125</v>
       </c>
       <c r="W43">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.630447659900044</v>
+        <v>4.827048396059035</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4865,13 +4865,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09767381421662677</v>
+        <v>0.09669606126335351</v>
       </c>
       <c r="C44">
-        <v>2235.931452236618</v>
+        <v>2280.88527149135</v>
       </c>
       <c r="D44">
-        <v>3557.697693418699</v>
+        <v>3602.651512673431</v>
       </c>
       <c r="E44">
         <v>-232.5819521085878</v>
@@ -4898,37 +4898,37 @@
         <v>425.55</v>
       </c>
       <c r="M44">
-        <v>94.14408720518681</v>
+        <v>90.3096949781134</v>
       </c>
       <c r="N44">
-        <v>331.4059127948132</v>
+        <v>335.2403050218866</v>
       </c>
       <c r="O44">
-        <v>41.42573909935165</v>
+        <v>41.90503812773583</v>
       </c>
       <c r="P44">
-        <v>289.9801736954616</v>
+        <v>293.3352668941508</v>
       </c>
       <c r="Q44">
-        <v>316.6801736954616</v>
+        <v>320.0352668941508</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1279549268847336</v>
+        <v>0.1279165597239176</v>
       </c>
       <c r="T44">
         <v>1.600604592491393</v>
       </c>
       <c r="U44">
-        <v>0.0638366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V44">
         <v>0.125</v>
       </c>
       <c r="W44">
-        <v>0.05585703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.520198906092901</v>
+        <v>4.712118672343344</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4947,13 +4947,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.098689772003462</v>
+        <v>0.09671104840764688</v>
       </c>
       <c r="C45">
-        <v>2154.248892783636</v>
+        <v>2245.058128103522</v>
       </c>
       <c r="D45">
-        <v>3511.128615898623</v>
+        <v>3601.93785121851</v>
       </c>
       <c r="E45">
         <v>-197.468470175681</v>
@@ -4980,45 +4980,45 @@
         <v>425.55</v>
       </c>
       <c r="M45">
-        <v>100.3113003711235</v>
+        <v>92.45992581092563</v>
       </c>
       <c r="N45">
-        <v>325.2386996288765</v>
+        <v>333.0900741890744</v>
       </c>
       <c r="O45">
-        <v>40.65483745360956</v>
+        <v>41.63625927363429</v>
       </c>
       <c r="P45">
-        <v>284.5838621752669</v>
+        <v>291.45381491544</v>
       </c>
       <c r="Q45">
-        <v>311.2838621752669</v>
+        <v>318.15381491544</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1292859561126027</v>
+        <v>0.1292469673480148</v>
       </c>
       <c r="T45">
         <v>1.626536713371455</v>
       </c>
       <c r="U45">
-        <v>0.06643661666253409</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.05813203957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.242293723893369</v>
+        <v>4.602534517172567</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5029,13 +5029,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09875022979029725</v>
+        <v>0.09768853555194028</v>
       </c>
       <c r="C46">
-        <v>2116.402573690758</v>
+        <v>2164.001236225035</v>
       </c>
       <c r="D46">
-        <v>3508.395778738653</v>
+        <v>3555.994441272929</v>
       </c>
       <c r="E46">
         <v>-162.3549882427744</v>
@@ -5062,37 +5062,37 @@
         <v>425.55</v>
       </c>
       <c r="M46">
-        <v>102.6441213099869</v>
+        <v>98.47263965635757</v>
       </c>
       <c r="N46">
-        <v>322.9058786900131</v>
+        <v>327.0773603436425</v>
       </c>
       <c r="O46">
-        <v>40.36323483625164</v>
+        <v>40.88467004295531</v>
       </c>
       <c r="P46">
-        <v>282.5426438537615</v>
+        <v>286.1926903006872</v>
       </c>
       <c r="Q46">
-        <v>309.2426438537615</v>
+        <v>312.8926903006871</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.13066452209861</v>
+        <v>0.1306248895301154</v>
       </c>
       <c r="T46">
         <v>1.653394981425805</v>
       </c>
       <c r="U46">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V46">
         <v>0.125</v>
       </c>
       <c r="W46">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.145877957441248</v>
+        <v>4.321504952899125</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5111,13 +5111,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09881068757713249</v>
+        <v>0.09772539769623365</v>
       </c>
       <c r="C47">
-        <v>2078.560505419402</v>
+        <v>2127.178098139917</v>
       </c>
       <c r="D47">
-        <v>3505.667192400203</v>
+        <v>3554.284785120718</v>
       </c>
       <c r="E47">
         <v>-127.2415063098676</v>
@@ -5144,37 +5144,37 @@
         <v>425.55</v>
       </c>
       <c r="M47">
-        <v>104.9769422488502</v>
+        <v>100.7106541940021</v>
       </c>
       <c r="N47">
-        <v>320.5730577511498</v>
+        <v>324.8393458059979</v>
       </c>
       <c r="O47">
-        <v>40.07163221889373</v>
+        <v>40.60491822574974</v>
       </c>
       <c r="P47">
-        <v>280.5014255322561</v>
+        <v>284.2344275802482</v>
       </c>
       <c r="Q47">
-        <v>307.2014255322561</v>
+        <v>310.9344275802482</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1320932177568358</v>
+        <v>0.1320529179733834</v>
       </c>
       <c r="T47">
         <v>1.681229913773041</v>
       </c>
       <c r="U47">
-        <v>0.06643661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V47">
         <v>0.125</v>
       </c>
       <c r="W47">
-        <v>0.05813203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.053747336164776</v>
+        <v>4.225471509501366</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5193,13 +5193,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09995789536396772</v>
+        <v>0.09776225984052705</v>
       </c>
       <c r="C48">
-        <v>1992.463800516463</v>
+        <v>2090.356603206717</v>
       </c>
       <c r="D48">
-        <v>3454.683969430171</v>
+        <v>3552.576772120425</v>
       </c>
       <c r="E48">
         <v>-92.12802437696087</v>
@@ -5226,45 +5226,45 @@
         <v>425.55</v>
       </c>
       <c r="M48">
-        <v>111.6708576437806</v>
+        <v>102.9486687316466</v>
       </c>
       <c r="N48">
-        <v>313.8791423562194</v>
+        <v>322.6013312683534</v>
       </c>
       <c r="O48">
-        <v>39.23489279452743</v>
+        <v>40.32516640854418</v>
       </c>
       <c r="P48">
-        <v>274.644249561692</v>
+        <v>282.2761648598092</v>
       </c>
       <c r="Q48">
-        <v>301.344249561692</v>
+        <v>308.9761648598092</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1335748280690699</v>
+        <v>0.1335338363589946</v>
       </c>
       <c r="T48">
         <v>1.710095769540545</v>
       </c>
       <c r="U48">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V48">
         <v>0.125</v>
       </c>
       <c r="W48">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y48">
-        <v>3.810752500508808</v>
+        <v>4.133613433207858</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5275,13 +5275,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.100041978150803</v>
+        <v>0.09779912198482042</v>
       </c>
       <c r="C49">
-        <v>1953.671848191186</v>
+        <v>2053.536749057726</v>
       </c>
       <c r="D49">
-        <v>3451.0054990378</v>
+        <v>3550.87039990434</v>
       </c>
       <c r="E49">
         <v>-57.01454244405409</v>
@@ -5308,45 +5308,45 @@
         <v>425.55</v>
       </c>
       <c r="M49">
-        <v>114.0984849838628</v>
+        <v>105.1866832692911</v>
       </c>
       <c r="N49">
-        <v>311.4515150161373</v>
+        <v>320.363316730709</v>
       </c>
       <c r="O49">
-        <v>38.93143937701716</v>
+        <v>40.04541459133862</v>
       </c>
       <c r="P49">
-        <v>272.5200756391201</v>
+        <v>280.3179021393703</v>
       </c>
       <c r="Q49">
-        <v>299.2200756391201</v>
+        <v>307.0179021393703</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1351123482044072</v>
+        <v>0.1350706384572703</v>
       </c>
       <c r="T49">
         <v>1.740050902884181</v>
       </c>
       <c r="U49">
-        <v>0.06913661666253409</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.06049453957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.72967266007245</v>
+        <v>4.045664211224713</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5357,13 +5357,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.1001260609376382</v>
+        <v>0.09930598412911379</v>
       </c>
       <c r="C50">
-        <v>1914.887721040199</v>
+        <v>1950.04572875971</v>
       </c>
       <c r="D50">
-        <v>3447.33485381972</v>
+        <v>3482.492861539231</v>
       </c>
       <c r="E50">
         <v>-21.90106051114753</v>
@@ -5390,37 +5390,37 @@
         <v>425.55</v>
       </c>
       <c r="M50">
-        <v>116.526112323945</v>
+        <v>113.3237627716639</v>
       </c>
       <c r="N50">
-        <v>309.023887676055</v>
+        <v>312.2262372283361</v>
       </c>
       <c r="O50">
-        <v>38.62798595950688</v>
+        <v>39.02827965354201</v>
       </c>
       <c r="P50">
-        <v>270.3959017165482</v>
+        <v>273.1979575747941</v>
       </c>
       <c r="Q50">
-        <v>297.0959017165482</v>
+        <v>299.8979575747941</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1367090037295652</v>
+        <v>0.1366665483285567</v>
       </c>
       <c r="T50">
         <v>1.771158156741033</v>
       </c>
       <c r="U50">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V50">
         <v>0.125</v>
       </c>
       <c r="W50">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.651971146320941</v>
+        <v>3.755170050763678</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5439,13 +5439,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.1002101437244734</v>
+        <v>0.09937347127340718</v>
       </c>
       <c r="C51">
-        <v>1876.11139412041</v>
+        <v>1911.931412529936</v>
       </c>
       <c r="D51">
-        <v>3443.672008832838</v>
+        <v>3479.492027242363</v>
       </c>
       <c r="E51">
         <v>13.21242142175902</v>
@@ -5472,37 +5472,37 @@
         <v>425.55</v>
       </c>
       <c r="M51">
-        <v>118.9537396640271</v>
+        <v>115.6846744960735</v>
       </c>
       <c r="N51">
-        <v>306.5962603359729</v>
+        <v>309.8653255039265</v>
       </c>
       <c r="O51">
-        <v>38.32453254199661</v>
+        <v>38.73316568799081</v>
       </c>
       <c r="P51">
-        <v>268.2717277939763</v>
+        <v>271.1321598159357</v>
       </c>
       <c r="Q51">
-        <v>294.9717277939762</v>
+        <v>297.8321598159357</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1383682731968862</v>
+        <v>0.1383250429006778</v>
       </c>
       <c r="T51">
         <v>1.803485302905998</v>
       </c>
       <c r="U51">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V51">
         <v>0.125</v>
       </c>
       <c r="W51">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.577441122926637</v>
+        <v>3.678533927278705</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5521,13 +5521,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.1002942265113087</v>
+        <v>0.09944095841770058</v>
       </c>
       <c r="C52">
-        <v>1837.342842594619</v>
+        <v>1873.822263434152</v>
       </c>
       <c r="D52">
-        <v>3440.016939239953</v>
+        <v>3476.496360079486</v>
       </c>
       <c r="E52">
         <v>48.3259033546658</v>
@@ -5554,37 +5554,37 @@
         <v>425.55</v>
       </c>
       <c r="M52">
-        <v>121.3813670041093</v>
+        <v>118.0455862204832</v>
       </c>
       <c r="N52">
-        <v>304.1686329958907</v>
+        <v>307.5044137795168</v>
       </c>
       <c r="O52">
-        <v>38.02107912448633</v>
+        <v>38.4380517224396</v>
       </c>
       <c r="P52">
-        <v>266.1475538714043</v>
+        <v>269.0663620570772</v>
       </c>
       <c r="Q52">
-        <v>292.8475538714043</v>
+        <v>295.7663620570772</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1400939134429</v>
+        <v>0.1400498772556838</v>
       </c>
       <c r="T52">
         <v>1.837105534917561</v>
       </c>
       <c r="U52">
-        <v>0.06913661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V52">
         <v>0.125</v>
       </c>
       <c r="W52">
-        <v>0.06049453957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.505892300468104</v>
+        <v>3.604963248733131</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5603,13 +5603,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.1024756842981439</v>
+        <v>0.09950844556199397</v>
       </c>
       <c r="C53">
-        <v>1710.040854166637</v>
+        <v>1835.718268137916</v>
       </c>
       <c r="D53">
-        <v>3347.828432744878</v>
+        <v>3473.505846716157</v>
       </c>
       <c r="E53">
         <v>83.43938528757258</v>
@@ -5636,45 +5636,45 @@
         <v>425.55</v>
       </c>
       <c r="M53">
-        <v>132.2256959635093</v>
+        <v>120.4064979448929</v>
       </c>
       <c r="N53">
-        <v>293.3243040364907</v>
+        <v>305.1435020551071</v>
       </c>
       <c r="O53">
-        <v>36.66553800456134</v>
+        <v>38.14293775688839</v>
       </c>
       <c r="P53">
-        <v>256.6587660319294</v>
+        <v>267.0005642982188</v>
       </c>
       <c r="Q53">
-        <v>283.3587660319294</v>
+        <v>293.7005642982188</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1418899879846696</v>
+        <v>0.141845113012935</v>
       </c>
       <c r="T53">
         <v>1.872098021296944</v>
       </c>
       <c r="U53">
-        <v>0.0738366166625341</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V53">
         <v>0.125</v>
       </c>
       <c r="W53">
-        <v>0.06460703957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.218360825398418</v>
+        <v>3.534277694836403</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5685,13 +5685,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.1026008920849792</v>
+        <v>0.1008499327062874</v>
       </c>
       <c r="C54">
-        <v>1669.785794368517</v>
+        <v>1742.209974750729</v>
       </c>
       <c r="D54">
-        <v>3342.686854879665</v>
+        <v>3415.111035261877</v>
       </c>
       <c r="E54">
         <v>118.5528672204791</v>
@@ -5718,37 +5718,37 @@
         <v>425.55</v>
       </c>
       <c r="M54">
-        <v>134.8183566686761</v>
+        <v>127.8799326387337</v>
       </c>
       <c r="N54">
-        <v>290.7316433313239</v>
+        <v>297.6700673612663</v>
       </c>
       <c r="O54">
-        <v>36.34145541641549</v>
+        <v>37.20875842015829</v>
       </c>
       <c r="P54">
-        <v>254.3901879149084</v>
+        <v>260.461308941108</v>
       </c>
       <c r="Q54">
-        <v>281.0901879149084</v>
+        <v>287.161308941108</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1437608989656795</v>
+        <v>0.1437151502600715</v>
       </c>
       <c r="T54">
         <v>1.908548527942133</v>
       </c>
       <c r="U54">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V54">
         <v>0.125</v>
       </c>
       <c r="W54">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.156469271063834</v>
+        <v>3.327730873945618</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5767,13 +5767,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.1027260998718144</v>
+        <v>0.1009419198505807</v>
       </c>
       <c r="C55">
-        <v>1629.546503171287</v>
+        <v>1703.164150490133</v>
       </c>
       <c r="D55">
-        <v>3337.561045615342</v>
+        <v>3411.178692934188</v>
       </c>
       <c r="E55">
         <v>153.6663491533859</v>
@@ -5800,37 +5800,37 @@
         <v>425.55</v>
       </c>
       <c r="M55">
-        <v>137.411017373843</v>
+        <v>130.3391621125555</v>
       </c>
       <c r="N55">
-        <v>288.138982626157</v>
+        <v>295.2108378874445</v>
       </c>
       <c r="O55">
-        <v>36.01737282826963</v>
+        <v>36.90135473593056</v>
       </c>
       <c r="P55">
-        <v>252.1216097978874</v>
+        <v>258.3094831515139</v>
       </c>
       <c r="Q55">
-        <v>278.8216097978874</v>
+        <v>285.0094831515139</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1457114231799239</v>
+        <v>0.1456647635602777</v>
       </c>
       <c r="T55">
         <v>1.94655011997648</v>
       </c>
       <c r="U55">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V55">
         <v>0.125</v>
       </c>
       <c r="W55">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.096913247081497</v>
+        <v>3.264943498965511</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5849,13 +5849,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.1028513076586496</v>
+        <v>0.1010339069948741</v>
       </c>
       <c r="C56">
-        <v>1589.322908145408</v>
+        <v>1664.127371634627</v>
       </c>
       <c r="D56">
-        <v>3332.450932522369</v>
+        <v>3407.255396011588</v>
       </c>
       <c r="E56">
         <v>188.7798310862927</v>
@@ -5882,37 +5882,37 @@
         <v>425.55</v>
       </c>
       <c r="M56">
-        <v>140.0036780790098</v>
+        <v>132.7983915863773</v>
       </c>
       <c r="N56">
-        <v>285.5463219209902</v>
+        <v>292.7516084136226</v>
       </c>
       <c r="O56">
-        <v>35.69329024012377</v>
+        <v>36.59395105170283</v>
       </c>
       <c r="P56">
-        <v>249.8530316808664</v>
+        <v>256.1576573619198</v>
       </c>
       <c r="Q56">
-        <v>276.5530316808664</v>
+        <v>282.8576573619198</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1477467527947876</v>
+        <v>0.1476991426561451</v>
       </c>
       <c r="T56">
         <v>1.986203955142755</v>
       </c>
       <c r="U56">
-        <v>0.0738366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V56">
         <v>0.125</v>
       </c>
       <c r="W56">
-        <v>0.06460703957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.039563001765173</v>
+        <v>3.204481582318001</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5931,13 +5931,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.1074521404454849</v>
+        <v>0.1011258941391675</v>
       </c>
       <c r="C57">
-        <v>1376.709172335771</v>
+        <v>1625.099607009902</v>
       </c>
       <c r="D57">
-        <v>3154.950678645639</v>
+        <v>3403.34111331977</v>
       </c>
       <c r="E57">
         <v>223.8933130191995</v>
@@ -5964,45 +5964,45 @@
         <v>425.55</v>
       </c>
       <c r="M57">
-        <v>160.5568847928584</v>
+        <v>135.2576210601991</v>
       </c>
       <c r="N57">
-        <v>264.9931152071416</v>
+        <v>290.2923789398009</v>
       </c>
       <c r="O57">
-        <v>33.1241394008927</v>
+        <v>36.28654736747511</v>
       </c>
       <c r="P57">
-        <v>231.8689758062489</v>
+        <v>254.0058315723257</v>
       </c>
       <c r="Q57">
-        <v>258.5689758062489</v>
+        <v>280.7058315723257</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1498725415036452</v>
+        <v>0.1498239386007177</v>
       </c>
       <c r="T57">
         <v>2.027620182983087</v>
       </c>
       <c r="U57">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V57">
         <v>0.125</v>
       </c>
       <c r="W57">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.650462485922176</v>
+        <v>3.14621828082131</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6013,13 +6013,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1076587232323201</v>
+        <v>0.1012178812834609</v>
       </c>
       <c r="C58">
-        <v>1334.068237574237</v>
+        <v>1586.080825584746</v>
       </c>
       <c r="D58">
-        <v>3147.423225817012</v>
+        <v>3399.435813827521</v>
       </c>
       <c r="E58">
         <v>259.006794952106</v>
@@ -6046,45 +6046,45 @@
         <v>425.55</v>
       </c>
       <c r="M58">
-        <v>163.4761008800013</v>
+        <v>137.7168505340209</v>
       </c>
       <c r="N58">
-        <v>262.0738991199987</v>
+        <v>287.8331494659791</v>
       </c>
       <c r="O58">
-        <v>32.75923738999984</v>
+        <v>35.97914368324739</v>
       </c>
       <c r="P58">
-        <v>229.3146617299989</v>
+        <v>251.8540057827317</v>
       </c>
       <c r="Q58">
-        <v>256.0146617299989</v>
+        <v>278.5540057827317</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1520949569719964</v>
+        <v>0.1520453161791345</v>
       </c>
       <c r="T58">
         <v>2.070918966634342</v>
       </c>
       <c r="U58">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V58">
         <v>0.125</v>
       </c>
       <c r="W58">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.603132798673566</v>
+        <v>3.09003581152093</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6095,13 +6095,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1078653060191554</v>
+        <v>0.1013098684277543</v>
       </c>
       <c r="C59">
-        <v>1291.463137081736</v>
+        <v>1547.070996470211</v>
       </c>
       <c r="D59">
-        <v>3139.931607257418</v>
+        <v>3395.539466645892</v>
       </c>
       <c r="E59">
         <v>294.1202768850128</v>
@@ -6128,45 +6128,45 @@
         <v>425.55</v>
       </c>
       <c r="M59">
-        <v>166.3953169671442</v>
+        <v>140.1760800078428</v>
       </c>
       <c r="N59">
-        <v>259.1546830328558</v>
+        <v>285.3739199921573</v>
       </c>
       <c r="O59">
-        <v>32.39433537910698</v>
+        <v>35.67173999901966</v>
       </c>
       <c r="P59">
-        <v>226.7603476537489</v>
+        <v>249.7021799931376</v>
       </c>
       <c r="Q59">
-        <v>253.4603476537488</v>
+        <v>276.4021799931376</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.1544207406016662</v>
+        <v>0.1543700136449195</v>
       </c>
       <c r="T59">
         <v>2.116231647199609</v>
       </c>
       <c r="U59">
-        <v>0.08313661666253409</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V59">
         <v>0.125</v>
       </c>
       <c r="W59">
-        <v>0.07274453957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.557463802205609</v>
+        <v>3.035824656932843</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6177,13 +6177,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.1080718888059906</v>
+        <v>0.1053603555720476</v>
       </c>
       <c r="C60">
-        <v>1248.893615583542</v>
+        <v>1348.819126569168</v>
       </c>
       <c r="D60">
-        <v>3132.47556769213</v>
+        <v>3232.401078677755</v>
       </c>
       <c r="E60">
         <v>329.2337588179191</v>
@@ -6210,37 +6210,37 @@
         <v>425.55</v>
       </c>
       <c r="M60">
-        <v>169.314533054287</v>
+        <v>158.5206487081115</v>
       </c>
       <c r="N60">
-        <v>256.235466945713</v>
+        <v>267.0293512918885</v>
       </c>
       <c r="O60">
-        <v>32.02943336821412</v>
+        <v>33.37866891148606</v>
       </c>
       <c r="P60">
-        <v>224.2060335774989</v>
+        <v>233.6506823804024</v>
       </c>
       <c r="Q60">
-        <v>250.9060335774988</v>
+        <v>260.3506823804024</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.1568572758327489</v>
+        <v>0.1568054109900276</v>
       </c>
       <c r="T60">
         <v>2.163702074458461</v>
       </c>
       <c r="U60">
-        <v>0.08313661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V60">
         <v>0.125</v>
       </c>
       <c r="W60">
-        <v>0.07274453957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.513369598719306</v>
+        <v>2.684508317800144</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6259,13 +6259,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.1107048465928258</v>
+        <v>0.105520592716341</v>
       </c>
       <c r="C61">
-        <v>1121.761323989208</v>
+        <v>1307.57361980725</v>
       </c>
       <c r="D61">
-        <v>3040.456758030703</v>
+        <v>3226.269053848745</v>
       </c>
       <c r="E61">
         <v>364.3472407508259</v>
@@ -6292,45 +6292,45 @@
         <v>425.55</v>
       </c>
       <c r="M61">
-        <v>181.9707176814249</v>
+        <v>161.25376334101</v>
       </c>
       <c r="N61">
-        <v>243.5792823185751</v>
+        <v>264.29623665899</v>
       </c>
       <c r="O61">
-        <v>30.44741028982189</v>
+        <v>33.03702958237375</v>
       </c>
       <c r="P61">
-        <v>213.1318720287532</v>
+        <v>231.2592070766162</v>
       </c>
       <c r="Q61">
-        <v>239.8318720287532</v>
+        <v>257.9592070766162</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1594126664409576</v>
+        <v>0.1593596082056288</v>
       </c>
       <c r="T61">
         <v>2.213488132315305</v>
       </c>
       <c r="U61">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V61">
         <v>0.125</v>
       </c>
       <c r="W61">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y61">
-        <v>2.338563068949411</v>
+        <v>2.63900817682048</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6341,13 +6341,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.1109525543796611</v>
+        <v>0.1056808298606344</v>
       </c>
       <c r="C62">
-        <v>1078.268210459556</v>
+        <v>1266.351334502272</v>
       </c>
       <c r="D62">
-        <v>3032.077126433957</v>
+        <v>3220.160250476673</v>
       </c>
       <c r="E62">
         <v>399.4607226837327</v>
@@ -6374,45 +6374,45 @@
         <v>425.55</v>
       </c>
       <c r="M62">
-        <v>185.0549671336525</v>
+        <v>163.9868779739085</v>
       </c>
       <c r="N62">
-        <v>240.4950328663475</v>
+        <v>261.5631220260915</v>
       </c>
       <c r="O62">
-        <v>30.06187910829344</v>
+        <v>32.69539025326144</v>
       </c>
       <c r="P62">
-        <v>210.4331537580541</v>
+        <v>228.86773177283</v>
       </c>
       <c r="Q62">
-        <v>237.1331537580541</v>
+        <v>255.56773177283</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1620958265795767</v>
+        <v>0.1620415152820101</v>
       </c>
       <c r="T62">
         <v>2.265763493064993</v>
       </c>
       <c r="U62">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V62">
         <v>0.125</v>
       </c>
       <c r="W62">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>2.299587017800254</v>
+        <v>2.595024707206805</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6423,13 +6423,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.1112002621664963</v>
+        <v>0.1058410670049278</v>
       </c>
       <c r="C63">
-        <v>1034.821159241372</v>
+        <v>1225.152138996993</v>
       </c>
       <c r="D63">
-        <v>3023.74355714868</v>
+        <v>3214.074536904302</v>
       </c>
       <c r="E63">
         <v>434.5742046166395</v>
@@ -6456,45 +6456,45 @@
         <v>425.55</v>
       </c>
       <c r="M63">
-        <v>188.13921658588</v>
+        <v>166.719992606807</v>
       </c>
       <c r="N63">
-        <v>237.41078341412</v>
+        <v>258.830007393193</v>
       </c>
       <c r="O63">
-        <v>29.676347926765</v>
+        <v>32.35375092414913</v>
       </c>
       <c r="P63">
-        <v>207.734435487355</v>
+        <v>226.4762564690439</v>
       </c>
       <c r="Q63">
-        <v>234.434435487355</v>
+        <v>253.1762564690439</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1649165846740224</v>
+        <v>0.164860956054616</v>
       </c>
       <c r="T63">
         <v>2.320719641545432</v>
       </c>
       <c r="U63">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V63">
         <v>0.125</v>
       </c>
       <c r="W63">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.261888869967463</v>
+        <v>2.552483318564071</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6505,13 +6505,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.1114479699533315</v>
+        <v>0.1060013041492212</v>
       </c>
       <c r="C64">
-        <v>991.4197915731975</v>
+        <v>1183.975902627564</v>
       </c>
       <c r="D64">
-        <v>3015.455671413412</v>
+        <v>3208.011782467779</v>
       </c>
       <c r="E64">
         <v>469.6876865495462</v>
@@ -6538,45 +6538,45 @@
         <v>425.55</v>
       </c>
       <c r="M64">
-        <v>191.2234660381076</v>
+        <v>169.4531072397055</v>
       </c>
       <c r="N64">
-        <v>234.3265339618924</v>
+        <v>256.0968927602945</v>
       </c>
       <c r="O64">
-        <v>29.29081674523655</v>
+        <v>32.01211159503681</v>
       </c>
       <c r="P64">
-        <v>205.0357172166559</v>
+        <v>224.0847811652577</v>
       </c>
       <c r="Q64">
-        <v>231.7357172166559</v>
+        <v>250.7847811652577</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1678858037208074</v>
+        <v>0.1678287884468327</v>
       </c>
       <c r="T64">
         <v>2.378568218893264</v>
       </c>
       <c r="U64">
-        <v>0.08783661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V64">
         <v>0.125</v>
       </c>
       <c r="W64">
-        <v>0.07685703957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.225406791419601</v>
+        <v>2.511314232780779</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6587,13 +6587,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.1116956777401668</v>
+        <v>0.1083114162935146</v>
       </c>
       <c r="C65">
-        <v>948.0637328348625</v>
+        <v>1063.931252964906</v>
       </c>
       <c r="D65">
-        <v>3007.213094607984</v>
+        <v>3123.080614738027</v>
       </c>
       <c r="E65">
         <v>504.8011684824526</v>
@@ -6620,37 +6620,37 @@
         <v>425.55</v>
       </c>
       <c r="M65">
-        <v>194.3077154903351</v>
+        <v>180.813604383519</v>
       </c>
       <c r="N65">
-        <v>231.2422845096649</v>
+        <v>244.736395616481</v>
       </c>
       <c r="O65">
-        <v>28.90528556370812</v>
+        <v>30.59204945206012</v>
       </c>
       <c r="P65">
-        <v>202.3369989459568</v>
+        <v>214.1443461644209</v>
       </c>
       <c r="Q65">
-        <v>229.0369989459568</v>
+        <v>240.8443461644208</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1710155210944456</v>
+        <v>0.1709570442116018</v>
       </c>
       <c r="T65">
         <v>2.439543746368005</v>
       </c>
       <c r="U65">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V65">
         <v>0.125</v>
       </c>
       <c r="W65">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.190082874095481</v>
+        <v>2.35352865980912</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6669,13 +6669,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.111943385527002</v>
+        <v>0.108505778437808</v>
       </c>
       <c r="C66">
-        <v>904.7526124910487</v>
+        <v>1021.876697322748</v>
       </c>
       <c r="D66">
-        <v>2999.015456197077</v>
+        <v>3116.139541028776</v>
       </c>
       <c r="E66">
         <v>539.9146504153593</v>
@@ -6702,37 +6702,37 @@
         <v>425.55</v>
       </c>
       <c r="M66">
-        <v>197.3919649425627</v>
+        <v>183.6836615959559</v>
       </c>
       <c r="N66">
-        <v>228.1580350574374</v>
+        <v>241.8663384040441</v>
       </c>
       <c r="O66">
-        <v>28.51975438217967</v>
+        <v>30.23329230050552</v>
       </c>
       <c r="P66">
-        <v>199.6382806752577</v>
+        <v>211.6330461035386</v>
       </c>
       <c r="Q66">
-        <v>226.3382806752577</v>
+        <v>238.3330461035386</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1743191116555082</v>
+        <v>0.1742590919633024</v>
       </c>
       <c r="T66">
         <v>2.503906803146899</v>
       </c>
       <c r="U66">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V66">
         <v>0.125</v>
       </c>
       <c r="W66">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.155862829187738</v>
+        <v>2.316754774499603</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6751,13 +6751,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.1121910933138373</v>
+        <v>0.1087001405821013</v>
       </c>
       <c r="C67">
-        <v>861.4860640357533</v>
+        <v>979.8529264540089</v>
       </c>
       <c r="D67">
-        <v>2990.862389674688</v>
+        <v>3109.229252092944</v>
       </c>
       <c r="E67">
         <v>575.0281323482661</v>
@@ -6784,37 +6784,37 @@
         <v>425.55</v>
       </c>
       <c r="M67">
-        <v>200.4762143947902</v>
+        <v>186.5537188083927</v>
       </c>
       <c r="N67">
-        <v>225.0737856052098</v>
+        <v>238.9962811916073</v>
       </c>
       <c r="O67">
-        <v>28.13422320065123</v>
+        <v>29.87453514895092</v>
       </c>
       <c r="P67">
-        <v>196.9395624045586</v>
+        <v>209.1217460426564</v>
       </c>
       <c r="Q67">
-        <v>223.6395624045586</v>
+        <v>235.8217460426564</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.17781147882006</v>
+        <v>0.1777498281579574</v>
       </c>
       <c r="T67">
         <v>2.571947748884586</v>
       </c>
       <c r="U67">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V67">
         <v>0.125</v>
       </c>
       <c r="W67">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.122695708738696</v>
+        <v>2.281112393353455</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6833,13 +6833,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.1124388011006725</v>
+        <v>0.1088945027263947</v>
       </c>
       <c r="C68">
-        <v>818.2637249376762</v>
+        <v>937.859736008751</v>
       </c>
       <c r="D68">
-        <v>2982.753532509518</v>
+        <v>3102.349543580593</v>
       </c>
       <c r="E68">
         <v>610.1416142811729</v>
@@ -6866,37 +6866,37 @@
         <v>425.55</v>
       </c>
       <c r="M68">
-        <v>203.5604638470177</v>
+        <v>189.4237760208295</v>
       </c>
       <c r="N68">
-        <v>221.9895361529823</v>
+        <v>236.1262239791705</v>
       </c>
       <c r="O68">
-        <v>27.74869201912279</v>
+        <v>29.51577799739631</v>
       </c>
       <c r="P68">
-        <v>194.2408441338595</v>
+        <v>206.6104459817742</v>
       </c>
       <c r="Q68">
-        <v>220.9408441338595</v>
+        <v>233.3104459817742</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1815092793472326</v>
+        <v>0.1814459017758273</v>
       </c>
       <c r="T68">
         <v>2.643991103195079</v>
       </c>
       <c r="U68">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V68">
         <v>0.125</v>
       </c>
       <c r="W68">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.090533652545686</v>
+        <v>2.246550084363251</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6915,13 +6915,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.1126865088875078</v>
+        <v>0.1090888648706881</v>
       </c>
       <c r="C69">
-        <v>775.0852365864812</v>
+        <v>895.8969234416827</v>
       </c>
       <c r="D69">
-        <v>2974.68852609123</v>
+        <v>3095.500212946431</v>
       </c>
       <c r="E69">
         <v>645.2550962140797</v>
@@ -6948,37 +6948,37 @@
         <v>425.55</v>
       </c>
       <c r="M69">
-        <v>206.6447132992453</v>
+        <v>192.2938332332663</v>
       </c>
       <c r="N69">
-        <v>218.9052867007547</v>
+        <v>233.2561667667337</v>
       </c>
       <c r="O69">
-        <v>27.36316083759434</v>
+        <v>29.15702084584171</v>
       </c>
       <c r="P69">
-        <v>191.5421258631604</v>
+        <v>204.099145920892</v>
       </c>
       <c r="Q69">
-        <v>218.2421258631604</v>
+        <v>230.799145920892</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1854311889972641</v>
+        <v>0.1853659798553864</v>
       </c>
       <c r="T69">
         <v>2.720400721403177</v>
       </c>
       <c r="U69">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V69">
         <v>0.125</v>
       </c>
       <c r="W69">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.059331657731571</v>
+        <v>2.213019486089172</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6997,13 +6997,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.112934216674343</v>
+        <v>0.1092832270149815</v>
       </c>
       <c r="C70">
-        <v>731.950244239928</v>
+        <v>853.9642879922799</v>
       </c>
       <c r="D70">
-        <v>2966.667015677583</v>
+        <v>3088.681059429935</v>
       </c>
       <c r="E70">
         <v>680.3685781469865</v>
@@ -7030,37 +7030,37 @@
         <v>425.55</v>
       </c>
       <c r="M70">
-        <v>209.7289627514728</v>
+        <v>195.1638904457031</v>
       </c>
       <c r="N70">
-        <v>215.8210372485272</v>
+        <v>230.3861095542969</v>
       </c>
       <c r="O70">
-        <v>26.9776296560659</v>
+        <v>28.79826369428711</v>
       </c>
       <c r="P70">
-        <v>188.8434075924613</v>
+        <v>201.5878458600098</v>
       </c>
       <c r="Q70">
-        <v>215.5434075924613</v>
+        <v>228.2878458600098</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1895982180004226</v>
+        <v>0.1895310628149179</v>
       </c>
       <c r="T70">
         <v>2.801585940749282</v>
       </c>
       <c r="U70">
-        <v>0.08783661666253409</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V70">
         <v>0.125</v>
       </c>
       <c r="W70">
-        <v>0.07685703957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.029047368647283</v>
+        <v>2.180475081881978</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7079,13 +7079,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1230230494611782</v>
+        <v>0.1094775891592749</v>
       </c>
       <c r="C71">
-        <v>403.2552100070752</v>
+        <v>812.0616306651709</v>
       </c>
       <c r="D71">
-        <v>2673.085463377637</v>
+        <v>3081.891884035733</v>
       </c>
       <c r="E71">
         <v>715.4820600798932</v>
@@ -7112,45 +7112,45 @@
         <v>425.55</v>
       </c>
       <c r="M71">
-        <v>252.3053453336406</v>
+        <v>198.03394765814</v>
       </c>
       <c r="N71">
-        <v>173.2446546663595</v>
+        <v>227.51605234186</v>
       </c>
       <c r="O71">
-        <v>21.65558183329493</v>
+        <v>28.43950654273251</v>
       </c>
       <c r="P71">
-        <v>151.5890728330645</v>
+        <v>199.0765457991275</v>
       </c>
       <c r="Q71">
-        <v>178.2890728330645</v>
+        <v>225.7765457991275</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.19403408758443</v>
+        <v>0.1939648608040965</v>
       </c>
       <c r="T71">
         <v>2.888008916182232</v>
       </c>
       <c r="U71">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V71">
         <v>0.125</v>
       </c>
       <c r="W71">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y71">
-        <v>1.686646786802183</v>
+        <v>2.148873993738761</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7161,13 +7161,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1234133822480135</v>
+        <v>0.1096719513035683</v>
       </c>
       <c r="C72">
-        <v>357.9462570851788</v>
+        <v>770.1887542107806</v>
       </c>
       <c r="D72">
-        <v>2662.889992388647</v>
+        <v>3075.132489514249</v>
       </c>
       <c r="E72">
         <v>750.5955420128</v>
@@ -7194,45 +7194,45 @@
         <v>425.55</v>
       </c>
       <c r="M72">
-        <v>255.9619445413745</v>
+        <v>200.9040048705768</v>
       </c>
       <c r="N72">
-        <v>169.5880554586255</v>
+        <v>224.6459951294232</v>
       </c>
       <c r="O72">
-        <v>21.19850693232819</v>
+        <v>28.0807493911779</v>
       </c>
       <c r="P72">
-        <v>148.3895485262973</v>
+        <v>196.5652457382453</v>
       </c>
       <c r="Q72">
-        <v>175.0895485262973</v>
+        <v>223.2652457382453</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.1987656818073712</v>
+        <v>0.1986942453258871</v>
       </c>
       <c r="T72">
         <v>2.980193423310711</v>
       </c>
       <c r="U72">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V72">
         <v>0.125</v>
       </c>
       <c r="W72">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.662551832705009</v>
+        <v>2.118175793828208</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7243,13 +7243,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.1238037150348487</v>
+        <v>0.1098663134478617</v>
       </c>
       <c r="C73">
-        <v>312.7147821696722</v>
+        <v>728.345463106225</v>
       </c>
       <c r="D73">
-        <v>2652.771999406047</v>
+        <v>3068.4026803426</v>
       </c>
       <c r="E73">
         <v>785.7090239457063</v>
@@ -7276,45 +7276,45 @@
         <v>425.55</v>
       </c>
       <c r="M73">
-        <v>259.6185437491084</v>
+        <v>203.7740620830136</v>
       </c>
       <c r="N73">
-        <v>165.9314562508916</v>
+        <v>221.7759379169864</v>
       </c>
       <c r="O73">
-        <v>20.74143203136146</v>
+        <v>27.7219922396233</v>
       </c>
       <c r="P73">
-        <v>145.1900242195302</v>
+        <v>194.0539456773631</v>
       </c>
       <c r="Q73">
-        <v>171.8900242195302</v>
+        <v>220.7539456773631</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.2038235928732738</v>
+        <v>0.2037497942974563</v>
       </c>
       <c r="T73">
         <v>3.078735482654948</v>
       </c>
       <c r="U73">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V73">
         <v>0.125</v>
       </c>
       <c r="W73">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>1.639135609709164</v>
+        <v>2.088342331943303</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7325,13 +7325,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.124194047821684</v>
+        <v>0.110060675592155</v>
       </c>
       <c r="C74">
-        <v>267.5599054405952</v>
+        <v>686.5315635364614</v>
       </c>
       <c r="D74">
-        <v>2642.730604609877</v>
+        <v>3061.702262705743</v>
       </c>
       <c r="E74">
         <v>820.8225058786127</v>
@@ -7358,45 +7358,45 @@
         <v>425.55</v>
       </c>
       <c r="M74">
-        <v>263.2751429568423</v>
+        <v>206.6441192954503</v>
       </c>
       <c r="N74">
-        <v>162.2748570431577</v>
+        <v>218.9058807045497</v>
       </c>
       <c r="O74">
-        <v>20.28435713039472</v>
+        <v>27.36323508806871</v>
       </c>
       <c r="P74">
-        <v>141.990499912763</v>
+        <v>191.542645616481</v>
       </c>
       <c r="Q74">
-        <v>168.690499912763</v>
+        <v>218.242645616481</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.2092427833010267</v>
+        <v>0.2091664539098519</v>
       </c>
       <c r="T74">
         <v>3.184316260523773</v>
       </c>
       <c r="U74">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V74">
         <v>0.125</v>
       </c>
       <c r="W74">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y74">
-        <v>1.616369837352092</v>
+        <v>2.05933757733298</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7407,13 +7407,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.1245843806085192</v>
+        <v>0.1102550377364484</v>
       </c>
       <c r="C75">
-        <v>222.4807603490945</v>
+        <v>644.7468633756775</v>
       </c>
       <c r="D75">
-        <v>2632.764941451283</v>
+        <v>3055.031044477866</v>
       </c>
       <c r="E75">
         <v>855.9359878115195</v>
@@ -7440,45 +7440,45 @@
         <v>425.55</v>
       </c>
       <c r="M75">
-        <v>266.9317421645762</v>
+        <v>209.5141765078872</v>
       </c>
       <c r="N75">
-        <v>158.6182578354238</v>
+        <v>216.0358234921129</v>
       </c>
       <c r="O75">
-        <v>19.82728222942798</v>
+        <v>27.00447793651411</v>
       </c>
       <c r="P75">
-        <v>138.7909756059959</v>
+        <v>189.0313455555988</v>
       </c>
       <c r="Q75">
-        <v>165.4909756059959</v>
+        <v>215.7313455555988</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.2150633952419465</v>
+        <v>0.2149843475676102</v>
       </c>
       <c r="T75">
         <v>3.297717836753252</v>
       </c>
       <c r="U75">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V75">
         <v>0.125</v>
       </c>
       <c r="W75">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y75">
-        <v>1.594227784785625</v>
+        <v>2.031127473533898</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7489,13 +7489,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.1249747133953544</v>
+        <v>0.1104493998807418</v>
       </c>
       <c r="C76">
-        <v>177.4764933681395</v>
+        <v>602.9911721689346</v>
       </c>
       <c r="D76">
-        <v>2622.874156403234</v>
+        <v>3048.388835204029</v>
       </c>
       <c r="E76">
         <v>891.0494697444262</v>
@@ -7522,45 +7522,45 @@
         <v>425.55</v>
       </c>
       <c r="M76">
-        <v>270.5883413723101</v>
+        <v>212.384233720324</v>
       </c>
       <c r="N76">
-        <v>154.9616586276899</v>
+        <v>213.165766279676</v>
       </c>
       <c r="O76">
-        <v>19.37020732846123</v>
+        <v>26.6457207849595</v>
       </c>
       <c r="P76">
-        <v>135.5914512992287</v>
+        <v>186.5200454947165</v>
       </c>
       <c r="Q76">
-        <v>162.2914512992286</v>
+        <v>213.2200454947165</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.221331746562937</v>
+        <v>0.2212497715067345</v>
       </c>
       <c r="T76">
         <v>3.419842611154229</v>
       </c>
       <c r="U76">
-        <v>0.1041366166625341</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V76">
         <v>0.125</v>
       </c>
       <c r="W76">
-        <v>0.09111953957971733</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y76">
-        <v>1.572684166072306</v>
+        <v>2.003679804972629</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7571,13 +7571,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.1253650461821897</v>
+        <v>0.1199625120250352</v>
       </c>
       <c r="C77">
-        <v>132.5462637488317</v>
+        <v>274.6805791800762</v>
       </c>
       <c r="D77">
-        <v>2613.057408716833</v>
+        <v>2755.191724148078</v>
       </c>
       <c r="E77">
         <v>926.162951677333</v>
@@ -7604,37 +7604,37 @@
         <v>425.55</v>
       </c>
       <c r="M77">
-        <v>274.244940580044</v>
+        <v>252.6501491913064</v>
       </c>
       <c r="N77">
-        <v>151.305059419956</v>
+        <v>172.8998508086936</v>
       </c>
       <c r="O77">
-        <v>18.9131324274945</v>
+        <v>21.6124813510867</v>
       </c>
       <c r="P77">
-        <v>132.3919269924615</v>
+        <v>151.2873694576069</v>
       </c>
       <c r="Q77">
-        <v>159.0919269924615</v>
+        <v>177.9873694576069</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.2281015659896067</v>
+        <v>0.2280164293609887</v>
       </c>
       <c r="T77">
         <v>3.551737367507285</v>
       </c>
       <c r="U77">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V77">
         <v>0.125</v>
       </c>
       <c r="W77">
-        <v>0.09111953957971733</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.551715043858009</v>
+        <v>1.684344938493482</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7653,13 +7653,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1257553789690249</v>
+        <v>0.1202811241693286</v>
       </c>
       <c r="C78">
-        <v>87.68924328217417</v>
+        <v>230.7203397808607</v>
       </c>
       <c r="D78">
-        <v>2603.313870183083</v>
+        <v>2746.344966681769</v>
       </c>
       <c r="E78">
         <v>961.2764336102398</v>
@@ -7686,37 +7686,37 @@
         <v>425.55</v>
       </c>
       <c r="M78">
-        <v>277.901539787778</v>
+        <v>256.0188178471905</v>
       </c>
       <c r="N78">
-        <v>147.648460212222</v>
+        <v>169.5311821528095</v>
       </c>
       <c r="O78">
-        <v>18.45605752652775</v>
+        <v>21.19139776910119</v>
       </c>
       <c r="P78">
-        <v>129.1924026856942</v>
+        <v>148.3397843837083</v>
       </c>
       <c r="Q78">
-        <v>155.8924026856942</v>
+        <v>175.0397843837083</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.2354355370351656</v>
+        <v>0.2353469753697641</v>
       </c>
       <c r="T78">
         <v>3.694623353556429</v>
       </c>
       <c r="U78">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V78">
         <v>0.125</v>
       </c>
       <c r="W78">
-        <v>0.09111953957971733</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.53129774064935</v>
+        <v>1.662182505092252</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7735,13 +7735,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1261457117558601</v>
+        <v>0.120599736313622</v>
       </c>
       <c r="C79">
-        <v>42.90461606614326</v>
+        <v>186.8167313715448</v>
       </c>
       <c r="D79">
-        <v>2593.642724899958</v>
+        <v>2737.55484020536</v>
       </c>
       <c r="E79">
         <v>996.3899155431466</v>
@@ -7768,37 +7768,37 @@
         <v>425.55</v>
       </c>
       <c r="M79">
-        <v>281.5581389955119</v>
+        <v>259.3874865030746</v>
       </c>
       <c r="N79">
-        <v>143.9918610044881</v>
+        <v>166.1625134969254</v>
       </c>
       <c r="O79">
-        <v>17.99898262556101</v>
+        <v>20.77031418711567</v>
       </c>
       <c r="P79">
-        <v>125.9928783789271</v>
+        <v>145.3921993098097</v>
       </c>
       <c r="Q79">
-        <v>152.6928783789271</v>
+        <v>172.0921993098097</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.2434072446933818</v>
+        <v>0.2433149601619113</v>
       </c>
       <c r="T79">
         <v>3.849934207957672</v>
       </c>
       <c r="U79">
-        <v>0.1041366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V79">
         <v>0.125</v>
       </c>
       <c r="W79">
-        <v>0.09111953957971733</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.511410757004554</v>
+        <v>1.640595719311833</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7817,13 +7817,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1729618367735233</v>
+        <v>0.1209183484579153</v>
       </c>
       <c r="C80">
-        <v>-791.6456118258327</v>
+        <v>142.9692119167521</v>
       </c>
       <c r="D80">
-        <v>1794.205978940889</v>
+        <v>2728.820802683474</v>
       </c>
       <c r="E80">
         <v>1031.503397476053</v>
@@ -7850,45 +7850,45 @@
         <v>425.55</v>
       </c>
       <c r="M80">
-        <v>464.3356322393895</v>
+        <v>262.7561551589587</v>
       </c>
       <c r="N80">
-        <v>-38.78563223938949</v>
+        <v>162.7938448410413</v>
       </c>
       <c r="O80">
-        <v>-4.848204029923686</v>
+        <v>20.34923060513016</v>
       </c>
       <c r="P80">
-        <v>-33.9374282094658</v>
+        <v>142.4446142359111</v>
       </c>
       <c r="Q80">
-        <v>-7.237428209465801</v>
+        <v>169.1446142359111</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.2539653251322559</v>
+        <v>0.2520073072078901</v>
       </c>
       <c r="T80">
-        <v>4.055634738396533</v>
+        <v>4.019364230940846</v>
       </c>
       <c r="U80">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V80">
-        <v>0.1145588369849157</v>
+        <v>0.125</v>
       </c>
       <c r="W80">
-        <v>0.1501146990313167</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y80">
-        <v>0.9164706958793258</v>
+        <v>1.619562440859117</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7899,13 +7899,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1741992029401487</v>
+        <v>0.1212369606022087</v>
       </c>
       <c r="C81">
-        <v>-841.2576692695454</v>
+        <v>99.17724627645521</v>
       </c>
       <c r="D81">
-        <v>1779.707403430083</v>
+        <v>2720.142318976084</v>
       </c>
       <c r="E81">
         <v>1066.61687940896</v>
@@ -7932,45 +7932,45 @@
         <v>425.55</v>
       </c>
       <c r="M81">
-        <v>470.2886531655354</v>
+        <v>266.1248238148428</v>
       </c>
       <c r="N81">
-        <v>-44.73865316553542</v>
+        <v>159.4251761851572</v>
       </c>
       <c r="O81">
-        <v>-5.592331645691928</v>
+        <v>19.92814702314465</v>
       </c>
       <c r="P81">
-        <v>-39.1463215198435</v>
+        <v>139.4970291620126</v>
       </c>
       <c r="Q81">
-        <v>-12.4463215198435</v>
+        <v>166.1970291620126</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2638779596623634</v>
+        <v>0.2615274968296764</v>
       </c>
       <c r="T81">
-        <v>4.248760202129701</v>
+        <v>4.204930446589086</v>
       </c>
       <c r="U81">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V81">
-        <v>0.1131087251243472</v>
+        <v>0.125</v>
       </c>
       <c r="W81">
-        <v>0.1503605460899397</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y81">
-        <v>0.9048698009947775</v>
+        <v>1.599061650468495</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7981,13 +7981,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.175436569106774</v>
+        <v>0.1215555727465021</v>
       </c>
       <c r="C82">
-        <v>-890.6372855538384</v>
+        <v>55.44030609668334</v>
       </c>
       <c r="D82">
-        <v>1765.441269078697</v>
+        <v>2711.518860729218</v>
       </c>
       <c r="E82">
         <v>1101.730361341866</v>
@@ -8014,45 +8014,45 @@
         <v>425.55</v>
       </c>
       <c r="M82">
-        <v>476.2416740916815</v>
+        <v>269.4934924707269</v>
       </c>
       <c r="N82">
-        <v>-50.69167409168148</v>
+        <v>156.0565075292731</v>
       </c>
       <c r="O82">
-        <v>-6.336459261460185</v>
+        <v>19.50706344115914</v>
       </c>
       <c r="P82">
-        <v>-44.35521483022129</v>
+        <v>136.549444088114</v>
       </c>
       <c r="Q82">
-        <v>-17.65521483022129</v>
+        <v>163.249444088114</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2747818576454816</v>
+        <v>0.2719997054136412</v>
       </c>
       <c r="T82">
-        <v>4.461198212236186</v>
+        <v>4.409053283802148</v>
       </c>
       <c r="U82">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V82">
-        <v>0.1116948660602928</v>
+        <v>0.125</v>
       </c>
       <c r="W82">
-        <v>0.1506002469720971</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.8935589284823428</v>
+        <v>1.579073379837639</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8063,13 +8063,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1766739352733994</v>
+        <v>0.1218741848907955</v>
       </c>
       <c r="C83">
-        <v>-939.7900059725621</v>
+        <v>11.75786970228955</v>
       </c>
       <c r="D83">
-        <v>1751.40203059288</v>
+        <v>2702.949906267731</v>
       </c>
       <c r="E83">
         <v>1136.843843274773</v>
@@ -8096,45 +8096,45 @@
         <v>425.55</v>
       </c>
       <c r="M83">
-        <v>482.1946950178275</v>
+        <v>272.8621611266109</v>
       </c>
       <c r="N83">
-        <v>-56.64469501782753</v>
+        <v>152.6878388733891</v>
       </c>
       <c r="O83">
-        <v>-7.080586877228441</v>
+        <v>19.08597985917363</v>
       </c>
       <c r="P83">
-        <v>-49.56410814059909</v>
+        <v>133.6018590142154</v>
       </c>
       <c r="Q83">
-        <v>-22.86410814059909</v>
+        <v>160.3018590142154</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2868335343636648</v>
+        <v>0.2835742517432866</v>
       </c>
       <c r="T83">
-        <v>4.695998118143355</v>
+        <v>4.634662735458691</v>
       </c>
       <c r="U83">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V83">
-        <v>0.1103159170965855</v>
+        <v>0.125</v>
       </c>
       <c r="W83">
-        <v>0.1508340293139544</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y83">
-        <v>0.8825273367726841</v>
+        <v>1.559578646753224</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8145,13 +8145,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1779113014400247</v>
+        <v>0.1221927970350889</v>
       </c>
       <c r="C84">
-        <v>-988.7212008208467</v>
+        <v>-31.87057800824368</v>
       </c>
       <c r="D84">
-        <v>1737.584317677502</v>
+        <v>2694.434940490105</v>
       </c>
       <c r="E84">
         <v>1171.95732520768</v>
@@ -8178,45 +8178,45 @@
         <v>425.55</v>
       </c>
       <c r="M84">
-        <v>488.1477159439735</v>
+        <v>276.2308297824951</v>
       </c>
       <c r="N84">
-        <v>-62.59771594397353</v>
+        <v>149.319170217505</v>
       </c>
       <c r="O84">
-        <v>-7.824714492996691</v>
+        <v>18.66489627718812</v>
       </c>
       <c r="P84">
-        <v>-54.77300145097684</v>
+        <v>130.6542739403168</v>
       </c>
       <c r="Q84">
-        <v>-28.07300145097684</v>
+        <v>157.3542739403168</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.3002242862727573</v>
+        <v>0.2964348587762259</v>
       </c>
       <c r="T84">
-        <v>4.956886902484652</v>
+        <v>4.885339903965961</v>
       </c>
       <c r="U84">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V84">
-        <v>0.108970601034432</v>
+        <v>0.125</v>
       </c>
       <c r="W84">
-        <v>0.1510621096474737</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y84">
-        <v>0.8717648082754563</v>
+        <v>1.54055939496355</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8227,13 +8227,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.17914866760665</v>
+        <v>0.1225114091793823</v>
       </c>
       <c r="C85">
-        <v>-1037.436072244341</v>
+        <v>-75.4455456660271</v>
       </c>
       <c r="D85">
-        <v>1723.982928186915</v>
+        <v>2685.973454765228</v>
       </c>
       <c r="E85">
         <v>1207.070807140587</v>
@@ -8260,45 +8260,45 @@
         <v>425.55</v>
       </c>
       <c r="M85">
-        <v>494.1007368701196</v>
+        <v>279.5994984383792</v>
       </c>
       <c r="N85">
-        <v>-68.55073687011958</v>
+        <v>145.9505015616209</v>
       </c>
       <c r="O85">
-        <v>-8.568842108764947</v>
+        <v>18.24381269520261</v>
       </c>
       <c r="P85">
-        <v>-59.98189476135463</v>
+        <v>127.7066888664182</v>
       </c>
       <c r="Q85">
-        <v>-33.28189476135464</v>
+        <v>154.4066888664182</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.3151904207593901</v>
+        <v>0.3108084784012758</v>
       </c>
       <c r="T85">
-        <v>5.24846848498375</v>
+        <v>5.165508504062322</v>
       </c>
       <c r="U85">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V85">
-        <v>0.1076577022267883</v>
+        <v>0.125</v>
       </c>
       <c r="W85">
-        <v>0.1512846940693419</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.8612616178143062</v>
+        <v>1.521998438397724</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8309,13 +8309,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1803860337732754</v>
+        <v>0.1228300213236756</v>
       </c>
       <c r="C86">
-        <v>-1085.939660769262</v>
+        <v>-118.9675355330373</v>
       </c>
       <c r="D86">
-        <v>1710.5928215949</v>
+        <v>2677.564946831124</v>
       </c>
       <c r="E86">
         <v>1242.184289073493</v>
@@ -8342,45 +8342,45 @@
         <v>425.55</v>
       </c>
       <c r="M86">
-        <v>500.0537577962655</v>
+        <v>282.9681670942632</v>
       </c>
       <c r="N86">
-        <v>-74.50375779626552</v>
+        <v>142.5818329057368</v>
       </c>
       <c r="O86">
-        <v>-9.31296972453319</v>
+        <v>17.8227291132171</v>
       </c>
       <c r="P86">
-        <v>-65.19078807173233</v>
+        <v>124.7591037925197</v>
       </c>
       <c r="Q86">
-        <v>-38.49078807173233</v>
+        <v>151.4591037925197</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.3320273220568519</v>
+        <v>0.3269788004794567</v>
       </c>
       <c r="T86">
-        <v>5.576497765295231</v>
+        <v>5.480698179170724</v>
       </c>
       <c r="U86">
-        <v>0.1695366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V86">
-        <v>0.1063760629145646</v>
+        <v>0.125</v>
       </c>
       <c r="W86">
-        <v>0.151501978862118</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>0.851008503316517</v>
+        <v>1.50387940936918</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8391,13 +8391,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1816233999399007</v>
+        <v>0.1668279649355852</v>
       </c>
       <c r="C87">
-        <v>-1134.236851530484</v>
+        <v>-962.2323281818885</v>
       </c>
       <c r="D87">
-        <v>1697.409112766585</v>
+        <v>1869.41363611518</v>
       </c>
       <c r="E87">
         <v>1277.2977710064</v>
@@ -8424,37 +8424,37 @@
         <v>425.55</v>
       </c>
       <c r="M87">
-        <v>506.0067787224116</v>
+        <v>455.8647265222208</v>
       </c>
       <c r="N87">
-        <v>-80.45677872241157</v>
+        <v>-30.31472652222078</v>
       </c>
       <c r="O87">
-        <v>-10.05709734030145</v>
+        <v>-3.789340815277598</v>
       </c>
       <c r="P87">
-        <v>-70.39968138211012</v>
+        <v>-26.52538570694318</v>
       </c>
       <c r="Q87">
-        <v>-43.69968138211011</v>
+        <v>0.1746142930568162</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.3511091435273087</v>
+        <v>0.3476729101652054</v>
       </c>
       <c r="T87">
-        <v>5.94826428298158</v>
+        <v>5.884064894872069</v>
       </c>
       <c r="U87">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V87">
-        <v>0.1051245798214521</v>
+        <v>0.1166875761715841</v>
       </c>
       <c r="W87">
-        <v>0.1517141510715346</v>
+        <v>0.1349141510715346</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8409966385716168</v>
+        <v>0.933500609372673</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8473,13 +8473,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1828607661065261</v>
+        <v>0.1678973311022106</v>
       </c>
       <c r="C88">
-        <v>-1182.332380213817</v>
+        <v>-1010.959563262421</v>
       </c>
       <c r="D88">
-        <v>1684.427066016158</v>
+        <v>1855.799882967554</v>
       </c>
       <c r="E88">
         <v>1312.411252939307</v>
@@ -8506,37 +8506,37 @@
         <v>425.55</v>
       </c>
       <c r="M88">
-        <v>511.9597996485576</v>
+        <v>461.227840951894</v>
       </c>
       <c r="N88">
-        <v>-86.40979964855762</v>
+        <v>-35.67784095189398</v>
       </c>
       <c r="O88">
-        <v>-10.8012249560697</v>
+        <v>-4.459730118986748</v>
       </c>
       <c r="P88">
-        <v>-75.60857469248792</v>
+        <v>-31.21811083290724</v>
       </c>
       <c r="Q88">
-        <v>-48.90857469248792</v>
+        <v>-4.518110832907237</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.3729169394935451</v>
+        <v>0.3692352608912914</v>
       </c>
       <c r="T88">
-        <v>6.373140303194551</v>
+        <v>6.304355244505787</v>
       </c>
       <c r="U88">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V88">
-        <v>0.1039022009863189</v>
+        <v>0.1153307438905192</v>
       </c>
       <c r="W88">
-        <v>0.151921389043523</v>
+        <v>0.135121389043523</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8312176078905513</v>
+        <v>0.9226459511241535</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8555,13 +8555,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1840981322731514</v>
+        <v>0.1689666972688359</v>
       </c>
       <c r="C89">
-        <v>-1230.230838727684</v>
+        <v>-1059.489951206455</v>
       </c>
       <c r="D89">
-        <v>1671.642089435198</v>
+        <v>1842.382976956427</v>
       </c>
       <c r="E89">
         <v>1347.524734872213</v>
@@ -8588,37 +8588,37 @@
         <v>425.55</v>
       </c>
       <c r="M89">
-        <v>517.9128205747037</v>
+        <v>466.5909553815672</v>
       </c>
       <c r="N89">
-        <v>-92.36282057470368</v>
+        <v>-41.04095538156719</v>
       </c>
       <c r="O89">
-        <v>-11.54535257183796</v>
+        <v>-5.130119422695898</v>
       </c>
       <c r="P89">
-        <v>-80.81746800286572</v>
+        <v>-35.91083595887129</v>
       </c>
       <c r="Q89">
-        <v>-54.11746800286572</v>
+        <v>-9.210835958871289</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3980797809930485</v>
+        <v>0.3941148963444677</v>
       </c>
       <c r="T89">
-        <v>6.863381864978747</v>
+        <v>6.78930564792931</v>
       </c>
       <c r="U89">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V89">
-        <v>0.1027079228140624</v>
+        <v>0.1140051031561454</v>
       </c>
       <c r="W89">
-        <v>0.1521238629242013</v>
+        <v>0.1353238629242013</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.821663382512499</v>
+        <v>0.9120408252491632</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8637,13 +8637,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.1853354984397768</v>
+        <v>0.1700360634354612</v>
       </c>
       <c r="C90">
-        <v>-1277.936680618438</v>
+        <v>-1107.827730815303</v>
       </c>
       <c r="D90">
-        <v>1659.049729477351</v>
+        <v>1829.158679280485</v>
       </c>
       <c r="E90">
         <v>1382.63821680512</v>
@@ -8670,37 +8670,37 @@
         <v>425.55</v>
       </c>
       <c r="M90">
-        <v>523.8658415008496</v>
+        <v>471.9540698112403</v>
       </c>
       <c r="N90">
-        <v>-98.31584150084956</v>
+        <v>-46.40406981124033</v>
       </c>
       <c r="O90">
-        <v>-12.28948018760619</v>
+        <v>-5.800508726405042</v>
       </c>
       <c r="P90">
-        <v>-86.02636131324337</v>
+        <v>-40.60356108483529</v>
       </c>
       <c r="Q90">
-        <v>-59.32636131324337</v>
+        <v>-13.90356108483529</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.427436429409136</v>
+        <v>0.4231411377065068</v>
       </c>
       <c r="T90">
-        <v>7.435330353726977</v>
+        <v>7.355081118590087</v>
       </c>
       <c r="U90">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V90">
-        <v>0.101540787327539</v>
+        <v>0.1127095906202801</v>
       </c>
       <c r="W90">
-        <v>0.1523217351257732</v>
+        <v>0.1355217351257732</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8123262986203117</v>
+        <v>0.9016767249622409</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8719,13 +8719,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1865728646064021</v>
+        <v>0.1711054296020866</v>
       </c>
       <c r="C91">
-        <v>-1325.45422624276</v>
+        <v>-1155.97702005616</v>
       </c>
       <c r="D91">
-        <v>1646.645665785935</v>
+        <v>1816.122871972535</v>
       </c>
       <c r="E91">
         <v>1417.751698738027</v>
@@ -8752,37 +8752,37 @@
         <v>425.55</v>
       </c>
       <c r="M91">
-        <v>529.8188624269957</v>
+        <v>477.3171842409135</v>
       </c>
       <c r="N91">
-        <v>-104.2688624269957</v>
+        <v>-51.76718424091354</v>
       </c>
       <c r="O91">
-        <v>-13.03360780337446</v>
+        <v>-6.470898030114192</v>
       </c>
       <c r="P91">
-        <v>-91.23525462362122</v>
+        <v>-45.29628621079934</v>
       </c>
       <c r="Q91">
-        <v>-64.53525462362121</v>
+        <v>-18.59628621079935</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.4621306502645119</v>
+        <v>0.4574448774980074</v>
       </c>
       <c r="T91">
-        <v>8.111269476793066</v>
+        <v>8.023724856643732</v>
       </c>
       <c r="U91">
-        <v>0.1695366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1003998796047576</v>
+        <v>0.1114431907256702</v>
       </c>
       <c r="W91">
-        <v>0.1525151607610177</v>
+        <v>0.1357151607610177</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8031990368380608</v>
+        <v>0.8915455258053617</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8801,13 +8801,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.2358481162948784</v>
+        <v>0.1721747957687119</v>
       </c>
       <c r="C92">
-        <v>-1738.355672451215</v>
+        <v>-1203.941820337347</v>
       </c>
       <c r="D92">
-        <v>1268.857701510387</v>
+        <v>1803.271553624255</v>
       </c>
       <c r="E92">
         <v>1452.865180670933</v>
@@ -8834,45 +8834,45 @@
         <v>425.55</v>
       </c>
       <c r="M92">
-        <v>700.7350214739373</v>
+        <v>482.6802986705868</v>
       </c>
       <c r="N92">
-        <v>-275.1850214739373</v>
+        <v>-57.13029867058674</v>
       </c>
       <c r="O92">
-        <v>-34.39812768424216</v>
+        <v>-7.141287333823342</v>
       </c>
       <c r="P92">
-        <v>-240.7868937896951</v>
+        <v>-49.9890113367634</v>
       </c>
       <c r="Q92">
-        <v>-214.0868937896952</v>
+        <v>-23.2890113367634</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.5143425705094726</v>
+        <v>0.4986093652478082</v>
       </c>
       <c r="T92">
-        <v>9.12850170492384</v>
+        <v>8.826097342308106</v>
       </c>
       <c r="U92">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V92">
-        <v>0.07591136216955649</v>
+        <v>0.1102049330509405</v>
       </c>
       <c r="W92">
-        <v>0.2049042880488124</v>
+        <v>0.1359042880488124</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y92">
-        <v>0.6072908973564519</v>
+        <v>0.8816394644075244</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8883,13 +8883,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.2376074824615037</v>
+        <v>0.1732441619353373</v>
       </c>
       <c r="C93">
-        <v>-1783.77883327864</v>
+        <v>-1251.726020603332</v>
       </c>
       <c r="D93">
-        <v>1258.548022615869</v>
+        <v>1790.600835291177</v>
       </c>
       <c r="E93">
         <v>1487.97866260384</v>
@@ -8916,45 +8916,45 @@
         <v>425.55</v>
       </c>
       <c r="M93">
-        <v>708.5209661569811</v>
+        <v>488.04341310026</v>
       </c>
       <c r="N93">
-        <v>-282.9709661569811</v>
+        <v>-62.49341310025994</v>
       </c>
       <c r="O93">
-        <v>-35.37137076962264</v>
+        <v>-7.811676637532493</v>
       </c>
       <c r="P93">
-        <v>-247.5995953873584</v>
+        <v>-54.68173646272745</v>
       </c>
       <c r="Q93">
-        <v>-220.8995953873585</v>
+        <v>-27.98173646272745</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.5664028561216363</v>
+        <v>0.5489215169420091</v>
       </c>
       <c r="T93">
-        <v>10.1427796721376</v>
+        <v>9.806774824786785</v>
       </c>
       <c r="U93">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V93">
-        <v>0.07507717137648444</v>
+        <v>0.1089938898306005</v>
       </c>
       <c r="W93">
-        <v>0.2050892586929192</v>
+        <v>0.1360892586929192</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y93">
-        <v>0.6006173710118755</v>
+        <v>0.8719511186448043</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8965,13 +8965,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.2393668486281291</v>
+        <v>0.1743135281019626</v>
       </c>
       <c r="C94">
-        <v>-1829.035808694309</v>
+        <v>-1299.333401258302</v>
       </c>
       <c r="D94">
-        <v>1248.404529133107</v>
+        <v>1778.106936569114</v>
       </c>
       <c r="E94">
         <v>1523.092144536747</v>
@@ -8998,45 +8998,45 @@
         <v>425.55</v>
       </c>
       <c r="M94">
-        <v>716.3069108400248</v>
+        <v>493.4065275299332</v>
       </c>
       <c r="N94">
-        <v>-290.7569108400248</v>
+        <v>-67.85652752993315</v>
       </c>
       <c r="O94">
-        <v>-36.3446138550031</v>
+        <v>-8.482065941241643</v>
       </c>
       <c r="P94">
-        <v>-254.4122969850217</v>
+        <v>-59.3744615886915</v>
       </c>
       <c r="Q94">
-        <v>-227.7122969850217</v>
+        <v>-32.6744615886915</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.6314782131368409</v>
+        <v>0.6118117065597605</v>
       </c>
       <c r="T94">
-        <v>11.4106271311548</v>
+        <v>11.03262167788514</v>
       </c>
       <c r="U94">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V94">
-        <v>0.07426111516587049</v>
+        <v>0.1078091736367897</v>
       </c>
       <c r="W94">
-        <v>0.2052702082360672</v>
+        <v>0.1362702082360672</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y94">
-        <v>0.5940889213269639</v>
+        <v>0.8624733890943173</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9047,13 +9047,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.2411262147947544</v>
+        <v>0.175382894268588</v>
       </c>
       <c r="C95">
-        <v>-1874.130584775106</v>
+        <v>-1346.767637926622</v>
       </c>
       <c r="D95">
-        <v>1238.423234985216</v>
+        <v>1765.7861818337</v>
       </c>
       <c r="E95">
         <v>1558.205626469654</v>
@@ -9080,45 +9080,45 @@
         <v>425.55</v>
       </c>
       <c r="M95">
-        <v>724.0928555230686</v>
+        <v>498.7696419596063</v>
       </c>
       <c r="N95">
-        <v>-298.5428555230686</v>
+        <v>-73.21964195960629</v>
       </c>
       <c r="O95">
-        <v>-37.31785694038357</v>
+        <v>-9.152455244950787</v>
       </c>
       <c r="P95">
-        <v>-261.224998582685</v>
+        <v>-64.06718671465551</v>
       </c>
       <c r="Q95">
-        <v>-234.524998582685</v>
+        <v>-37.3671867146555</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.715146529299247</v>
+        <v>0.6926705217825834</v>
       </c>
       <c r="T95">
-        <v>13.04071672131978</v>
+        <v>12.60871048901159</v>
       </c>
       <c r="U95">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V95">
-        <v>0.07346260855118369</v>
+        <v>0.1066499352105876</v>
       </c>
       <c r="W95">
-        <v>0.2054472663911905</v>
+        <v>0.1364472663911905</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.5877008684094696</v>
+        <v>0.8531994816847011</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9129,13 +9129,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2428855809613798</v>
+        <v>0.1764522604352133</v>
       </c>
       <c r="C96">
-        <v>-1919.06702113048</v>
+        <v>-1394.032305058024</v>
       </c>
       <c r="D96">
-        <v>1228.600280562749</v>
+        <v>1753.634996635205</v>
       </c>
       <c r="E96">
         <v>1593.31910840256</v>
@@ -9162,45 +9162,45 @@
         <v>425.55</v>
       </c>
       <c r="M96">
-        <v>731.8788002061124</v>
+        <v>504.1327563892795</v>
       </c>
       <c r="N96">
-        <v>-306.3288002061124</v>
+        <v>-78.5827563892795</v>
       </c>
       <c r="O96">
-        <v>-38.29110002576405</v>
+        <v>-9.822844548659937</v>
       </c>
       <c r="P96">
-        <v>-268.0377001803483</v>
+        <v>-68.75991184061957</v>
       </c>
       <c r="Q96">
-        <v>-241.3377001803483</v>
+        <v>-42.05991184061956</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.826704284182455</v>
+        <v>0.8004822754130142</v>
       </c>
       <c r="T96">
-        <v>15.21416950820641</v>
+        <v>14.71016223718019</v>
       </c>
       <c r="U96">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V96">
-        <v>0.07268109143893706</v>
+        <v>0.1055153614317516</v>
       </c>
       <c r="W96">
-        <v>0.2056205573515239</v>
+        <v>0.1366205573515239</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5814487315114965</v>
+        <v>0.8441228914540126</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9211,13 +9211,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2446449471280051</v>
+        <v>0.1775216266018387</v>
       </c>
       <c r="C97">
-        <v>-1963.848855878568</v>
+        <v>-1441.130879384959</v>
       </c>
       <c r="D97">
-        <v>1218.931927747568</v>
+        <v>1741.649904241177</v>
       </c>
       <c r="E97">
         <v>1628.432590335467</v>
@@ -9244,45 +9244,45 @@
         <v>425.55</v>
       </c>
       <c r="M97">
-        <v>739.6647448891562</v>
+        <v>509.4958708189527</v>
       </c>
       <c r="N97">
-        <v>-314.1147448891562</v>
+        <v>-83.9458708189527</v>
       </c>
       <c r="O97">
-        <v>-39.26434311114452</v>
+        <v>-10.49323385236909</v>
       </c>
       <c r="P97">
-        <v>-274.8504017780116</v>
+        <v>-73.45263696658361</v>
       </c>
       <c r="Q97">
-        <v>-248.1504017780117</v>
+        <v>-46.75263696658361</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.9828851410189464</v>
+        <v>0.9514187304956175</v>
       </c>
       <c r="T97">
-        <v>18.25700340984771</v>
+        <v>17.65219468461623</v>
       </c>
       <c r="U97">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V97">
-        <v>0.0719160273185272</v>
+        <v>0.1044046734166805</v>
       </c>
       <c r="W97">
-        <v>0.2057902000811135</v>
+        <v>0.1367902000811135</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y97">
-        <v>0.5753282185482176</v>
+        <v>0.8352373873334441</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9293,13 +9293,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.2464043132946304</v>
+        <v>0.178590992768464</v>
       </c>
       <c r="C98">
-        <v>-2008.479710389187</v>
+        <v>-1488.066743239141</v>
       </c>
       <c r="D98">
-        <v>1209.414555169855</v>
+        <v>1729.827522319901</v>
       </c>
       <c r="E98">
         <v>1663.546072268374</v>
@@ -9326,45 +9326,45 @@
         <v>425.55</v>
       </c>
       <c r="M98">
-        <v>747.4506895721997</v>
+        <v>514.8589852486259</v>
       </c>
       <c r="N98">
-        <v>-321.9006895721997</v>
+        <v>-89.3089852486259</v>
       </c>
       <c r="O98">
-        <v>-40.23758619652497</v>
+        <v>-11.16362315607824</v>
       </c>
       <c r="P98">
-        <v>-281.6631033756748</v>
+        <v>-78.14536209254766</v>
       </c>
       <c r="Q98">
-        <v>-254.9631033756748</v>
+        <v>-51.44536209254765</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>1.21715642627368</v>
+        <v>1.177823413119519</v>
       </c>
       <c r="T98">
-        <v>22.82125426230958</v>
+        <v>22.06524335577024</v>
       </c>
       <c r="U98">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V98">
-        <v>0.07116690203395921</v>
+        <v>0.1033171247352568</v>
       </c>
       <c r="W98">
-        <v>0.20595630858717</v>
+        <v>0.13695630858717</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.5693352162716738</v>
+        <v>0.826536997882054</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9375,13 +9375,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.2481636794612558</v>
+        <v>0.1796603589350893</v>
       </c>
       <c r="C99">
-        <v>-2052.963093806356</v>
+        <v>-1534.843187733924</v>
       </c>
       <c r="D99">
-        <v>1200.044653685592</v>
+        <v>1718.164559758024</v>
       </c>
       <c r="E99">
         <v>1698.65955420128</v>
@@ -9408,45 +9408,45 @@
         <v>425.55</v>
       </c>
       <c r="M99">
-        <v>755.2366342552434</v>
+        <v>520.2220996782989</v>
       </c>
       <c r="N99">
-        <v>-329.6866342552434</v>
+        <v>-94.67209967829893</v>
       </c>
       <c r="O99">
-        <v>-41.21082928190543</v>
+        <v>-11.83401245978737</v>
       </c>
       <c r="P99">
-        <v>-288.475804973338</v>
+        <v>-82.83808721851156</v>
       </c>
       <c r="Q99">
-        <v>-261.775804973338</v>
+        <v>-56.13808721851156</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.607608568364908</v>
+        <v>1.555164550826026</v>
       </c>
       <c r="T99">
-        <v>30.42833901641277</v>
+        <v>29.42032447436032</v>
       </c>
       <c r="U99">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V99">
-        <v>0.07043322263154728</v>
+        <v>0.1022519997379861</v>
       </c>
       <c r="W99">
-        <v>0.2061189921755758</v>
+        <v>0.1371189921755758</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y99">
-        <v>0.5634657810523782</v>
+        <v>0.8180159979038888</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9457,13 +9457,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.2499230456278811</v>
+        <v>0.1807297251017146</v>
       </c>
       <c r="C100">
-        <v>-2097.302407362205</v>
+        <v>-1581.463415818798</v>
       </c>
       <c r="D100">
-        <v>1190.81882206265</v>
+        <v>1706.657813606058</v>
       </c>
       <c r="E100">
         <v>1733.773036134187</v>
@@ -9490,45 +9490,45 @@
         <v>425.55</v>
       </c>
       <c r="M100">
-        <v>763.0225789382872</v>
+        <v>525.5852141079722</v>
       </c>
       <c r="N100">
-        <v>-337.4725789382872</v>
+        <v>-100.0352141079722</v>
       </c>
       <c r="O100">
-        <v>-42.1840723672859</v>
+        <v>-12.50440176349652</v>
       </c>
       <c r="P100">
-        <v>-295.2885065710013</v>
+        <v>-87.53081234447566</v>
       </c>
       <c r="Q100">
-        <v>-268.5885065710013</v>
+        <v>-60.83081234447566</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>2.388512852547361</v>
+        <v>2.309846826239038</v>
       </c>
       <c r="T100">
-        <v>45.64250852461916</v>
+        <v>44.13048671154048</v>
       </c>
       <c r="U100">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V100">
-        <v>0.06971451627816413</v>
+        <v>0.1012086119855577</v>
       </c>
       <c r="W100">
-        <v>0.2062783556907488</v>
+        <v>0.1372783556907488</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y100">
-        <v>0.5577161302253131</v>
+        <v>0.8096688958844612</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9539,13 +9539,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.2516824117945065</v>
+        <v>0.18179909126834</v>
       </c>
       <c r="C101">
-        <v>-2141.500948493409</v>
+        <v>-1627.930545211969</v>
       </c>
       <c r="D101">
-        <v>1181.733762864353</v>
+        <v>1695.304166145793</v>
       </c>
       <c r="E101">
         <v>1768.886518067093</v>
@@ -9572,45 +9572,45 @@
         <v>425.55</v>
       </c>
       <c r="M101">
-        <v>770.808523621331</v>
+        <v>530.9483285376454</v>
       </c>
       <c r="N101">
-        <v>-345.258523621331</v>
+        <v>-105.3983285376453</v>
       </c>
       <c r="O101">
-        <v>-43.15731545266637</v>
+        <v>-13.17479106720567</v>
       </c>
       <c r="P101">
-        <v>-302.1012081686646</v>
+        <v>-92.22353747043968</v>
       </c>
       <c r="Q101">
-        <v>-275.4012081686647</v>
+        <v>-65.52353747043968</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>4.731225705094722</v>
+        <v>4.573893652478077</v>
       </c>
       <c r="T101">
-        <v>91.28501704923833</v>
+        <v>88.26097342308096</v>
       </c>
       <c r="U101">
-        <v>0.2217366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V101">
-        <v>0.06901032924505136</v>
+        <v>0.1001863027735823</v>
       </c>
       <c r="W101">
-        <v>0.2064344997409689</v>
+        <v>0.1374344997409689</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y101">
-        <v>0.5520826339604109</v>
+        <v>0.8014904221886586</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/ireland/ireland_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/ireland/ireland_publishing_newspapers.xlsx
@@ -1281,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1418,22 +1418,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09606660120303137</v>
+        <v>0.09603783834732474</v>
       </c>
       <c r="C2">
-        <v>3785.88280440116</v>
+        <v>3752.162852136417</v>
       </c>
       <c r="D2">
-        <v>3632.88280440116</v>
+        <v>3634.276334069324</v>
       </c>
       <c r="E2">
-        <v>-1707.348193290669</v>
+        <v>-1672.234711357762</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>35.11348193290669</v>
       </c>
       <c r="G2">
         <v>153</v>
@@ -1454,28 +1454,28 @@
         <v>425.55</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.97466342314769</v>
       </c>
       <c r="N2">
-        <v>425.55</v>
+        <v>423.5753365768523</v>
       </c>
       <c r="O2">
-        <v>53.19375</v>
+        <v>52.94691707210654</v>
       </c>
       <c r="P2">
-        <v>372.35625</v>
+        <v>370.6284195047458</v>
       </c>
       <c r="Q2">
-        <v>399.05625</v>
+        <v>397.3284195047457</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09606660120303137</v>
+        <v>0.09651087671871472</v>
       </c>
       <c r="T2">
-        <v>0.9797896186226994</v>
+        <v>0.9884493753529506</v>
       </c>
       <c r="U2">
         <v>0.0562366166625341</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>215.5050805172948</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1500,22 +1500,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09603783834732474</v>
+        <v>0.09600907549161812</v>
       </c>
       <c r="C3">
-        <v>3752.162852136417</v>
+        <v>3718.443969363989</v>
       </c>
       <c r="D3">
-        <v>3634.276334069324</v>
+        <v>3635.670933229802</v>
       </c>
       <c r="E3">
-        <v>-1672.234711357762</v>
+        <v>-1637.121229424855</v>
       </c>
       <c r="F3">
-        <v>35.11348193290669</v>
+        <v>70.22696386581337</v>
       </c>
       <c r="G3">
         <v>153</v>
@@ -1536,28 +1536,28 @@
         <v>425.55</v>
       </c>
       <c r="M3">
-        <v>1.97466342314769</v>
+        <v>3.949326846295381</v>
       </c>
       <c r="N3">
-        <v>423.5753365768523</v>
+        <v>421.6006731537046</v>
       </c>
       <c r="O3">
-        <v>52.94691707210654</v>
+        <v>52.70008414421308</v>
       </c>
       <c r="P3">
-        <v>370.6284195047458</v>
+        <v>368.9005890094916</v>
       </c>
       <c r="Q3">
-        <v>397.3284195047457</v>
+        <v>395.6005890094916</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09651087671871472</v>
+        <v>0.09696421908165692</v>
       </c>
       <c r="T3">
-        <v>0.9884493753529506</v>
+        <v>0.9972858618123904</v>
       </c>
       <c r="U3">
         <v>0.0562366166625341</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>215.5050805172948</v>
+        <v>107.7525402586474</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,22 +1582,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09600907549161812</v>
+        <v>0.09598031263591153</v>
       </c>
       <c r="C4">
-        <v>3718.443969363989</v>
+        <v>3684.726157315552</v>
       </c>
       <c r="D4">
-        <v>3635.670933229802</v>
+        <v>3637.066603114272</v>
       </c>
       <c r="E4">
-        <v>-1637.121229424855</v>
+        <v>-1602.007747491949</v>
       </c>
       <c r="F4">
-        <v>70.22696386581337</v>
+        <v>105.3404457987201</v>
       </c>
       <c r="G4">
         <v>153</v>
@@ -1618,28 +1618,28 @@
         <v>425.55</v>
       </c>
       <c r="M4">
-        <v>3.949326846295381</v>
+        <v>5.923990269443071</v>
       </c>
       <c r="N4">
-        <v>421.6006731537046</v>
+        <v>419.6260097305569</v>
       </c>
       <c r="O4">
-        <v>52.70008414421308</v>
+        <v>52.45325121631961</v>
       </c>
       <c r="P4">
-        <v>368.9005890094916</v>
+        <v>367.1727585142373</v>
       </c>
       <c r="Q4">
-        <v>395.6005890094916</v>
+        <v>393.8727585142373</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09696421908165692</v>
+        <v>0.09742690870981444</v>
       </c>
       <c r="T4">
-        <v>0.9972858618123904</v>
+        <v>1.006304543868932</v>
       </c>
       <c r="U4">
         <v>0.0562366166625341</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>107.7525402586474</v>
+        <v>71.83502683909826</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,22 +1664,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09598031263591153</v>
+        <v>0.0959515497802049</v>
       </c>
       <c r="C5">
-        <v>3684.726157315552</v>
+        <v>3651.00941722468</v>
       </c>
       <c r="D5">
-        <v>3637.066603114272</v>
+        <v>3638.463344956307</v>
       </c>
       <c r="E5">
-        <v>-1602.007747491949</v>
+        <v>-1566.894265559042</v>
       </c>
       <c r="F5">
-        <v>105.3404457987201</v>
+        <v>140.4539277316267</v>
       </c>
       <c r="G5">
         <v>153</v>
@@ -1700,28 +1700,28 @@
         <v>425.55</v>
       </c>
       <c r="M5">
-        <v>5.923990269443071</v>
+        <v>7.898653692590761</v>
       </c>
       <c r="N5">
-        <v>419.6260097305569</v>
+        <v>417.6513463074093</v>
       </c>
       <c r="O5">
-        <v>52.45325121631961</v>
+        <v>52.20641828842616</v>
       </c>
       <c r="P5">
-        <v>367.1727585142373</v>
+        <v>365.4449280189831</v>
       </c>
       <c r="Q5">
-        <v>393.8727585142373</v>
+        <v>392.1449280189831</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09742690870981444</v>
+        <v>0.09789923770522521</v>
       </c>
       <c r="T5">
-        <v>1.006304543868932</v>
+        <v>1.015511115134985</v>
       </c>
       <c r="U5">
         <v>0.0562366166625341</v>
@@ -1738,7 +1738,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>71.83502683909826</v>
+        <v>53.87627012932371</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,22 +1746,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0959515497802049</v>
+        <v>0.09592278692449828</v>
       </c>
       <c r="C6">
-        <v>3651.00941722468</v>
+        <v>3617.293750326835</v>
       </c>
       <c r="D6">
-        <v>3638.463344956307</v>
+        <v>3639.861159991369</v>
       </c>
       <c r="E6">
-        <v>-1566.894265559042</v>
+        <v>-1531.780783626135</v>
       </c>
       <c r="F6">
-        <v>140.4539277316267</v>
+        <v>175.5674096645334</v>
       </c>
       <c r="G6">
         <v>153</v>
@@ -1782,28 +1782,28 @@
         <v>425.55</v>
       </c>
       <c r="M6">
-        <v>7.898653692590761</v>
+        <v>9.873317115738452</v>
       </c>
       <c r="N6">
-        <v>417.6513463074093</v>
+        <v>415.6766828842615</v>
       </c>
       <c r="O6">
-        <v>52.20641828842616</v>
+        <v>51.95958536053269</v>
       </c>
       <c r="P6">
-        <v>365.4449280189831</v>
+        <v>363.7170975237289</v>
       </c>
       <c r="Q6">
-        <v>392.1449280189831</v>
+        <v>390.4170975237288</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09789923770522521</v>
+        <v>0.09838151046896045</v>
       </c>
       <c r="T6">
-        <v>1.015511115134985</v>
+        <v>1.024911508954008</v>
       </c>
       <c r="U6">
         <v>0.0562366166625341</v>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>53.87627012932371</v>
+        <v>43.10101610345896</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,22 +1828,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09592278692449828</v>
+        <v>0.09589402406879168</v>
       </c>
       <c r="C7">
-        <v>3617.293750326835</v>
+        <v>3583.579157859382</v>
       </c>
       <c r="D7">
-        <v>3639.861159991369</v>
+        <v>3641.260049456822</v>
       </c>
       <c r="E7">
-        <v>-1531.780783626135</v>
+        <v>-1496.667301693228</v>
       </c>
       <c r="F7">
-        <v>175.5674096645334</v>
+        <v>210.6808915974401</v>
       </c>
       <c r="G7">
         <v>153</v>
@@ -1864,28 +1864,28 @@
         <v>425.55</v>
       </c>
       <c r="M7">
-        <v>9.873317115738452</v>
+        <v>11.84798053888614</v>
       </c>
       <c r="N7">
-        <v>415.6766828842615</v>
+        <v>413.7020194611139</v>
       </c>
       <c r="O7">
-        <v>51.95958536053269</v>
+        <v>51.71275243263923</v>
       </c>
       <c r="P7">
-        <v>363.7170975237289</v>
+        <v>361.9892670284746</v>
       </c>
       <c r="Q7">
-        <v>390.4170975237288</v>
+        <v>388.6892670284746</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09838151046896045</v>
+        <v>0.09887404435532834</v>
       </c>
       <c r="T7">
-        <v>1.024911508954008</v>
+        <v>1.034511911152159</v>
       </c>
       <c r="U7">
         <v>0.0562366166625341</v>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.10101610345896</v>
+        <v>35.91751341954914</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,22 +1910,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09589402406879168</v>
+        <v>0.09586526121308507</v>
       </c>
       <c r="C8">
-        <v>3583.579157859382</v>
+        <v>3549.865641061588</v>
       </c>
       <c r="D8">
-        <v>3641.260049456822</v>
+        <v>3642.660014591935</v>
       </c>
       <c r="E8">
-        <v>-1496.667301693228</v>
+        <v>-1461.553819760322</v>
       </c>
       <c r="F8">
-        <v>210.6808915974401</v>
+        <v>245.7943735303468</v>
       </c>
       <c r="G8">
         <v>153</v>
@@ -1946,28 +1946,28 @@
         <v>425.55</v>
       </c>
       <c r="M8">
-        <v>11.84798053888614</v>
+        <v>13.82264396203383</v>
       </c>
       <c r="N8">
-        <v>413.7020194611139</v>
+        <v>411.7273560379662</v>
       </c>
       <c r="O8">
-        <v>51.71275243263923</v>
+        <v>51.46591950474577</v>
       </c>
       <c r="P8">
-        <v>361.9892670284746</v>
+        <v>360.2614365332204</v>
       </c>
       <c r="Q8">
-        <v>388.6892670284746</v>
+        <v>386.9614365332204</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09887404435532834</v>
+        <v>0.09937717036828478</v>
       </c>
       <c r="T8">
-        <v>1.034511911152159</v>
+        <v>1.044318773612635</v>
       </c>
       <c r="U8">
         <v>0.0562366166625341</v>
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>35.91751341954914</v>
+        <v>30.78644007389926</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,22 +1992,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09586526121308506</v>
+        <v>0.09583649835737845</v>
       </c>
       <c r="C9">
-        <v>3549.865641061589</v>
+        <v>3516.15320117463</v>
       </c>
       <c r="D9">
-        <v>3642.660014591936</v>
+        <v>3644.061056637884</v>
       </c>
       <c r="E9">
-        <v>-1461.553819760322</v>
+        <v>-1426.440337827415</v>
       </c>
       <c r="F9">
-        <v>245.7943735303468</v>
+        <v>280.9078554632535</v>
       </c>
       <c r="G9">
         <v>153</v>
@@ -2028,28 +2028,28 @@
         <v>425.55</v>
       </c>
       <c r="M9">
-        <v>13.82264396203383</v>
+        <v>15.79730738518152</v>
       </c>
       <c r="N9">
-        <v>411.7273560379662</v>
+        <v>409.7526926148185</v>
       </c>
       <c r="O9">
-        <v>51.46591950474577</v>
+        <v>51.21908657685231</v>
       </c>
       <c r="P9">
-        <v>360.2614365332204</v>
+        <v>358.5336060379662</v>
       </c>
       <c r="Q9">
-        <v>386.9614365332204</v>
+        <v>385.2336060379662</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09937717036828478</v>
+        <v>0.09989123390326202</v>
       </c>
       <c r="T9">
-        <v>1.044318773612635</v>
+        <v>1.054338828735296</v>
       </c>
       <c r="U9">
         <v>0.0562366166625341</v>
@@ -2066,7 +2066,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>30.78644007389926</v>
+        <v>26.93813506466185</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,22 +2074,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09583649835737845</v>
+        <v>0.09580773550167182</v>
       </c>
       <c r="C10">
-        <v>3516.15320117463</v>
+        <v>3482.441839441591</v>
       </c>
       <c r="D10">
-        <v>3644.061056637884</v>
+        <v>3645.463176837751</v>
       </c>
       <c r="E10">
-        <v>-1426.440337827415</v>
+        <v>-1391.326855894509</v>
       </c>
       <c r="F10">
-        <v>280.9078554632535</v>
+        <v>316.0213373961602</v>
       </c>
       <c r="G10">
         <v>153</v>
@@ -2110,28 +2110,28 @@
         <v>425.55</v>
       </c>
       <c r="M10">
-        <v>15.79730738518152</v>
+        <v>17.77197080832921</v>
       </c>
       <c r="N10">
-        <v>409.7526926148185</v>
+        <v>407.7780291916708</v>
       </c>
       <c r="O10">
-        <v>51.21908657685231</v>
+        <v>50.97225364895885</v>
       </c>
       <c r="P10">
-        <v>358.5336060379662</v>
+        <v>356.805775542712</v>
       </c>
       <c r="Q10">
-        <v>385.2336060379662</v>
+        <v>383.5057755427119</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09989123390326202</v>
+        <v>0.1004165955379091</v>
       </c>
       <c r="T10">
-        <v>1.054338828735296</v>
+        <v>1.064579104849664</v>
       </c>
       <c r="U10">
         <v>0.0562366166625341</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>26.93813506466185</v>
+        <v>23.94500894636609</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,22 +2156,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09580773550167182</v>
+        <v>0.09577897264596522</v>
       </c>
       <c r="C11">
-        <v>3482.441839441591</v>
+        <v>3448.731557107466</v>
       </c>
       <c r="D11">
-        <v>3645.463176837751</v>
+        <v>3646.866376436533</v>
       </c>
       <c r="E11">
-        <v>-1391.326855894509</v>
+        <v>-1356.213373961602</v>
       </c>
       <c r="F11">
-        <v>316.0213373961602</v>
+        <v>351.1348193290668</v>
       </c>
       <c r="G11">
         <v>153</v>
@@ -2192,28 +2192,28 @@
         <v>425.55</v>
       </c>
       <c r="M11">
-        <v>17.77197080832921</v>
+        <v>19.7466342314769</v>
       </c>
       <c r="N11">
-        <v>407.7780291916708</v>
+        <v>405.8033657685231</v>
       </c>
       <c r="O11">
-        <v>50.97225364895885</v>
+        <v>50.72542072106539</v>
       </c>
       <c r="P11">
-        <v>356.805775542712</v>
+        <v>355.0779450474577</v>
       </c>
       <c r="Q11">
-        <v>383.5057755427119</v>
+        <v>381.7779450474577</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1004165955379091</v>
+        <v>0.1009536318755483</v>
       </c>
       <c r="T11">
-        <v>1.064579104849664</v>
+        <v>1.075046942655462</v>
       </c>
       <c r="U11">
         <v>0.0562366166625341</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>23.94500894636609</v>
+        <v>21.55050805172949</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,22 +2238,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09577897264596522</v>
+        <v>0.09575020979025861</v>
       </c>
       <c r="C12">
-        <v>3448.731557107466</v>
+        <v>3415.022355419174</v>
       </c>
       <c r="D12">
-        <v>3646.866376436533</v>
+        <v>3648.270656681148</v>
       </c>
       <c r="E12">
-        <v>-1356.213373961602</v>
+        <v>-1321.099892028695</v>
       </c>
       <c r="F12">
-        <v>351.1348193290669</v>
+        <v>386.2483012619736</v>
       </c>
       <c r="G12">
         <v>153</v>
@@ -2274,28 +2274,28 @@
         <v>425.55</v>
       </c>
       <c r="M12">
-        <v>19.7466342314769</v>
+        <v>21.72129765462459</v>
       </c>
       <c r="N12">
-        <v>405.8033657685231</v>
+        <v>403.8287023453754</v>
       </c>
       <c r="O12">
-        <v>50.72542072106539</v>
+        <v>50.47858779317193</v>
       </c>
       <c r="P12">
-        <v>355.0779450474577</v>
+        <v>353.3501145522035</v>
       </c>
       <c r="Q12">
-        <v>381.7779450474577</v>
+        <v>380.0501145522035</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1009536318755483</v>
+        <v>0.101502736445494</v>
       </c>
       <c r="T12">
-        <v>1.075046942655462</v>
+        <v>1.085750012771503</v>
       </c>
       <c r="U12">
         <v>0.0562366166625341</v>
@@ -2312,7 +2312,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.55050805172948</v>
+        <v>19.59137095611771</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,22 +2320,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09575020979025861</v>
+        <v>0.09572144693455198</v>
       </c>
       <c r="C13">
-        <v>3415.022355419174</v>
+        <v>3381.314235625553</v>
       </c>
       <c r="D13">
-        <v>3648.270656681148</v>
+        <v>3649.676018820434</v>
       </c>
       <c r="E13">
-        <v>-1321.099892028695</v>
+        <v>-1285.986410095788</v>
       </c>
       <c r="F13">
-        <v>386.2483012619736</v>
+        <v>421.3617831948803</v>
       </c>
       <c r="G13">
         <v>153</v>
@@ -2356,28 +2356,28 @@
         <v>425.55</v>
       </c>
       <c r="M13">
-        <v>21.72129765462459</v>
+        <v>23.69596107777229</v>
       </c>
       <c r="N13">
-        <v>403.8287023453754</v>
+        <v>401.8540389222277</v>
       </c>
       <c r="O13">
-        <v>50.47858779317193</v>
+        <v>50.23175486527847</v>
       </c>
       <c r="P13">
-        <v>353.3501145522035</v>
+        <v>351.6222840569493</v>
       </c>
       <c r="Q13">
-        <v>380.0501145522035</v>
+        <v>378.3222840569493</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.101502736445494</v>
+        <v>0.1020643206647567</v>
       </c>
       <c r="T13">
-        <v>1.085750012771503</v>
+        <v>1.09669633448109</v>
       </c>
       <c r="U13">
         <v>0.0562366166625341</v>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.59137095611771</v>
+        <v>17.95875670977457</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,22 +2402,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09572144693455198</v>
+        <v>0.09569268407884537</v>
       </c>
       <c r="C14">
-        <v>3381.314235625553</v>
+        <v>3347.607198977364</v>
       </c>
       <c r="D14">
-        <v>3649.676018820434</v>
+        <v>3651.082464105151</v>
       </c>
       <c r="E14">
-        <v>-1285.986410095788</v>
+        <v>-1250.872928162882</v>
       </c>
       <c r="F14">
-        <v>421.3617831948803</v>
+        <v>456.4752651277869</v>
       </c>
       <c r="G14">
         <v>153</v>
@@ -2438,28 +2438,28 @@
         <v>425.55</v>
       </c>
       <c r="M14">
-        <v>23.69596107777229</v>
+        <v>25.67062450091997</v>
       </c>
       <c r="N14">
-        <v>401.8540389222277</v>
+        <v>399.87937549908</v>
       </c>
       <c r="O14">
-        <v>50.23175486527847</v>
+        <v>49.984921937385</v>
       </c>
       <c r="P14">
-        <v>351.6222840569493</v>
+        <v>349.894453561695</v>
       </c>
       <c r="Q14">
-        <v>378.3222840569493</v>
+        <v>376.594453561695</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1020643206647567</v>
+        <v>0.1026388148660714</v>
       </c>
       <c r="T14">
-        <v>1.09669633448109</v>
+        <v>1.107894295770208</v>
       </c>
       <c r="U14">
         <v>0.0562366166625341</v>
@@ -2476,7 +2476,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>17.95875670977457</v>
+        <v>16.57731388594576</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,22 +2484,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09569268407884537</v>
+        <v>0.09566392122313874</v>
       </c>
       <c r="C15">
-        <v>3347.607198977364</v>
+        <v>3313.901246727298</v>
       </c>
       <c r="D15">
-        <v>3651.082464105151</v>
+        <v>3652.489993787992</v>
       </c>
       <c r="E15">
-        <v>-1250.872928162882</v>
+        <v>-1215.759446229975</v>
       </c>
       <c r="F15">
-        <v>456.4752651277869</v>
+        <v>491.5887470606937</v>
       </c>
       <c r="G15">
         <v>153</v>
@@ -2520,28 +2520,28 @@
         <v>425.55</v>
       </c>
       <c r="M15">
-        <v>25.67062450091997</v>
+        <v>27.64528792406767</v>
       </c>
       <c r="N15">
-        <v>399.87937549908</v>
+        <v>397.9047120759324</v>
       </c>
       <c r="O15">
-        <v>49.984921937385</v>
+        <v>49.73808900949155</v>
       </c>
       <c r="P15">
-        <v>349.894453561695</v>
+        <v>348.1666230664408</v>
       </c>
       <c r="Q15">
-        <v>376.594453561695</v>
+        <v>374.8666230664408</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1026388148660714</v>
+        <v>0.1032266693976492</v>
       </c>
       <c r="T15">
-        <v>1.107894295770208</v>
+        <v>1.119352674763723</v>
       </c>
       <c r="U15">
         <v>0.0562366166625341</v>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.57731388594576</v>
+        <v>15.39322003694963</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,22 +2566,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09566392122313874</v>
+        <v>0.09563515836743214</v>
       </c>
       <c r="C16">
-        <v>3313.901246727298</v>
+        <v>3280.196380129978</v>
       </c>
       <c r="D16">
-        <v>3652.489993787992</v>
+        <v>3653.898609123578</v>
       </c>
       <c r="E16">
-        <v>-1215.759446229975</v>
+        <v>-1180.645964297068</v>
       </c>
       <c r="F16">
-        <v>491.5887470606937</v>
+        <v>526.7022289936004</v>
       </c>
       <c r="G16">
         <v>153</v>
@@ -2602,28 +2602,28 @@
         <v>425.55</v>
       </c>
       <c r="M16">
-        <v>27.64528792406767</v>
+        <v>29.61995134721536</v>
       </c>
       <c r="N16">
-        <v>397.9047120759324</v>
+        <v>395.9300486527846</v>
       </c>
       <c r="O16">
-        <v>49.73808900949155</v>
+        <v>49.49125608159808</v>
       </c>
       <c r="P16">
-        <v>348.1666230664408</v>
+        <v>346.4387925711866</v>
       </c>
       <c r="Q16">
-        <v>374.8666230664408</v>
+        <v>373.1387925711866</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1032266693976492</v>
+        <v>0.1038283558005583</v>
       </c>
       <c r="T16">
-        <v>1.119352674763723</v>
+        <v>1.131080662674734</v>
       </c>
       <c r="U16">
         <v>0.0562366166625341</v>
@@ -2640,7 +2640,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.39322003694963</v>
+        <v>14.36700536781965</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,22 +2648,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09563515836743214</v>
+        <v>0.09560639551172552</v>
       </c>
       <c r="C17">
-        <v>3280.196380129978</v>
+        <v>3246.492600441964</v>
       </c>
       <c r="D17">
-        <v>3653.898609123578</v>
+        <v>3655.308311368471</v>
       </c>
       <c r="E17">
-        <v>-1180.645964297068</v>
+        <v>-1145.532482364162</v>
       </c>
       <c r="F17">
-        <v>526.7022289936003</v>
+        <v>561.815710926507</v>
       </c>
       <c r="G17">
         <v>153</v>
@@ -2684,28 +2684,28 @@
         <v>425.55</v>
       </c>
       <c r="M17">
-        <v>29.61995134721536</v>
+        <v>31.59461477036304</v>
       </c>
       <c r="N17">
-        <v>395.9300486527846</v>
+        <v>393.955385229637</v>
       </c>
       <c r="O17">
-        <v>49.49125608159808</v>
+        <v>49.24442315370462</v>
       </c>
       <c r="P17">
-        <v>346.4387925711866</v>
+        <v>344.7109620759323</v>
       </c>
       <c r="Q17">
-        <v>373.1387925711866</v>
+        <v>371.4109620759323</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1038283558005583</v>
+        <v>0.1044443680702033</v>
       </c>
       <c r="T17">
-        <v>1.131080662674734</v>
+        <v>1.143087888393149</v>
       </c>
       <c r="U17">
         <v>0.0562366166625341</v>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.36700536781965</v>
+        <v>13.46906753233093</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,22 +2730,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09560639551172552</v>
+        <v>0.09580075765601889</v>
       </c>
       <c r="C18">
-        <v>3246.492600441964</v>
+        <v>3201.87429985764</v>
       </c>
       <c r="D18">
-        <v>3655.308311368471</v>
+        <v>3645.803492717054</v>
       </c>
       <c r="E18">
-        <v>-1145.532482364162</v>
+        <v>-1110.419000431255</v>
       </c>
       <c r="F18">
-        <v>561.815710926507</v>
+        <v>596.9291928594138</v>
       </c>
       <c r="G18">
         <v>153</v>
@@ -2766,45 +2766,45 @@
         <v>425.55</v>
       </c>
       <c r="M18">
-        <v>31.59461477036304</v>
+        <v>34.46467198279986</v>
       </c>
       <c r="N18">
-        <v>393.955385229637</v>
+        <v>391.0853280172001</v>
       </c>
       <c r="O18">
-        <v>49.24442315370462</v>
+        <v>48.88566600215002</v>
       </c>
       <c r="P18">
-        <v>344.7109620759323</v>
+        <v>342.1996620150501</v>
       </c>
       <c r="Q18">
-        <v>371.4109620759323</v>
+        <v>368.8996620150501</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1044443680702033</v>
+        <v>0.1050752240089963</v>
       </c>
       <c r="T18">
-        <v>1.143087888393149</v>
+        <v>1.155384444851768</v>
       </c>
       <c r="U18">
-        <v>0.0562366166625341</v>
+        <v>0.05773661666253409</v>
       </c>
       <c r="V18">
         <v>0.125</v>
       </c>
       <c r="W18">
-        <v>0.04920703957971734</v>
+        <v>0.05051953957971733</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>13.46906753233093</v>
+        <v>12.34742637946409</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,22 +2812,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09580075765601889</v>
+        <v>0.09578511980031229</v>
       </c>
       <c r="C19">
-        <v>3201.87429985764</v>
+        <v>3167.52372117722</v>
       </c>
       <c r="D19">
-        <v>3645.803492717054</v>
+        <v>3646.566395969541</v>
       </c>
       <c r="E19">
-        <v>-1110.419000431255</v>
+        <v>-1075.305518498348</v>
       </c>
       <c r="F19">
-        <v>596.9291928594138</v>
+        <v>632.0426747923204</v>
       </c>
       <c r="G19">
         <v>153</v>
@@ -2848,28 +2848,28 @@
         <v>425.55</v>
       </c>
       <c r="M19">
-        <v>34.46467198279986</v>
+        <v>36.4920056288469</v>
       </c>
       <c r="N19">
-        <v>391.0853280172001</v>
+        <v>389.0579943711531</v>
       </c>
       <c r="O19">
-        <v>48.88566600215002</v>
+        <v>48.63224929639414</v>
       </c>
       <c r="P19">
-        <v>342.1996620150501</v>
+        <v>340.4257450747589</v>
       </c>
       <c r="Q19">
-        <v>368.8996620150501</v>
+        <v>367.1257450747589</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1050752240089963</v>
+        <v>0.1057214666780039</v>
       </c>
       <c r="T19">
-        <v>1.155384444851768</v>
+        <v>1.167980917321572</v>
       </c>
       <c r="U19">
         <v>0.05773661666253409</v>
@@ -2886,7 +2886,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>12.34742637946409</v>
+        <v>11.66145824727164</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,22 +2894,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09578511980031229</v>
+        <v>0.09576948194460567</v>
       </c>
       <c r="C20">
-        <v>3167.523721177221</v>
+        <v>3133.173461846536</v>
       </c>
       <c r="D20">
-        <v>3646.566395969541</v>
+        <v>3647.329618571763</v>
       </c>
       <c r="E20">
-        <v>-1075.305518498348</v>
+        <v>-1040.192036565441</v>
       </c>
       <c r="F20">
-        <v>632.0426747923203</v>
+        <v>667.1561567252271</v>
       </c>
       <c r="G20">
         <v>153</v>
@@ -2930,28 +2930,28 @@
         <v>425.55</v>
       </c>
       <c r="M20">
-        <v>36.4920056288469</v>
+        <v>38.51933927489396</v>
       </c>
       <c r="N20">
-        <v>389.0579943711531</v>
+        <v>387.030660725106</v>
       </c>
       <c r="O20">
-        <v>48.63224929639414</v>
+        <v>48.37883259063825</v>
       </c>
       <c r="P20">
-        <v>340.4257450747589</v>
+        <v>338.6518281344678</v>
       </c>
       <c r="Q20">
-        <v>367.1257450747589</v>
+        <v>365.3518281344678</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1057214666780039</v>
+        <v>0.1063836659561227</v>
       </c>
       <c r="T20">
-        <v>1.167980917321572</v>
+        <v>1.180888413802976</v>
       </c>
       <c r="U20">
         <v>0.05773661666253409</v>
@@ -2968,7 +2968,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.66145824727165</v>
+        <v>11.04769728688892</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,22 +2976,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09576948194460567</v>
+        <v>0.09575384408889905</v>
       </c>
       <c r="C21">
-        <v>3133.173461846536</v>
+        <v>3098.823522066148</v>
       </c>
       <c r="D21">
-        <v>3647.329618571763</v>
+        <v>3648.093160724282</v>
       </c>
       <c r="E21">
-        <v>-1040.192036565441</v>
+        <v>-1005.078554632535</v>
       </c>
       <c r="F21">
-        <v>667.1561567252271</v>
+        <v>702.2696386581338</v>
       </c>
       <c r="G21">
         <v>153</v>
@@ -3012,28 +3012,28 @@
         <v>425.55</v>
       </c>
       <c r="M21">
-        <v>38.51933927489396</v>
+        <v>40.54667292094101</v>
       </c>
       <c r="N21">
-        <v>387.030660725106</v>
+        <v>385.003327079059</v>
       </c>
       <c r="O21">
-        <v>48.37883259063825</v>
+        <v>48.12541588488237</v>
       </c>
       <c r="P21">
-        <v>338.6518281344678</v>
+        <v>336.8779111941766</v>
       </c>
       <c r="Q21">
-        <v>365.3518281344678</v>
+        <v>363.5779111941766</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1063836659561227</v>
+        <v>0.1070624202161945</v>
       </c>
       <c r="T21">
-        <v>1.180888413802976</v>
+        <v>1.194118597696415</v>
       </c>
       <c r="U21">
         <v>0.05773661666253409</v>
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.04769728688892</v>
+        <v>10.49531242254448</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,22 +3058,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09575384408889905</v>
+        <v>0.09573820623319244</v>
       </c>
       <c r="C22">
-        <v>3098.823522066148</v>
+        <v>3064.473902036782</v>
       </c>
       <c r="D22">
-        <v>3648.093160724282</v>
+        <v>3648.857022627823</v>
       </c>
       <c r="E22">
-        <v>-1005.078554632535</v>
+        <v>-969.9650726996281</v>
       </c>
       <c r="F22">
-        <v>702.2696386581338</v>
+        <v>737.3831205910406</v>
       </c>
       <c r="G22">
         <v>153</v>
@@ -3094,28 +3094,28 @@
         <v>425.55</v>
       </c>
       <c r="M22">
-        <v>40.54667292094101</v>
+        <v>42.57400656698806</v>
       </c>
       <c r="N22">
-        <v>385.003327079059</v>
+        <v>382.9759934330119</v>
       </c>
       <c r="O22">
-        <v>48.12541588488237</v>
+        <v>47.87199917912649</v>
       </c>
       <c r="P22">
-        <v>336.8779111941766</v>
+        <v>335.1039942538854</v>
       </c>
       <c r="Q22">
-        <v>363.5779111941766</v>
+        <v>361.8039942538854</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1070624202161945</v>
+        <v>0.10775835812842</v>
       </c>
       <c r="T22">
-        <v>1.194118597696415</v>
+        <v>1.207683722954245</v>
       </c>
       <c r="U22">
         <v>0.05773661666253409</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.49531242254448</v>
+        <v>9.99553564051855</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,22 +3140,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09573820623319244</v>
+        <v>0.09604981837748582</v>
       </c>
       <c r="C23">
-        <v>3064.473902036782</v>
+        <v>3014.199181978634</v>
       </c>
       <c r="D23">
-        <v>3648.857022627823</v>
+        <v>3633.695784502582</v>
       </c>
       <c r="E23">
-        <v>-969.9650726996282</v>
+        <v>-934.8515907667215</v>
       </c>
       <c r="F23">
-        <v>737.3831205910404</v>
+        <v>772.4966025239471</v>
       </c>
       <c r="G23">
         <v>153</v>
@@ -3176,45 +3176,45 @@
         <v>425.55</v>
       </c>
       <c r="M23">
-        <v>42.57400656698805</v>
+        <v>45.91458443732581</v>
       </c>
       <c r="N23">
-        <v>382.975993433012</v>
+        <v>379.6354155626742</v>
       </c>
       <c r="O23">
-        <v>47.8719991791265</v>
+        <v>47.45442694533428</v>
       </c>
       <c r="P23">
-        <v>335.1039942538855</v>
+        <v>332.1809886173399</v>
       </c>
       <c r="Q23">
-        <v>361.8039942538855</v>
+        <v>358.8809886173399</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.10775835812842</v>
+        <v>0.1084721406024974</v>
       </c>
       <c r="T23">
-        <v>1.207683722954245</v>
+        <v>1.221596671936635</v>
       </c>
       <c r="U23">
-        <v>0.05773661666253409</v>
+        <v>0.05943661666253409</v>
       </c>
       <c r="V23">
         <v>0.125</v>
       </c>
       <c r="W23">
-        <v>0.05051953957971733</v>
+        <v>0.05200703957971733</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>9.995535640518554</v>
+        <v>9.268296886817804</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,22 +3222,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09604981837748582</v>
+        <v>0.09604905552177921</v>
       </c>
       <c r="C24">
-        <v>3014.199181978634</v>
+        <v>2979.122662332305</v>
       </c>
       <c r="D24">
-        <v>3633.695784502582</v>
+        <v>3633.732746789159</v>
       </c>
       <c r="E24">
-        <v>-934.8515907667215</v>
+        <v>-899.7381088338147</v>
       </c>
       <c r="F24">
-        <v>772.4966025239471</v>
+        <v>807.6100844568539</v>
       </c>
       <c r="G24">
         <v>153</v>
@@ -3258,28 +3258,28 @@
         <v>425.55</v>
       </c>
       <c r="M24">
-        <v>45.91458443732581</v>
+        <v>48.00161100265881</v>
       </c>
       <c r="N24">
-        <v>379.6354155626742</v>
+        <v>377.5483889973412</v>
       </c>
       <c r="O24">
-        <v>47.45442694533428</v>
+        <v>47.19354862466765</v>
       </c>
       <c r="P24">
-        <v>332.1809886173399</v>
+        <v>330.3548403726736</v>
       </c>
       <c r="Q24">
-        <v>358.8809886173399</v>
+        <v>357.0548403726735</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1084721406024974</v>
+        <v>0.1092044628810964</v>
       </c>
       <c r="T24">
-        <v>1.221596671936635</v>
+        <v>1.235870996217268</v>
       </c>
       <c r="U24">
         <v>0.05943661666253409</v>
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.268296886817804</v>
+        <v>8.865327456956159</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,22 +3304,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09604905552177921</v>
+        <v>0.09604829266607259</v>
       </c>
       <c r="C25">
-        <v>2979.122662332305</v>
+        <v>2944.046143437951</v>
       </c>
       <c r="D25">
-        <v>3633.732746789159</v>
+        <v>3633.769709827712</v>
       </c>
       <c r="E25">
-        <v>-899.7381088338147</v>
+        <v>-864.6246269009081</v>
       </c>
       <c r="F25">
-        <v>807.6100844568539</v>
+        <v>842.7235663897605</v>
       </c>
       <c r="G25">
         <v>153</v>
@@ -3340,28 +3340,28 @@
         <v>425.55</v>
       </c>
       <c r="M25">
-        <v>48.00161100265881</v>
+        <v>50.0886375679918</v>
       </c>
       <c r="N25">
-        <v>377.5483889973412</v>
+        <v>375.4613624320082</v>
       </c>
       <c r="O25">
-        <v>47.19354862466765</v>
+        <v>46.93267030400103</v>
       </c>
       <c r="P25">
-        <v>330.3548403726736</v>
+        <v>328.5286921280072</v>
       </c>
       <c r="Q25">
-        <v>357.0548403726735</v>
+        <v>355.2286921280072</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1092044628810964</v>
+        <v>0.1099560567986058</v>
       </c>
       <c r="T25">
-        <v>1.235870996217268</v>
+        <v>1.250520960610551</v>
       </c>
       <c r="U25">
         <v>0.05943661666253409</v>
@@ -3378,7 +3378,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.865327456956159</v>
+        <v>8.495938812916322</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,22 +3386,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09604829266607258</v>
+        <v>0.09604752981036596</v>
       </c>
       <c r="C26">
-        <v>2944.046143437952</v>
+        <v>2908.969625295596</v>
       </c>
       <c r="D26">
-        <v>3633.769709827713</v>
+        <v>3633.806673618263</v>
       </c>
       <c r="E26">
-        <v>-864.6246269009081</v>
+        <v>-829.5111449680014</v>
       </c>
       <c r="F26">
-        <v>842.7235663897605</v>
+        <v>877.8370483226672</v>
       </c>
       <c r="G26">
         <v>153</v>
@@ -3422,28 +3422,28 @@
         <v>425.55</v>
       </c>
       <c r="M26">
-        <v>50.0886375679918</v>
+        <v>52.17566413332479</v>
       </c>
       <c r="N26">
-        <v>375.4613624320082</v>
+        <v>373.3743358666752</v>
       </c>
       <c r="O26">
-        <v>46.93267030400103</v>
+        <v>46.6717919833344</v>
       </c>
       <c r="P26">
-        <v>328.5286921280072</v>
+        <v>326.7025438833408</v>
       </c>
       <c r="Q26">
-        <v>355.2286921280072</v>
+        <v>353.4025438833408</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1099560567986058</v>
+        <v>0.1107276932205822</v>
       </c>
       <c r="T26">
-        <v>1.250520960610551</v>
+        <v>1.265561590720987</v>
       </c>
       <c r="U26">
         <v>0.05943661666253409</v>
@@ -3460,7 +3460,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.495938812916322</v>
+        <v>8.156101260399666</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,22 +3468,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09604752981036596</v>
+        <v>0.09604676695465936</v>
       </c>
       <c r="C27">
-        <v>2908.969625295596</v>
+        <v>2873.893107905261</v>
       </c>
       <c r="D27">
-        <v>3633.806673618263</v>
+        <v>3633.843638160835</v>
       </c>
       <c r="E27">
-        <v>-829.5111449680014</v>
+        <v>-794.3976630350948</v>
       </c>
       <c r="F27">
-        <v>877.8370483226672</v>
+        <v>912.9505302555739</v>
       </c>
       <c r="G27">
         <v>153</v>
@@ -3504,28 +3504,28 @@
         <v>425.55</v>
       </c>
       <c r="M27">
-        <v>52.17566413332479</v>
+        <v>54.26269069865778</v>
       </c>
       <c r="N27">
-        <v>373.3743358666752</v>
+        <v>371.2873093013422</v>
       </c>
       <c r="O27">
-        <v>46.6717919833344</v>
+        <v>46.41091366266778</v>
       </c>
       <c r="P27">
-        <v>326.7025438833408</v>
+        <v>324.8763956386745</v>
       </c>
       <c r="Q27">
-        <v>353.4025438833408</v>
+        <v>351.5763956386745</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1107276932205822</v>
+        <v>0.1115201846809903</v>
       </c>
       <c r="T27">
-        <v>1.265561590720987</v>
+        <v>1.281008724347921</v>
       </c>
       <c r="U27">
         <v>0.05943661666253409</v>
@@ -3542,7 +3542,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.156101260399666</v>
+        <v>7.842405058076603</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,22 +3550,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09604676695465936</v>
+        <v>0.09623500409895275</v>
       </c>
       <c r="C28">
-        <v>2873.893107905261</v>
+        <v>2829.681248829607</v>
       </c>
       <c r="D28">
-        <v>3633.843638160835</v>
+        <v>3624.745261018088</v>
       </c>
       <c r="E28">
-        <v>-794.3976630350948</v>
+        <v>-759.284181102188</v>
       </c>
       <c r="F28">
-        <v>912.9505302555739</v>
+        <v>948.0640121884807</v>
       </c>
       <c r="G28">
         <v>153</v>
@@ -3586,45 +3586,45 @@
         <v>425.55</v>
       </c>
       <c r="M28">
-        <v>54.26269069865778</v>
+        <v>57.10816847374156</v>
       </c>
       <c r="N28">
-        <v>371.2873093013422</v>
+        <v>368.4418315262585</v>
       </c>
       <c r="O28">
-        <v>46.41091366266778</v>
+        <v>46.05522894078231</v>
       </c>
       <c r="P28">
-        <v>324.8763956386745</v>
+        <v>322.3866025854762</v>
       </c>
       <c r="Q28">
-        <v>351.5763956386745</v>
+        <v>349.0866025854762</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1115201846809903</v>
+        <v>0.1123343882362042</v>
       </c>
       <c r="T28">
-        <v>1.281008724347921</v>
+        <v>1.29687906711532</v>
       </c>
       <c r="U28">
-        <v>0.05943661666253409</v>
+        <v>0.0602366166625341</v>
       </c>
       <c r="V28">
         <v>0.125</v>
       </c>
       <c r="W28">
-        <v>0.05200703957971733</v>
+        <v>0.05270703957971733</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y28">
-        <v>7.842405058076603</v>
+        <v>7.45164853598253</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,22 +3632,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09623500409895275</v>
+        <v>0.09624124124324612</v>
       </c>
       <c r="C29">
-        <v>2829.681248829607</v>
+        <v>2794.267076452096</v>
       </c>
       <c r="D29">
-        <v>3624.745261018088</v>
+        <v>3624.444570573484</v>
       </c>
       <c r="E29">
-        <v>-759.284181102188</v>
+        <v>-724.1706991692813</v>
       </c>
       <c r="F29">
-        <v>948.0640121884807</v>
+        <v>983.1774941213873</v>
       </c>
       <c r="G29">
         <v>153</v>
@@ -3668,28 +3668,28 @@
         <v>425.55</v>
       </c>
       <c r="M29">
-        <v>57.10816847374156</v>
+        <v>59.22328582462088</v>
       </c>
       <c r="N29">
-        <v>368.4418315262585</v>
+        <v>366.3267141753792</v>
       </c>
       <c r="O29">
-        <v>46.05522894078231</v>
+        <v>45.79083927192239</v>
       </c>
       <c r="P29">
-        <v>322.3866025854762</v>
+        <v>320.5358749034568</v>
       </c>
       <c r="Q29">
-        <v>349.0866025854762</v>
+        <v>347.2358749034568</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1123343882362042</v>
+        <v>0.1131712085568407</v>
       </c>
       <c r="T29">
-        <v>1.29687906711532</v>
+        <v>1.313190252737368</v>
       </c>
       <c r="U29">
         <v>0.0602366166625341</v>
@@ -3706,7 +3706,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>7.45164853598253</v>
+        <v>7.185518231126012</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,22 +3714,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09624124124324612</v>
+        <v>0.09624747838753951</v>
       </c>
       <c r="C30">
-        <v>2794.267076452096</v>
+        <v>2758.852953957949</v>
       </c>
       <c r="D30">
-        <v>3624.444570573484</v>
+        <v>3624.143930012243</v>
       </c>
       <c r="E30">
-        <v>-724.1706991692813</v>
+        <v>-689.0572172363745</v>
       </c>
       <c r="F30">
-        <v>983.1774941213873</v>
+        <v>1018.290976054294</v>
       </c>
       <c r="G30">
         <v>153</v>
@@ -3750,28 +3750,28 @@
         <v>425.55</v>
       </c>
       <c r="M30">
-        <v>59.22328582462088</v>
+        <v>61.3384031755002</v>
       </c>
       <c r="N30">
-        <v>366.3267141753792</v>
+        <v>364.2115968244998</v>
       </c>
       <c r="O30">
-        <v>45.79083927192239</v>
+        <v>45.52644960306247</v>
       </c>
       <c r="P30">
-        <v>320.5358749034568</v>
+        <v>318.6851472214373</v>
       </c>
       <c r="Q30">
-        <v>347.2358749034568</v>
+        <v>345.3851472214373</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1131712085568407</v>
+        <v>0.1140316012808753</v>
       </c>
       <c r="T30">
-        <v>1.313190252737368</v>
+        <v>1.329960908376939</v>
       </c>
       <c r="U30">
         <v>0.0602366166625341</v>
@@ -3788,7 +3788,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.185518231126012</v>
+        <v>6.937741740397527</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,22 +3796,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09624747838753951</v>
+        <v>0.09625371553183287</v>
       </c>
       <c r="C31">
-        <v>2758.852953957949</v>
+        <v>2723.438881334755</v>
       </c>
       <c r="D31">
-        <v>3624.143930012243</v>
+        <v>3623.843339321956</v>
       </c>
       <c r="E31">
-        <v>-689.0572172363748</v>
+        <v>-653.943735303468</v>
       </c>
       <c r="F31">
-        <v>1018.290976054294</v>
+        <v>1053.404457987201</v>
       </c>
       <c r="G31">
         <v>153</v>
@@ -3832,28 +3832,28 @@
         <v>425.55</v>
       </c>
       <c r="M31">
-        <v>61.33840317550019</v>
+        <v>63.45352052637951</v>
       </c>
       <c r="N31">
-        <v>364.2115968244998</v>
+        <v>362.0964794736205</v>
       </c>
       <c r="O31">
-        <v>45.52644960306247</v>
+        <v>45.26205993420256</v>
       </c>
       <c r="P31">
-        <v>318.6851472214373</v>
+        <v>316.8344195394179</v>
       </c>
       <c r="Q31">
-        <v>345.3851472214373</v>
+        <v>343.5344195394179</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1140316012808753</v>
+        <v>0.1149165766541681</v>
       </c>
       <c r="T31">
-        <v>1.329960908376939</v>
+        <v>1.347210725606212</v>
       </c>
       <c r="U31">
         <v>0.0602366166625341</v>
@@ -3870,7 +3870,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.937741740397529</v>
+        <v>6.706483682384278</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,22 +3878,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09625371553183287</v>
+        <v>0.09625995267612628</v>
       </c>
       <c r="C32">
-        <v>2723.438881334755</v>
+        <v>2688.024858570103</v>
       </c>
       <c r="D32">
-        <v>3623.843339321956</v>
+        <v>3623.54279849021</v>
       </c>
       <c r="E32">
-        <v>-653.943735303468</v>
+        <v>-618.8302533705612</v>
       </c>
       <c r="F32">
-        <v>1053.404457987201</v>
+        <v>1088.517939920107</v>
       </c>
       <c r="G32">
         <v>153</v>
@@ -3914,28 +3914,28 @@
         <v>425.55</v>
       </c>
       <c r="M32">
-        <v>63.45352052637951</v>
+        <v>65.56863787725884</v>
       </c>
       <c r="N32">
-        <v>362.0964794736205</v>
+        <v>359.9813621227412</v>
       </c>
       <c r="O32">
-        <v>45.26205993420256</v>
+        <v>44.99767026534265</v>
       </c>
       <c r="P32">
-        <v>316.8344195394179</v>
+        <v>314.9836918573985</v>
       </c>
       <c r="Q32">
-        <v>343.5344195394179</v>
+        <v>341.6836918573985</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1149165766541681</v>
+        <v>0.1158272034875564</v>
       </c>
       <c r="T32">
-        <v>1.347210725606212</v>
+        <v>1.364960537537782</v>
       </c>
       <c r="U32">
         <v>0.0602366166625341</v>
@@ -3952,7 +3952,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.706483682384278</v>
+        <v>6.490145499081558</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,22 +3960,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09625995267612628</v>
+        <v>0.09626618982041966</v>
       </c>
       <c r="C33">
-        <v>2688.024858570103</v>
+        <v>2652.610885651591</v>
       </c>
       <c r="D33">
-        <v>3623.54279849021</v>
+        <v>3623.242307504605</v>
       </c>
       <c r="E33">
-        <v>-618.8302533705612</v>
+        <v>-583.7167714376546</v>
       </c>
       <c r="F33">
-        <v>1088.517939920107</v>
+        <v>1123.631421853014</v>
       </c>
       <c r="G33">
         <v>153</v>
@@ -3996,28 +3996,28 @@
         <v>425.55</v>
       </c>
       <c r="M33">
-        <v>65.56863787725884</v>
+        <v>67.68375522813814</v>
       </c>
       <c r="N33">
-        <v>359.9813621227412</v>
+        <v>357.8662447718619</v>
       </c>
       <c r="O33">
-        <v>44.99767026534265</v>
+        <v>44.73328059648274</v>
       </c>
       <c r="P33">
-        <v>314.9836918573985</v>
+        <v>313.1329641753791</v>
       </c>
       <c r="Q33">
-        <v>341.6836918573985</v>
+        <v>339.8329641753791</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1158272034875564</v>
+        <v>0.1167646134631031</v>
       </c>
       <c r="T33">
-        <v>1.364960537537782</v>
+        <v>1.383232402761458</v>
       </c>
       <c r="U33">
         <v>0.0602366166625341</v>
@@ -4034,7 +4034,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.490145499081558</v>
+        <v>6.287328452235261</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,22 +4042,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09626618982041966</v>
+        <v>0.09656117696471303</v>
       </c>
       <c r="C34">
-        <v>2652.610885651591</v>
+        <v>2603.342310681721</v>
       </c>
       <c r="D34">
-        <v>3623.242307504605</v>
+        <v>3609.087214467642</v>
       </c>
       <c r="E34">
-        <v>-583.7167714376546</v>
+        <v>-548.6032895047479</v>
       </c>
       <c r="F34">
-        <v>1123.631421853014</v>
+        <v>1158.744903785921</v>
       </c>
       <c r="G34">
         <v>153</v>
@@ -4078,45 +4078,45 @@
         <v>425.55</v>
       </c>
       <c r="M34">
-        <v>67.68375522813814</v>
+        <v>70.95761748280339</v>
       </c>
       <c r="N34">
-        <v>357.8662447718619</v>
+        <v>354.5923825171966</v>
       </c>
       <c r="O34">
-        <v>44.73328059648274</v>
+        <v>44.32404781464957</v>
       </c>
       <c r="P34">
-        <v>313.1329641753791</v>
+        <v>310.268334702547</v>
       </c>
       <c r="Q34">
-        <v>339.8329641753791</v>
+        <v>336.968334702547</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1167646134631031</v>
+        <v>0.1177300058259796</v>
       </c>
       <c r="T34">
-        <v>1.383232402761458</v>
+        <v>1.402049696797781</v>
       </c>
       <c r="U34">
-        <v>0.0602366166625341</v>
+        <v>0.0612366166625341</v>
       </c>
       <c r="V34">
         <v>0.125</v>
       </c>
       <c r="W34">
-        <v>0.05270703957971733</v>
+        <v>0.05358203957971733</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y34">
-        <v>6.287328452235261</v>
+        <v>5.9972419466188</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,22 +4124,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09656117696471303</v>
+        <v>0.09657616410900642</v>
       </c>
       <c r="C35">
-        <v>2603.342310681721</v>
+        <v>2567.512615529953</v>
       </c>
       <c r="D35">
-        <v>3609.087214467642</v>
+        <v>3608.371001248781</v>
       </c>
       <c r="E35">
-        <v>-548.6032895047479</v>
+        <v>-513.4898075718411</v>
       </c>
       <c r="F35">
-        <v>1158.744903785921</v>
+        <v>1193.858385718828</v>
       </c>
       <c r="G35">
         <v>153</v>
@@ -4160,28 +4160,28 @@
         <v>425.55</v>
       </c>
       <c r="M35">
-        <v>70.95761748280339</v>
+        <v>73.10784831561561</v>
       </c>
       <c r="N35">
-        <v>354.5923825171966</v>
+        <v>352.4421516843844</v>
       </c>
       <c r="O35">
-        <v>44.32404781464957</v>
+        <v>44.05526896054805</v>
       </c>
       <c r="P35">
-        <v>310.268334702547</v>
+        <v>308.3868827238363</v>
       </c>
       <c r="Q35">
-        <v>336.968334702547</v>
+        <v>335.0868827238363</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1177300058259796</v>
+        <v>0.1187246525028826</v>
       </c>
       <c r="T35">
-        <v>1.402049696797781</v>
+        <v>1.421437211865507</v>
       </c>
       <c r="U35">
         <v>0.0612366166625341</v>
@@ -4198,7 +4198,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.9972419466188</v>
+        <v>5.8208524776006</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,22 +4206,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09657616410900642</v>
+        <v>0.09659115125329981</v>
       </c>
       <c r="C36">
-        <v>2567.512615529953</v>
+        <v>2531.683204582789</v>
       </c>
       <c r="D36">
-        <v>3608.371001248781</v>
+        <v>3607.655072234523</v>
       </c>
       <c r="E36">
-        <v>-513.4898075718411</v>
+        <v>-478.3763256389343</v>
       </c>
       <c r="F36">
-        <v>1193.858385718828</v>
+        <v>1228.971867651734</v>
       </c>
       <c r="G36">
         <v>153</v>
@@ -4242,28 +4242,28 @@
         <v>425.55</v>
       </c>
       <c r="M36">
-        <v>73.10784831561561</v>
+        <v>75.25807914842784</v>
       </c>
       <c r="N36">
-        <v>352.4421516843844</v>
+        <v>350.2919208515722</v>
       </c>
       <c r="O36">
-        <v>44.05526896054805</v>
+        <v>43.78649010644652</v>
       </c>
       <c r="P36">
-        <v>308.3868827238363</v>
+        <v>306.5054307451256</v>
       </c>
       <c r="Q36">
-        <v>335.0868827238363</v>
+        <v>333.2054307451256</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1187246525028826</v>
+        <v>0.1197499036929212</v>
       </c>
       <c r="T36">
-        <v>1.421437211865507</v>
+        <v>1.441421265858394</v>
       </c>
       <c r="U36">
         <v>0.0612366166625341</v>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.8208524776006</v>
+        <v>5.654542406812012</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,22 +4288,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09659115125329981</v>
+        <v>0.09660613839759317</v>
       </c>
       <c r="C37">
-        <v>2531.683204582789</v>
+        <v>2495.854077671098</v>
       </c>
       <c r="D37">
-        <v>3607.655072234523</v>
+        <v>3606.939427255739</v>
       </c>
       <c r="E37">
-        <v>-478.3763256389343</v>
+        <v>-443.2628437060278</v>
       </c>
       <c r="F37">
-        <v>1228.971867651734</v>
+        <v>1264.085349584641</v>
       </c>
       <c r="G37">
         <v>153</v>
@@ -4324,28 +4324,28 @@
         <v>425.55</v>
       </c>
       <c r="M37">
-        <v>75.25807914842784</v>
+        <v>77.40830998124007</v>
       </c>
       <c r="N37">
-        <v>350.2919208515722</v>
+        <v>348.14169001876</v>
       </c>
       <c r="O37">
-        <v>43.78649010644652</v>
+        <v>43.51771125234499</v>
       </c>
       <c r="P37">
-        <v>306.5054307451256</v>
+        <v>304.623978766415</v>
       </c>
       <c r="Q37">
-        <v>333.2054307451256</v>
+        <v>331.3239787664149</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1197499036929212</v>
+        <v>0.1208071939826484</v>
       </c>
       <c r="T37">
-        <v>1.441421265858394</v>
+        <v>1.462029821538559</v>
       </c>
       <c r="U37">
         <v>0.0612366166625341</v>
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.654542406812012</v>
+        <v>5.497471784400567</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,22 +4370,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09660613839759319</v>
+        <v>0.09662112554188658</v>
       </c>
       <c r="C38">
-        <v>2495.854077671097</v>
+        <v>2460.025234625878</v>
       </c>
       <c r="D38">
-        <v>3606.939427255738</v>
+        <v>3606.224066143425</v>
       </c>
       <c r="E38">
-        <v>-443.262843706028</v>
+        <v>-408.1493617731212</v>
       </c>
       <c r="F38">
-        <v>1264.085349584641</v>
+        <v>1299.198831517547</v>
       </c>
       <c r="G38">
         <v>153</v>
@@ -4406,28 +4406,28 @@
         <v>425.55</v>
       </c>
       <c r="M38">
-        <v>77.40830998124005</v>
+        <v>79.55854081405228</v>
       </c>
       <c r="N38">
-        <v>348.14169001876</v>
+        <v>345.9914591859477</v>
       </c>
       <c r="O38">
-        <v>43.51771125234499</v>
+        <v>43.24893239824347</v>
       </c>
       <c r="P38">
-        <v>304.623978766415</v>
+        <v>302.7425267877043</v>
       </c>
       <c r="Q38">
-        <v>331.3239787664149</v>
+        <v>329.4425267877043</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1208071939826484</v>
+        <v>0.121898049043478</v>
       </c>
       <c r="T38">
-        <v>1.462029821538559</v>
+        <v>1.483292617081587</v>
       </c>
       <c r="U38">
         <v>0.0612366166625341</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.497471784400568</v>
+        <v>5.348891465903255</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,22 +4452,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09662112554188658</v>
+        <v>0.09663611268617996</v>
       </c>
       <c r="C39">
-        <v>2460.025234625878</v>
+        <v>2424.196675278268</v>
       </c>
       <c r="D39">
-        <v>3606.224066143425</v>
+        <v>3605.508988728723</v>
       </c>
       <c r="E39">
-        <v>-408.1493617731212</v>
+        <v>-373.0358798402144</v>
       </c>
       <c r="F39">
-        <v>1299.198831517547</v>
+        <v>1334.312313450454</v>
       </c>
       <c r="G39">
         <v>153</v>
@@ -4488,28 +4488,28 @@
         <v>425.55</v>
       </c>
       <c r="M39">
-        <v>79.55854081405228</v>
+        <v>81.70877164686451</v>
       </c>
       <c r="N39">
-        <v>345.9914591859477</v>
+        <v>343.8412283531355</v>
       </c>
       <c r="O39">
-        <v>43.24893239824347</v>
+        <v>42.98015354414194</v>
       </c>
       <c r="P39">
-        <v>302.7425267877043</v>
+        <v>300.8610748089936</v>
       </c>
       <c r="Q39">
-        <v>329.4425267877043</v>
+        <v>327.5610748089936</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.121898049043478</v>
+        <v>0.1230240929772377</v>
       </c>
       <c r="T39">
-        <v>1.483292617081587</v>
+        <v>1.505241309255034</v>
       </c>
       <c r="U39">
         <v>0.0612366166625341</v>
@@ -4526,7 +4526,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.348891465903255</v>
+        <v>5.208131164168958</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,22 +4534,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09663611268617996</v>
+        <v>0.09665109983047335</v>
       </c>
       <c r="C40">
-        <v>2424.196675278268</v>
+        <v>2388.36839945954</v>
       </c>
       <c r="D40">
-        <v>3605.508988728723</v>
+        <v>3604.794194842902</v>
       </c>
       <c r="E40">
-        <v>-373.0358798402144</v>
+        <v>-337.9223979073076</v>
       </c>
       <c r="F40">
-        <v>1334.312313450454</v>
+        <v>1369.425795383361</v>
       </c>
       <c r="G40">
         <v>153</v>
@@ -4570,28 +4570,28 @@
         <v>425.55</v>
       </c>
       <c r="M40">
-        <v>81.70877164686451</v>
+        <v>83.85900247967673</v>
       </c>
       <c r="N40">
-        <v>343.8412283531355</v>
+        <v>341.6909975203233</v>
       </c>
       <c r="O40">
-        <v>42.98015354414194</v>
+        <v>42.71137469004041</v>
       </c>
       <c r="P40">
-        <v>300.8610748089936</v>
+        <v>298.9796228302828</v>
       </c>
       <c r="Q40">
-        <v>327.5610748089936</v>
+        <v>325.6796228302828</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1230240929772377</v>
+        <v>0.1241870563842354</v>
       </c>
       <c r="T40">
-        <v>1.505241309255034</v>
+        <v>1.52790963068007</v>
       </c>
       <c r="U40">
         <v>0.0612366166625341</v>
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.208131164168958</v>
+        <v>5.074589339446677</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,22 +4616,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09665109983047335</v>
+        <v>0.09666608697476675</v>
       </c>
       <c r="C41">
-        <v>2388.36839945954</v>
+        <v>2352.540407001095</v>
       </c>
       <c r="D41">
-        <v>3604.794194842902</v>
+        <v>3604.079684317363</v>
       </c>
       <c r="E41">
-        <v>-337.9223979073076</v>
+        <v>-302.8089159744011</v>
       </c>
       <c r="F41">
-        <v>1369.425795383361</v>
+        <v>1404.539277316268</v>
       </c>
       <c r="G41">
         <v>153</v>
@@ -4652,28 +4652,28 @@
         <v>425.55</v>
       </c>
       <c r="M41">
-        <v>83.85900247967673</v>
+        <v>86.00923331248894</v>
       </c>
       <c r="N41">
-        <v>341.6909975203233</v>
+        <v>339.5407666875111</v>
       </c>
       <c r="O41">
-        <v>42.71137469004041</v>
+        <v>42.44259583593888</v>
       </c>
       <c r="P41">
-        <v>298.9796228302828</v>
+        <v>297.0981708515721</v>
       </c>
       <c r="Q41">
-        <v>325.6796228302828</v>
+        <v>323.7981708515721</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1241870563842354</v>
+        <v>0.125388785238133</v>
       </c>
       <c r="T41">
-        <v>1.52790963068007</v>
+        <v>1.551333562819274</v>
       </c>
       <c r="U41">
         <v>0.0612366166625341</v>
@@ -4690,7 +4690,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.074589339446677</v>
+        <v>4.947724605960511</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,22 +4698,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09666608697476675</v>
+        <v>0.09668107411906011</v>
       </c>
       <c r="C42">
-        <v>2352.540407001095</v>
+        <v>2316.712697734476</v>
       </c>
       <c r="D42">
-        <v>3604.079684317363</v>
+        <v>3603.365456983651</v>
       </c>
       <c r="E42">
-        <v>-302.8089159744011</v>
+        <v>-267.6954340414943</v>
       </c>
       <c r="F42">
-        <v>1404.539277316268</v>
+        <v>1439.652759249174</v>
       </c>
       <c r="G42">
         <v>153</v>
@@ -4734,28 +4734,28 @@
         <v>425.55</v>
       </c>
       <c r="M42">
-        <v>86.00923331248894</v>
+        <v>88.15946414530117</v>
       </c>
       <c r="N42">
-        <v>339.5407666875111</v>
+        <v>337.3905358546988</v>
       </c>
       <c r="O42">
-        <v>42.44259583593888</v>
+        <v>42.17381698183735</v>
       </c>
       <c r="P42">
-        <v>297.0981708515721</v>
+        <v>295.2167188728615</v>
       </c>
       <c r="Q42">
-        <v>323.7981708515721</v>
+        <v>321.9167188728615</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.125388785238133</v>
+        <v>0.1266312506633492</v>
       </c>
       <c r="T42">
-        <v>1.551333562819274</v>
+        <v>1.575551526556417</v>
       </c>
       <c r="U42">
         <v>0.0612366166625341</v>
@@ -4772,7 +4772,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.947724605960511</v>
+        <v>4.827048396059035</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,22 +4780,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09668107411906011</v>
+        <v>0.09669606126335351</v>
       </c>
       <c r="C43">
-        <v>2316.712697734476</v>
+        <v>2280.88527149135</v>
       </c>
       <c r="D43">
-        <v>3603.365456983651</v>
+        <v>3602.651512673431</v>
       </c>
       <c r="E43">
-        <v>-267.6954340414943</v>
+        <v>-232.5819521085875</v>
       </c>
       <c r="F43">
-        <v>1439.652759249174</v>
+        <v>1474.766241182081</v>
       </c>
       <c r="G43">
         <v>153</v>
@@ -4816,28 +4816,28 @@
         <v>425.55</v>
       </c>
       <c r="M43">
-        <v>88.15946414530117</v>
+        <v>90.30969497811341</v>
       </c>
       <c r="N43">
-        <v>337.3905358546988</v>
+        <v>335.2403050218866</v>
       </c>
       <c r="O43">
-        <v>42.17381698183735</v>
+        <v>41.90503812773582</v>
       </c>
       <c r="P43">
-        <v>295.2167188728615</v>
+        <v>293.3352668941508</v>
       </c>
       <c r="Q43">
-        <v>321.9167188728615</v>
+        <v>320.0352668941508</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1266312506633492</v>
+        <v>0.1279165597239176</v>
       </c>
       <c r="T43">
-        <v>1.575551526556417</v>
+        <v>1.600604592491393</v>
       </c>
       <c r="U43">
         <v>0.0612366166625341</v>
@@ -4854,7 +4854,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.827048396059035</v>
+        <v>4.712118672343342</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,22 +4862,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09669606126335351</v>
+        <v>0.09671104840764688</v>
       </c>
       <c r="C44">
-        <v>2280.88527149135</v>
+        <v>2245.058128103522</v>
       </c>
       <c r="D44">
-        <v>3602.651512673431</v>
+        <v>3601.93785121851</v>
       </c>
       <c r="E44">
-        <v>-232.5819521085878</v>
+        <v>-197.468470175681</v>
       </c>
       <c r="F44">
-        <v>1474.766241182081</v>
+        <v>1509.879723114988</v>
       </c>
       <c r="G44">
         <v>153</v>
@@ -4898,28 +4898,28 @@
         <v>425.55</v>
       </c>
       <c r="M44">
-        <v>90.3096949781134</v>
+        <v>92.45992581092563</v>
       </c>
       <c r="N44">
-        <v>335.2403050218866</v>
+        <v>333.0900741890744</v>
       </c>
       <c r="O44">
-        <v>41.90503812773583</v>
+        <v>41.63625927363429</v>
       </c>
       <c r="P44">
-        <v>293.3352668941508</v>
+        <v>291.45381491544</v>
       </c>
       <c r="Q44">
-        <v>320.0352668941508</v>
+        <v>318.15381491544</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1279165597239176</v>
+        <v>0.1292469673480148</v>
       </c>
       <c r="T44">
-        <v>1.600604592491393</v>
+        <v>1.626536713371455</v>
       </c>
       <c r="U44">
         <v>0.0612366166625341</v>
@@ -4936,7 +4936,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.712118672343344</v>
+        <v>4.602534517172567</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,22 +4944,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09671104840764688</v>
+        <v>0.09768853555194028</v>
       </c>
       <c r="C45">
-        <v>2245.058128103522</v>
+        <v>2164.001236225035</v>
       </c>
       <c r="D45">
-        <v>3601.93785121851</v>
+        <v>3555.994441272929</v>
       </c>
       <c r="E45">
-        <v>-197.468470175681</v>
+        <v>-162.3549882427744</v>
       </c>
       <c r="F45">
-        <v>1509.879723114988</v>
+        <v>1544.993205047894</v>
       </c>
       <c r="G45">
         <v>153</v>
@@ -4980,45 +4980,45 @@
         <v>425.55</v>
       </c>
       <c r="M45">
-        <v>92.45992581092563</v>
+        <v>98.47263965635757</v>
       </c>
       <c r="N45">
-        <v>333.0900741890744</v>
+        <v>327.0773603436425</v>
       </c>
       <c r="O45">
-        <v>41.63625927363429</v>
+        <v>40.88467004295531</v>
       </c>
       <c r="P45">
-        <v>291.45381491544</v>
+        <v>286.1926903006872</v>
       </c>
       <c r="Q45">
-        <v>318.15381491544</v>
+        <v>312.8926903006871</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1292469673480148</v>
+        <v>0.1306248895301154</v>
       </c>
       <c r="T45">
-        <v>1.626536713371455</v>
+        <v>1.653394981425805</v>
       </c>
       <c r="U45">
-        <v>0.0612366166625341</v>
+        <v>0.06373661666253409</v>
       </c>
       <c r="V45">
         <v>0.125</v>
       </c>
       <c r="W45">
-        <v>0.05358203957971733</v>
+        <v>0.05576953957971733</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y45">
-        <v>4.602534517172567</v>
+        <v>4.321504952899125</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,22 +5026,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09768853555194028</v>
+        <v>0.09772539769623365</v>
       </c>
       <c r="C46">
-        <v>2164.001236225035</v>
+        <v>2127.178098139917</v>
       </c>
       <c r="D46">
-        <v>3555.994441272929</v>
+        <v>3554.284785120718</v>
       </c>
       <c r="E46">
-        <v>-162.3549882427744</v>
+        <v>-127.2415063098676</v>
       </c>
       <c r="F46">
-        <v>1544.993205047894</v>
+        <v>1580.106686980801</v>
       </c>
       <c r="G46">
         <v>153</v>
@@ -5062,28 +5062,28 @@
         <v>425.55</v>
       </c>
       <c r="M46">
-        <v>98.47263965635757</v>
+        <v>100.7106541940021</v>
       </c>
       <c r="N46">
-        <v>327.0773603436425</v>
+        <v>324.8393458059979</v>
       </c>
       <c r="O46">
-        <v>40.88467004295531</v>
+        <v>40.60491822574974</v>
       </c>
       <c r="P46">
-        <v>286.1926903006872</v>
+        <v>284.2344275802482</v>
       </c>
       <c r="Q46">
-        <v>312.8926903006871</v>
+        <v>310.9344275802482</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1306248895301154</v>
+        <v>0.1320529179733834</v>
       </c>
       <c r="T46">
-        <v>1.653394981425805</v>
+        <v>1.681229913773041</v>
       </c>
       <c r="U46">
         <v>0.06373661666253409</v>
@@ -5100,7 +5100,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.321504952899125</v>
+        <v>4.225471509501366</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,22 +5108,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09772539769623365</v>
+        <v>0.09776225984052705</v>
       </c>
       <c r="C47">
-        <v>2127.178098139917</v>
+        <v>2090.356603206717</v>
       </c>
       <c r="D47">
-        <v>3554.284785120718</v>
+        <v>3552.576772120425</v>
       </c>
       <c r="E47">
-        <v>-127.2415063098676</v>
+        <v>-92.12802437696087</v>
       </c>
       <c r="F47">
-        <v>1580.106686980801</v>
+        <v>1615.220168913708</v>
       </c>
       <c r="G47">
         <v>153</v>
@@ -5144,28 +5144,28 @@
         <v>425.55</v>
       </c>
       <c r="M47">
-        <v>100.7106541940021</v>
+        <v>102.9486687316466</v>
       </c>
       <c r="N47">
-        <v>324.8393458059979</v>
+        <v>322.6013312683534</v>
       </c>
       <c r="O47">
-        <v>40.60491822574974</v>
+        <v>40.32516640854418</v>
       </c>
       <c r="P47">
-        <v>284.2344275802482</v>
+        <v>282.2761648598092</v>
       </c>
       <c r="Q47">
-        <v>310.9344275802482</v>
+        <v>308.9761648598092</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1320529179733834</v>
+        <v>0.1335338363589946</v>
       </c>
       <c r="T47">
-        <v>1.681229913773041</v>
+        <v>1.710095769540545</v>
       </c>
       <c r="U47">
         <v>0.06373661666253409</v>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.225471509501366</v>
+        <v>4.133613433207858</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,22 +5190,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09776225984052705</v>
+        <v>0.09779912198482042</v>
       </c>
       <c r="C48">
-        <v>2090.356603206717</v>
+        <v>2053.536749057726</v>
       </c>
       <c r="D48">
-        <v>3552.576772120425</v>
+        <v>3550.87039990434</v>
       </c>
       <c r="E48">
-        <v>-92.12802437696087</v>
+        <v>-57.01454244405409</v>
       </c>
       <c r="F48">
-        <v>1615.220168913708</v>
+        <v>1650.333650846615</v>
       </c>
       <c r="G48">
         <v>153</v>
@@ -5226,28 +5226,28 @@
         <v>425.55</v>
       </c>
       <c r="M48">
-        <v>102.9486687316466</v>
+        <v>105.1866832692911</v>
       </c>
       <c r="N48">
-        <v>322.6013312683534</v>
+        <v>320.363316730709</v>
       </c>
       <c r="O48">
-        <v>40.32516640854418</v>
+        <v>40.04541459133862</v>
       </c>
       <c r="P48">
-        <v>282.2761648598092</v>
+        <v>280.3179021393703</v>
       </c>
       <c r="Q48">
-        <v>308.9761648598092</v>
+        <v>307.0179021393703</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1335338363589946</v>
+        <v>0.1350706384572703</v>
       </c>
       <c r="T48">
-        <v>1.710095769540545</v>
+        <v>1.740050902884181</v>
       </c>
       <c r="U48">
         <v>0.06373661666253409</v>
@@ -5264,7 +5264,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.133613433207858</v>
+        <v>4.045664211224713</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,22 +5272,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09779912198482042</v>
+        <v>0.09930598412911382</v>
       </c>
       <c r="C49">
-        <v>2053.536749057726</v>
+        <v>1950.045728759709</v>
       </c>
       <c r="D49">
-        <v>3550.87039990434</v>
+        <v>3482.49286153923</v>
       </c>
       <c r="E49">
-        <v>-57.01454244405409</v>
+        <v>-21.90106051114753</v>
       </c>
       <c r="F49">
-        <v>1650.333650846615</v>
+        <v>1685.447132779521</v>
       </c>
       <c r="G49">
         <v>153</v>
@@ -5308,45 +5308,45 @@
         <v>425.55</v>
       </c>
       <c r="M49">
-        <v>105.1866832692911</v>
+        <v>113.3237627716639</v>
       </c>
       <c r="N49">
-        <v>320.363316730709</v>
+        <v>312.2262372283361</v>
       </c>
       <c r="O49">
-        <v>40.04541459133862</v>
+        <v>39.02827965354201</v>
       </c>
       <c r="P49">
-        <v>280.3179021393703</v>
+        <v>273.1979575747941</v>
       </c>
       <c r="Q49">
-        <v>307.0179021393703</v>
+        <v>299.8979575747941</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1350706384572703</v>
+        <v>0.1366665483285567</v>
       </c>
       <c r="T49">
-        <v>1.740050902884181</v>
+        <v>1.771158156741033</v>
       </c>
       <c r="U49">
-        <v>0.06373661666253409</v>
+        <v>0.0672366166625341</v>
       </c>
       <c r="V49">
         <v>0.125</v>
       </c>
       <c r="W49">
-        <v>0.05576953957971733</v>
+        <v>0.05883203957971733</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.045664211224713</v>
+        <v>3.755170050763678</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,22 +5354,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09930598412911379</v>
+        <v>0.09937347127340718</v>
       </c>
       <c r="C50">
-        <v>1950.04572875971</v>
+        <v>1911.931412529936</v>
       </c>
       <c r="D50">
-        <v>3482.492861539231</v>
+        <v>3479.492027242363</v>
       </c>
       <c r="E50">
-        <v>-21.90106051114753</v>
+        <v>13.21242142175902</v>
       </c>
       <c r="F50">
-        <v>1685.447132779521</v>
+        <v>1720.560614712428</v>
       </c>
       <c r="G50">
         <v>153</v>
@@ -5390,28 +5390,28 @@
         <v>425.55</v>
       </c>
       <c r="M50">
-        <v>113.3237627716639</v>
+        <v>115.6846744960735</v>
       </c>
       <c r="N50">
-        <v>312.2262372283361</v>
+        <v>309.8653255039265</v>
       </c>
       <c r="O50">
-        <v>39.02827965354201</v>
+        <v>38.73316568799081</v>
       </c>
       <c r="P50">
-        <v>273.1979575747941</v>
+        <v>271.1321598159357</v>
       </c>
       <c r="Q50">
-        <v>299.8979575747941</v>
+        <v>297.8321598159357</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1366665483285567</v>
+        <v>0.1383250429006778</v>
       </c>
       <c r="T50">
-        <v>1.771158156741033</v>
+        <v>1.803485302905998</v>
       </c>
       <c r="U50">
         <v>0.0672366166625341</v>
@@ -5428,7 +5428,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.755170050763678</v>
+        <v>3.678533927278705</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,22 +5436,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09937347127340718</v>
+        <v>0.09944095841770058</v>
       </c>
       <c r="C51">
-        <v>1911.931412529936</v>
+        <v>1873.822263434152</v>
       </c>
       <c r="D51">
-        <v>3479.492027242363</v>
+        <v>3476.496360079486</v>
       </c>
       <c r="E51">
-        <v>13.21242142175902</v>
+        <v>48.3259033546658</v>
       </c>
       <c r="F51">
-        <v>1720.560614712428</v>
+        <v>1755.674096645334</v>
       </c>
       <c r="G51">
         <v>153</v>
@@ -5472,28 +5472,28 @@
         <v>425.55</v>
       </c>
       <c r="M51">
-        <v>115.6846744960735</v>
+        <v>118.0455862204832</v>
       </c>
       <c r="N51">
-        <v>309.8653255039265</v>
+        <v>307.5044137795168</v>
       </c>
       <c r="O51">
-        <v>38.73316568799081</v>
+        <v>38.4380517224396</v>
       </c>
       <c r="P51">
-        <v>271.1321598159357</v>
+        <v>269.0663620570772</v>
       </c>
       <c r="Q51">
-        <v>297.8321598159357</v>
+        <v>295.7663620570772</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1383250429006778</v>
+        <v>0.1400498772556838</v>
       </c>
       <c r="T51">
-        <v>1.803485302905998</v>
+        <v>1.837105534917561</v>
       </c>
       <c r="U51">
         <v>0.0672366166625341</v>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.678533927278705</v>
+        <v>3.604963248733131</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,22 +5518,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09944095841770058</v>
+        <v>0.09950844556199397</v>
       </c>
       <c r="C52">
-        <v>1873.822263434152</v>
+        <v>1835.718268137916</v>
       </c>
       <c r="D52">
-        <v>3476.496360079486</v>
+        <v>3473.505846716157</v>
       </c>
       <c r="E52">
-        <v>48.3259033546658</v>
+        <v>83.43938528757258</v>
       </c>
       <c r="F52">
-        <v>1755.674096645334</v>
+        <v>1790.787578578241</v>
       </c>
       <c r="G52">
         <v>153</v>
@@ -5554,28 +5554,28 @@
         <v>425.55</v>
       </c>
       <c r="M52">
-        <v>118.0455862204832</v>
+        <v>120.4064979448929</v>
       </c>
       <c r="N52">
-        <v>307.5044137795168</v>
+        <v>305.1435020551071</v>
       </c>
       <c r="O52">
-        <v>38.4380517224396</v>
+        <v>38.14293775688839</v>
       </c>
       <c r="P52">
-        <v>269.0663620570772</v>
+        <v>267.0005642982188</v>
       </c>
       <c r="Q52">
-        <v>295.7663620570772</v>
+        <v>293.7005642982188</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1400498772556838</v>
+        <v>0.141845113012935</v>
       </c>
       <c r="T52">
-        <v>1.837105534917561</v>
+        <v>1.872098021296944</v>
       </c>
       <c r="U52">
         <v>0.0672366166625341</v>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.604963248733131</v>
+        <v>3.534277694836403</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,22 +5600,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09950844556199397</v>
+        <v>0.1008499327062874</v>
       </c>
       <c r="C53">
-        <v>1835.718268137916</v>
+        <v>1742.209974750729</v>
       </c>
       <c r="D53">
-        <v>3473.505846716157</v>
+        <v>3415.111035261877</v>
       </c>
       <c r="E53">
-        <v>83.43938528757258</v>
+        <v>118.5528672204791</v>
       </c>
       <c r="F53">
-        <v>1790.787578578241</v>
+        <v>1825.901060511148</v>
       </c>
       <c r="G53">
         <v>153</v>
@@ -5636,45 +5636,45 @@
         <v>425.55</v>
       </c>
       <c r="M53">
-        <v>120.4064979448929</v>
+        <v>127.8799326387337</v>
       </c>
       <c r="N53">
-        <v>305.1435020551071</v>
+        <v>297.6700673612663</v>
       </c>
       <c r="O53">
-        <v>38.14293775688839</v>
+        <v>37.20875842015829</v>
       </c>
       <c r="P53">
-        <v>267.0005642982188</v>
+        <v>260.461308941108</v>
       </c>
       <c r="Q53">
-        <v>293.7005642982188</v>
+        <v>287.161308941108</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.141845113012935</v>
+        <v>0.1437151502600715</v>
       </c>
       <c r="T53">
-        <v>1.872098021296944</v>
+        <v>1.908548527942133</v>
       </c>
       <c r="U53">
-        <v>0.0672366166625341</v>
+        <v>0.07003661666253409</v>
       </c>
       <c r="V53">
         <v>0.125</v>
       </c>
       <c r="W53">
-        <v>0.05883203957971733</v>
+        <v>0.06128203957971733</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.534277694836403</v>
+        <v>3.327730873945618</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,22 +5682,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1008499327062874</v>
+        <v>0.1009419198505807</v>
       </c>
       <c r="C54">
-        <v>1742.209974750729</v>
+        <v>1703.164150490133</v>
       </c>
       <c r="D54">
-        <v>3415.111035261877</v>
+        <v>3411.178692934188</v>
       </c>
       <c r="E54">
-        <v>118.5528672204791</v>
+        <v>153.6663491533859</v>
       </c>
       <c r="F54">
-        <v>1825.901060511148</v>
+        <v>1861.014542444055</v>
       </c>
       <c r="G54">
         <v>153</v>
@@ -5718,28 +5718,28 @@
         <v>425.55</v>
       </c>
       <c r="M54">
-        <v>127.8799326387337</v>
+        <v>130.3391621125555</v>
       </c>
       <c r="N54">
-        <v>297.6700673612663</v>
+        <v>295.2108378874445</v>
       </c>
       <c r="O54">
-        <v>37.20875842015829</v>
+        <v>36.90135473593056</v>
       </c>
       <c r="P54">
-        <v>260.461308941108</v>
+        <v>258.3094831515139</v>
       </c>
       <c r="Q54">
-        <v>287.161308941108</v>
+        <v>285.0094831515139</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1437151502600715</v>
+        <v>0.1456647635602777</v>
       </c>
       <c r="T54">
-        <v>1.908548527942133</v>
+        <v>1.94655011997648</v>
       </c>
       <c r="U54">
         <v>0.07003661666253409</v>
@@ -5756,7 +5756,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.327730873945618</v>
+        <v>3.264943498965511</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,22 +5764,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1009419198505807</v>
+        <v>0.1010339069948741</v>
       </c>
       <c r="C55">
-        <v>1703.164150490133</v>
+        <v>1664.127371634627</v>
       </c>
       <c r="D55">
-        <v>3411.178692934188</v>
+        <v>3407.255396011588</v>
       </c>
       <c r="E55">
-        <v>153.6663491533859</v>
+        <v>188.7798310862927</v>
       </c>
       <c r="F55">
-        <v>1861.014542444055</v>
+        <v>1896.128024376961</v>
       </c>
       <c r="G55">
         <v>153</v>
@@ -5800,28 +5800,28 @@
         <v>425.55</v>
       </c>
       <c r="M55">
-        <v>130.3391621125555</v>
+        <v>132.7983915863773</v>
       </c>
       <c r="N55">
-        <v>295.2108378874445</v>
+        <v>292.7516084136226</v>
       </c>
       <c r="O55">
-        <v>36.90135473593056</v>
+        <v>36.59395105170283</v>
       </c>
       <c r="P55">
-        <v>258.3094831515139</v>
+        <v>256.1576573619198</v>
       </c>
       <c r="Q55">
-        <v>285.0094831515139</v>
+        <v>282.8576573619198</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1456647635602777</v>
+        <v>0.1476991426561451</v>
       </c>
       <c r="T55">
-        <v>1.94655011997648</v>
+        <v>1.986203955142755</v>
       </c>
       <c r="U55">
         <v>0.07003661666253409</v>
@@ -5838,7 +5838,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.264943498965511</v>
+        <v>3.204481582318001</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,22 +5846,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1010339069948741</v>
+        <v>0.1011258941391675</v>
       </c>
       <c r="C56">
-        <v>1664.127371634627</v>
+        <v>1625.099607009902</v>
       </c>
       <c r="D56">
-        <v>3407.255396011588</v>
+        <v>3403.34111331977</v>
       </c>
       <c r="E56">
-        <v>188.7798310862927</v>
+        <v>223.8933130191995</v>
       </c>
       <c r="F56">
-        <v>1896.128024376961</v>
+        <v>1931.241506309868</v>
       </c>
       <c r="G56">
         <v>153</v>
@@ -5882,28 +5882,28 @@
         <v>425.55</v>
       </c>
       <c r="M56">
-        <v>132.7983915863773</v>
+        <v>135.2576210601991</v>
       </c>
       <c r="N56">
-        <v>292.7516084136226</v>
+        <v>290.2923789398009</v>
       </c>
       <c r="O56">
-        <v>36.59395105170283</v>
+        <v>36.28654736747511</v>
       </c>
       <c r="P56">
-        <v>256.1576573619198</v>
+        <v>254.0058315723257</v>
       </c>
       <c r="Q56">
-        <v>282.8576573619198</v>
+        <v>280.7058315723257</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1476991426561451</v>
+        <v>0.1498239386007177</v>
       </c>
       <c r="T56">
-        <v>1.986203955142755</v>
+        <v>2.027620182983087</v>
       </c>
       <c r="U56">
         <v>0.07003661666253409</v>
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.204481582318001</v>
+        <v>3.14621828082131</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,22 +5928,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1011258941391675</v>
+        <v>0.1012178812834609</v>
       </c>
       <c r="C57">
-        <v>1625.099607009902</v>
+        <v>1586.080825584746</v>
       </c>
       <c r="D57">
-        <v>3403.34111331977</v>
+        <v>3399.435813827521</v>
       </c>
       <c r="E57">
-        <v>223.8933130191995</v>
+        <v>259.006794952106</v>
       </c>
       <c r="F57">
-        <v>1931.241506309868</v>
+        <v>1966.354988242775</v>
       </c>
       <c r="G57">
         <v>153</v>
@@ -5964,28 +5964,28 @@
         <v>425.55</v>
       </c>
       <c r="M57">
-        <v>135.2576210601991</v>
+        <v>137.7168505340209</v>
       </c>
       <c r="N57">
-        <v>290.2923789398009</v>
+        <v>287.8331494659791</v>
       </c>
       <c r="O57">
-        <v>36.28654736747511</v>
+        <v>35.97914368324739</v>
       </c>
       <c r="P57">
-        <v>254.0058315723257</v>
+        <v>251.8540057827317</v>
       </c>
       <c r="Q57">
-        <v>280.7058315723257</v>
+        <v>278.5540057827317</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1498239386007177</v>
+        <v>0.1520453161791345</v>
       </c>
       <c r="T57">
-        <v>2.027620182983087</v>
+        <v>2.070918966634342</v>
       </c>
       <c r="U57">
         <v>0.07003661666253409</v>
@@ -6002,7 +6002,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.14621828082131</v>
+        <v>3.09003581152093</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,22 +6010,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1012178812834609</v>
+        <v>0.1013098684277543</v>
       </c>
       <c r="C58">
-        <v>1586.080825584746</v>
+        <v>1547.070996470211</v>
       </c>
       <c r="D58">
-        <v>3399.435813827521</v>
+        <v>3395.539466645892</v>
       </c>
       <c r="E58">
-        <v>259.006794952106</v>
+        <v>294.1202768850128</v>
       </c>
       <c r="F58">
-        <v>1966.354988242775</v>
+        <v>2001.468470175681</v>
       </c>
       <c r="G58">
         <v>153</v>
@@ -6046,28 +6046,28 @@
         <v>425.55</v>
       </c>
       <c r="M58">
-        <v>137.7168505340209</v>
+        <v>140.1760800078428</v>
       </c>
       <c r="N58">
-        <v>287.8331494659791</v>
+        <v>285.3739199921573</v>
       </c>
       <c r="O58">
-        <v>35.97914368324739</v>
+        <v>35.67173999901966</v>
       </c>
       <c r="P58">
-        <v>251.8540057827317</v>
+        <v>249.7021799931376</v>
       </c>
       <c r="Q58">
-        <v>278.5540057827317</v>
+        <v>276.4021799931376</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1520453161791345</v>
+        <v>0.1543700136449195</v>
       </c>
       <c r="T58">
-        <v>2.070918966634342</v>
+        <v>2.116231647199609</v>
       </c>
       <c r="U58">
         <v>0.07003661666253409</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.09003581152093</v>
+        <v>3.035824656932843</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,22 +6092,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1013098684277543</v>
+        <v>0.1053603555720477</v>
       </c>
       <c r="C59">
-        <v>1547.070996470211</v>
+        <v>1348.819126569166</v>
       </c>
       <c r="D59">
-        <v>3395.539466645892</v>
+        <v>3232.401078677754</v>
       </c>
       <c r="E59">
-        <v>294.1202768850128</v>
+        <v>329.2337588179196</v>
       </c>
       <c r="F59">
-        <v>2001.468470175681</v>
+        <v>2036.581952108588</v>
       </c>
       <c r="G59">
         <v>153</v>
@@ -6128,45 +6128,45 @@
         <v>425.55</v>
       </c>
       <c r="M59">
-        <v>140.1760800078428</v>
+        <v>158.5206487081116</v>
       </c>
       <c r="N59">
-        <v>285.3739199921573</v>
+        <v>267.0293512918885</v>
       </c>
       <c r="O59">
-        <v>35.67173999901966</v>
+        <v>33.37866891148606</v>
       </c>
       <c r="P59">
-        <v>249.7021799931376</v>
+        <v>233.6506823804024</v>
       </c>
       <c r="Q59">
-        <v>276.4021799931376</v>
+        <v>260.3506823804024</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1543700136449195</v>
+        <v>0.1568054109900276</v>
       </c>
       <c r="T59">
-        <v>2.116231647199609</v>
+        <v>2.163702074458462</v>
       </c>
       <c r="U59">
-        <v>0.07003661666253409</v>
+        <v>0.07783661666253411</v>
       </c>
       <c r="V59">
         <v>0.125</v>
       </c>
       <c r="W59">
-        <v>0.06128203957971733</v>
+        <v>0.06810703957971734</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.035824656932843</v>
+        <v>2.684508317800143</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,22 +6174,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1053603555720476</v>
+        <v>0.105520592716341</v>
       </c>
       <c r="C60">
-        <v>1348.819126569168</v>
+        <v>1307.57361980725</v>
       </c>
       <c r="D60">
-        <v>3232.401078677755</v>
+        <v>3226.269053848745</v>
       </c>
       <c r="E60">
-        <v>329.2337588179191</v>
+        <v>364.3472407508259</v>
       </c>
       <c r="F60">
-        <v>2036.581952108588</v>
+        <v>2071.695434041495</v>
       </c>
       <c r="G60">
         <v>153</v>
@@ -6210,28 +6210,28 @@
         <v>425.55</v>
       </c>
       <c r="M60">
-        <v>158.5206487081115</v>
+        <v>161.25376334101</v>
       </c>
       <c r="N60">
-        <v>267.0293512918885</v>
+        <v>264.29623665899</v>
       </c>
       <c r="O60">
-        <v>33.37866891148606</v>
+        <v>33.03702958237375</v>
       </c>
       <c r="P60">
-        <v>233.6506823804024</v>
+        <v>231.2592070766162</v>
       </c>
       <c r="Q60">
-        <v>260.3506823804024</v>
+        <v>257.9592070766162</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1568054109900276</v>
+        <v>0.1593596082056288</v>
       </c>
       <c r="T60">
-        <v>2.163702074458461</v>
+        <v>2.213488132315305</v>
       </c>
       <c r="U60">
         <v>0.07783661666253411</v>
@@ -6248,7 +6248,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.684508317800144</v>
+        <v>2.63900817682048</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,22 +6256,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.105520592716341</v>
+        <v>0.1056808298606344</v>
       </c>
       <c r="C61">
-        <v>1307.57361980725</v>
+        <v>1266.351334502272</v>
       </c>
       <c r="D61">
-        <v>3226.269053848745</v>
+        <v>3220.160250476673</v>
       </c>
       <c r="E61">
-        <v>364.3472407508259</v>
+        <v>399.4607226837327</v>
       </c>
       <c r="F61">
-        <v>2071.695434041495</v>
+        <v>2106.808915974401</v>
       </c>
       <c r="G61">
         <v>153</v>
@@ -6292,28 +6292,28 @@
         <v>425.55</v>
       </c>
       <c r="M61">
-        <v>161.25376334101</v>
+        <v>163.9868779739085</v>
       </c>
       <c r="N61">
-        <v>264.29623665899</v>
+        <v>261.5631220260915</v>
       </c>
       <c r="O61">
-        <v>33.03702958237375</v>
+        <v>32.69539025326144</v>
       </c>
       <c r="P61">
-        <v>231.2592070766162</v>
+        <v>228.86773177283</v>
       </c>
       <c r="Q61">
-        <v>257.9592070766162</v>
+        <v>255.56773177283</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1593596082056288</v>
+        <v>0.1620415152820101</v>
       </c>
       <c r="T61">
-        <v>2.213488132315305</v>
+        <v>2.265763493064993</v>
       </c>
       <c r="U61">
         <v>0.07783661666253411</v>
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.63900817682048</v>
+        <v>2.595024707206805</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,22 +6338,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1056808298606344</v>
+        <v>0.1058410670049278</v>
       </c>
       <c r="C62">
-        <v>1266.351334502272</v>
+        <v>1225.152138996993</v>
       </c>
       <c r="D62">
-        <v>3220.160250476673</v>
+        <v>3214.074536904302</v>
       </c>
       <c r="E62">
-        <v>399.4607226837327</v>
+        <v>434.5742046166395</v>
       </c>
       <c r="F62">
-        <v>2106.808915974401</v>
+        <v>2141.922397907308</v>
       </c>
       <c r="G62">
         <v>153</v>
@@ -6374,28 +6374,28 @@
         <v>425.55</v>
       </c>
       <c r="M62">
-        <v>163.9868779739085</v>
+        <v>166.719992606807</v>
       </c>
       <c r="N62">
-        <v>261.5631220260915</v>
+        <v>258.830007393193</v>
       </c>
       <c r="O62">
-        <v>32.69539025326144</v>
+        <v>32.35375092414913</v>
       </c>
       <c r="P62">
-        <v>228.86773177283</v>
+        <v>226.4762564690439</v>
       </c>
       <c r="Q62">
-        <v>255.56773177283</v>
+        <v>253.1762564690439</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1620415152820101</v>
+        <v>0.164860956054616</v>
       </c>
       <c r="T62">
-        <v>2.265763493064993</v>
+        <v>2.320719641545432</v>
       </c>
       <c r="U62">
         <v>0.07783661666253411</v>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.595024707206805</v>
+        <v>2.552483318564071</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,22 +6420,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1058410670049278</v>
+        <v>0.1060013041492212</v>
       </c>
       <c r="C63">
-        <v>1225.152138996993</v>
+        <v>1183.975902627564</v>
       </c>
       <c r="D63">
-        <v>3214.074536904302</v>
+        <v>3208.011782467779</v>
       </c>
       <c r="E63">
-        <v>434.5742046166395</v>
+        <v>469.6876865495462</v>
       </c>
       <c r="F63">
-        <v>2141.922397907308</v>
+        <v>2177.035879840215</v>
       </c>
       <c r="G63">
         <v>153</v>
@@ -6456,28 +6456,28 @@
         <v>425.55</v>
       </c>
       <c r="M63">
-        <v>166.719992606807</v>
+        <v>169.4531072397055</v>
       </c>
       <c r="N63">
-        <v>258.830007393193</v>
+        <v>256.0968927602945</v>
       </c>
       <c r="O63">
-        <v>32.35375092414913</v>
+        <v>32.01211159503681</v>
       </c>
       <c r="P63">
-        <v>226.4762564690439</v>
+        <v>224.0847811652577</v>
       </c>
       <c r="Q63">
-        <v>253.1762564690439</v>
+        <v>250.7847811652577</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.164860956054616</v>
+        <v>0.1678287884468327</v>
       </c>
       <c r="T63">
-        <v>2.320719641545432</v>
+        <v>2.378568218893264</v>
       </c>
       <c r="U63">
         <v>0.07783661666253411</v>
@@ -6494,7 +6494,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.552483318564071</v>
+        <v>2.511314232780779</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,22 +6502,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1060013041492212</v>
+        <v>0.1083114162935146</v>
       </c>
       <c r="C64">
-        <v>1183.975902627564</v>
+        <v>1063.931252964906</v>
       </c>
       <c r="D64">
-        <v>3208.011782467779</v>
+        <v>3123.080614738027</v>
       </c>
       <c r="E64">
-        <v>469.6876865495462</v>
+        <v>504.8011684824526</v>
       </c>
       <c r="F64">
-        <v>2177.035879840215</v>
+        <v>2212.149361773121</v>
       </c>
       <c r="G64">
         <v>153</v>
@@ -6538,45 +6538,45 @@
         <v>425.55</v>
       </c>
       <c r="M64">
-        <v>169.4531072397055</v>
+        <v>180.813604383519</v>
       </c>
       <c r="N64">
-        <v>256.0968927602945</v>
+        <v>244.736395616481</v>
       </c>
       <c r="O64">
-        <v>32.01211159503681</v>
+        <v>30.59204945206012</v>
       </c>
       <c r="P64">
-        <v>224.0847811652577</v>
+        <v>214.1443461644209</v>
       </c>
       <c r="Q64">
-        <v>250.7847811652577</v>
+        <v>240.8443461644208</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1678287884468327</v>
+        <v>0.1709570442116018</v>
       </c>
       <c r="T64">
-        <v>2.378568218893264</v>
+        <v>2.439543746368005</v>
       </c>
       <c r="U64">
-        <v>0.07783661666253411</v>
+        <v>0.0817366166625341</v>
       </c>
       <c r="V64">
         <v>0.125</v>
       </c>
       <c r="W64">
-        <v>0.06810703957971734</v>
+        <v>0.07151953957971734</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.511314232780779</v>
+        <v>2.35352865980912</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,22 +6584,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1083114162935146</v>
+        <v>0.108505778437808</v>
       </c>
       <c r="C65">
-        <v>1063.931252964906</v>
+        <v>1021.876697322748</v>
       </c>
       <c r="D65">
-        <v>3123.080614738027</v>
+        <v>3116.139541028776</v>
       </c>
       <c r="E65">
-        <v>504.8011684824526</v>
+        <v>539.9146504153593</v>
       </c>
       <c r="F65">
-        <v>2212.149361773121</v>
+        <v>2247.262843706028</v>
       </c>
       <c r="G65">
         <v>153</v>
@@ -6620,28 +6620,28 @@
         <v>425.55</v>
       </c>
       <c r="M65">
-        <v>180.813604383519</v>
+        <v>183.6836615959559</v>
       </c>
       <c r="N65">
-        <v>244.736395616481</v>
+        <v>241.8663384040441</v>
       </c>
       <c r="O65">
-        <v>30.59204945206012</v>
+        <v>30.23329230050552</v>
       </c>
       <c r="P65">
-        <v>214.1443461644209</v>
+        <v>211.6330461035386</v>
       </c>
       <c r="Q65">
-        <v>240.8443461644208</v>
+        <v>238.3330461035386</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1709570442116018</v>
+        <v>0.1742590919633024</v>
       </c>
       <c r="T65">
-        <v>2.439543746368005</v>
+        <v>2.503906803146899</v>
       </c>
       <c r="U65">
         <v>0.0817366166625341</v>
@@ -6658,7 +6658,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.35352865980912</v>
+        <v>2.316754774499603</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,22 +6666,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.108505778437808</v>
+        <v>0.1087001405821013</v>
       </c>
       <c r="C66">
-        <v>1021.876697322748</v>
+        <v>979.8529264540089</v>
       </c>
       <c r="D66">
-        <v>3116.139541028776</v>
+        <v>3109.229252092944</v>
       </c>
       <c r="E66">
-        <v>539.9146504153593</v>
+        <v>575.0281323482661</v>
       </c>
       <c r="F66">
-        <v>2247.262843706028</v>
+        <v>2282.376325638935</v>
       </c>
       <c r="G66">
         <v>153</v>
@@ -6702,28 +6702,28 @@
         <v>425.55</v>
       </c>
       <c r="M66">
-        <v>183.6836615959559</v>
+        <v>186.5537188083927</v>
       </c>
       <c r="N66">
-        <v>241.8663384040441</v>
+        <v>238.9962811916073</v>
       </c>
       <c r="O66">
-        <v>30.23329230050552</v>
+        <v>29.87453514895092</v>
       </c>
       <c r="P66">
-        <v>211.6330461035386</v>
+        <v>209.1217460426564</v>
       </c>
       <c r="Q66">
-        <v>238.3330461035386</v>
+        <v>235.8217460426564</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1742590919633024</v>
+        <v>0.1777498281579574</v>
       </c>
       <c r="T66">
-        <v>2.503906803146899</v>
+        <v>2.571947748884586</v>
       </c>
       <c r="U66">
         <v>0.0817366166625341</v>
@@ -6740,7 +6740,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.316754774499603</v>
+        <v>2.281112393353455</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,22 +6748,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1087001405821013</v>
+        <v>0.1088945027263947</v>
       </c>
       <c r="C67">
-        <v>979.8529264540089</v>
+        <v>937.859736008751</v>
       </c>
       <c r="D67">
-        <v>3109.229252092944</v>
+        <v>3102.349543580593</v>
       </c>
       <c r="E67">
-        <v>575.0281323482661</v>
+        <v>610.1416142811729</v>
       </c>
       <c r="F67">
-        <v>2282.376325638935</v>
+        <v>2317.489807571842</v>
       </c>
       <c r="G67">
         <v>153</v>
@@ -6784,28 +6784,28 @@
         <v>425.55</v>
       </c>
       <c r="M67">
-        <v>186.5537188083927</v>
+        <v>189.4237760208295</v>
       </c>
       <c r="N67">
-        <v>238.9962811916073</v>
+        <v>236.1262239791705</v>
       </c>
       <c r="O67">
-        <v>29.87453514895092</v>
+        <v>29.51577799739631</v>
       </c>
       <c r="P67">
-        <v>209.1217460426564</v>
+        <v>206.6104459817742</v>
       </c>
       <c r="Q67">
-        <v>235.8217460426564</v>
+        <v>233.3104459817742</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1777498281579574</v>
+        <v>0.1814459017758273</v>
       </c>
       <c r="T67">
-        <v>2.571947748884586</v>
+        <v>2.643991103195079</v>
       </c>
       <c r="U67">
         <v>0.0817366166625341</v>
@@ -6822,7 +6822,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.281112393353455</v>
+        <v>2.246550084363251</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,22 +6830,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1088945027263947</v>
+        <v>0.1090888648706881</v>
       </c>
       <c r="C68">
-        <v>937.859736008751</v>
+        <v>895.8969234416827</v>
       </c>
       <c r="D68">
-        <v>3102.349543580593</v>
+        <v>3095.500212946431</v>
       </c>
       <c r="E68">
-        <v>610.1416142811729</v>
+        <v>645.2550962140797</v>
       </c>
       <c r="F68">
-        <v>2317.489807571842</v>
+        <v>2352.603289504748</v>
       </c>
       <c r="G68">
         <v>153</v>
@@ -6866,28 +6866,28 @@
         <v>425.55</v>
       </c>
       <c r="M68">
-        <v>189.4237760208295</v>
+        <v>192.2938332332663</v>
       </c>
       <c r="N68">
-        <v>236.1262239791705</v>
+        <v>233.2561667667337</v>
       </c>
       <c r="O68">
-        <v>29.51577799739631</v>
+        <v>29.15702084584171</v>
       </c>
       <c r="P68">
-        <v>206.6104459817742</v>
+        <v>204.099145920892</v>
       </c>
       <c r="Q68">
-        <v>233.3104459817742</v>
+        <v>230.799145920892</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1814459017758273</v>
+        <v>0.1853659798553864</v>
       </c>
       <c r="T68">
-        <v>2.643991103195079</v>
+        <v>2.720400721403177</v>
       </c>
       <c r="U68">
         <v>0.0817366166625341</v>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.246550084363251</v>
+        <v>2.213019486089172</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,22 +6912,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1090888648706881</v>
+        <v>0.1092832270149815</v>
       </c>
       <c r="C69">
-        <v>895.8969234416827</v>
+        <v>853.9642879922799</v>
       </c>
       <c r="D69">
-        <v>3095.500212946431</v>
+        <v>3088.681059429935</v>
       </c>
       <c r="E69">
-        <v>645.2550962140797</v>
+        <v>680.3685781469865</v>
       </c>
       <c r="F69">
-        <v>2352.603289504748</v>
+        <v>2387.716771437655</v>
       </c>
       <c r="G69">
         <v>153</v>
@@ -6948,28 +6948,28 @@
         <v>425.55</v>
       </c>
       <c r="M69">
-        <v>192.2938332332663</v>
+        <v>195.1638904457031</v>
       </c>
       <c r="N69">
-        <v>233.2561667667337</v>
+        <v>230.3861095542969</v>
       </c>
       <c r="O69">
-        <v>29.15702084584171</v>
+        <v>28.79826369428711</v>
       </c>
       <c r="P69">
-        <v>204.099145920892</v>
+        <v>201.5878458600098</v>
       </c>
       <c r="Q69">
-        <v>230.799145920892</v>
+        <v>228.2878458600098</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1853659798553864</v>
+        <v>0.1895310628149179</v>
       </c>
       <c r="T69">
-        <v>2.720400721403177</v>
+        <v>2.801585940749282</v>
       </c>
       <c r="U69">
         <v>0.0817366166625341</v>
@@ -6986,7 +6986,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.213019486089172</v>
+        <v>2.180475081881978</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,22 +6994,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1092832270149815</v>
+        <v>0.1094775891592749</v>
       </c>
       <c r="C70">
-        <v>853.9642879922799</v>
+        <v>812.0616306651709</v>
       </c>
       <c r="D70">
-        <v>3088.681059429935</v>
+        <v>3081.891884035733</v>
       </c>
       <c r="E70">
-        <v>680.3685781469865</v>
+        <v>715.4820600798932</v>
       </c>
       <c r="F70">
-        <v>2387.716771437655</v>
+        <v>2422.830253370562</v>
       </c>
       <c r="G70">
         <v>153</v>
@@ -7030,28 +7030,28 @@
         <v>425.55</v>
       </c>
       <c r="M70">
-        <v>195.1638904457031</v>
+        <v>198.03394765814</v>
       </c>
       <c r="N70">
-        <v>230.3861095542969</v>
+        <v>227.51605234186</v>
       </c>
       <c r="O70">
-        <v>28.79826369428711</v>
+        <v>28.43950654273251</v>
       </c>
       <c r="P70">
-        <v>201.5878458600098</v>
+        <v>199.0765457991275</v>
       </c>
       <c r="Q70">
-        <v>228.2878458600098</v>
+        <v>225.7765457991275</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1895310628149179</v>
+        <v>0.1939648608040965</v>
       </c>
       <c r="T70">
-        <v>2.801585940749282</v>
+        <v>2.888008916182232</v>
       </c>
       <c r="U70">
         <v>0.0817366166625341</v>
@@ -7068,7 +7068,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.180475081881978</v>
+        <v>2.148873993738761</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,22 +7076,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1094775891592749</v>
+        <v>0.1096719513035683</v>
       </c>
       <c r="C71">
-        <v>812.0616306651709</v>
+        <v>770.1887542107806</v>
       </c>
       <c r="D71">
-        <v>3081.891884035733</v>
+        <v>3075.132489514249</v>
       </c>
       <c r="E71">
-        <v>715.4820600798932</v>
+        <v>750.5955420128</v>
       </c>
       <c r="F71">
-        <v>2422.830253370562</v>
+        <v>2457.943735303469</v>
       </c>
       <c r="G71">
         <v>153</v>
@@ -7112,28 +7112,28 @@
         <v>425.55</v>
       </c>
       <c r="M71">
-        <v>198.03394765814</v>
+        <v>200.9040048705768</v>
       </c>
       <c r="N71">
-        <v>227.51605234186</v>
+        <v>224.6459951294232</v>
       </c>
       <c r="O71">
-        <v>28.43950654273251</v>
+        <v>28.0807493911779</v>
       </c>
       <c r="P71">
-        <v>199.0765457991275</v>
+        <v>196.5652457382453</v>
       </c>
       <c r="Q71">
-        <v>225.7765457991275</v>
+        <v>223.2652457382453</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1939648608040965</v>
+        <v>0.1986942453258871</v>
       </c>
       <c r="T71">
-        <v>2.888008916182232</v>
+        <v>2.980193423310711</v>
       </c>
       <c r="U71">
         <v>0.0817366166625341</v>
@@ -7150,7 +7150,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.148873993738761</v>
+        <v>2.118175793828208</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,22 +7158,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1096719513035683</v>
+        <v>0.1098663134478617</v>
       </c>
       <c r="C72">
-        <v>770.1887542107806</v>
+        <v>728.345463106225</v>
       </c>
       <c r="D72">
-        <v>3075.132489514249</v>
+        <v>3068.4026803426</v>
       </c>
       <c r="E72">
-        <v>750.5955420128</v>
+        <v>785.7090239457063</v>
       </c>
       <c r="F72">
-        <v>2457.943735303469</v>
+        <v>2493.057217236375</v>
       </c>
       <c r="G72">
         <v>153</v>
@@ -7194,28 +7194,28 @@
         <v>425.55</v>
       </c>
       <c r="M72">
-        <v>200.9040048705768</v>
+        <v>203.7740620830136</v>
       </c>
       <c r="N72">
-        <v>224.6459951294232</v>
+        <v>221.7759379169864</v>
       </c>
       <c r="O72">
-        <v>28.0807493911779</v>
+        <v>27.7219922396233</v>
       </c>
       <c r="P72">
-        <v>196.5652457382453</v>
+        <v>194.0539456773631</v>
       </c>
       <c r="Q72">
-        <v>223.2652457382453</v>
+        <v>220.7539456773631</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1986942453258871</v>
+        <v>0.2037497942974564</v>
       </c>
       <c r="T72">
-        <v>2.980193423310711</v>
+        <v>3.078735482654948</v>
       </c>
       <c r="U72">
         <v>0.0817366166625341</v>
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.118175793828208</v>
+        <v>2.088342331943303</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,22 +7240,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1098663134478617</v>
+        <v>0.110060675592155</v>
       </c>
       <c r="C73">
-        <v>728.345463106225</v>
+        <v>686.5315635364614</v>
       </c>
       <c r="D73">
-        <v>3068.4026803426</v>
+        <v>3061.702262705743</v>
       </c>
       <c r="E73">
-        <v>785.7090239457063</v>
+        <v>820.8225058786127</v>
       </c>
       <c r="F73">
-        <v>2493.057217236375</v>
+        <v>2528.170699169281</v>
       </c>
       <c r="G73">
         <v>153</v>
@@ -7276,28 +7276,28 @@
         <v>425.55</v>
       </c>
       <c r="M73">
-        <v>203.7740620830136</v>
+        <v>206.6441192954503</v>
       </c>
       <c r="N73">
-        <v>221.7759379169864</v>
+        <v>218.9058807045497</v>
       </c>
       <c r="O73">
-        <v>27.7219922396233</v>
+        <v>27.36323508806871</v>
       </c>
       <c r="P73">
-        <v>194.0539456773631</v>
+        <v>191.542645616481</v>
       </c>
       <c r="Q73">
-        <v>220.7539456773631</v>
+        <v>218.242645616481</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2037497942974563</v>
+        <v>0.2091664539098519</v>
       </c>
       <c r="T73">
-        <v>3.078735482654948</v>
+        <v>3.184316260523773</v>
       </c>
       <c r="U73">
         <v>0.0817366166625341</v>
@@ -7314,7 +7314,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.088342331943303</v>
+        <v>2.05933757733298</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,22 +7322,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.110060675592155</v>
+        <v>0.1102550377364484</v>
       </c>
       <c r="C74">
-        <v>686.5315635364614</v>
+        <v>644.7468633756775</v>
       </c>
       <c r="D74">
-        <v>3061.702262705743</v>
+        <v>3055.031044477866</v>
       </c>
       <c r="E74">
-        <v>820.8225058786127</v>
+        <v>855.9359878115195</v>
       </c>
       <c r="F74">
-        <v>2528.170699169281</v>
+        <v>2563.284181102188</v>
       </c>
       <c r="G74">
         <v>153</v>
@@ -7358,28 +7358,28 @@
         <v>425.55</v>
       </c>
       <c r="M74">
-        <v>206.6441192954503</v>
+        <v>209.5141765078872</v>
       </c>
       <c r="N74">
-        <v>218.9058807045497</v>
+        <v>216.0358234921129</v>
       </c>
       <c r="O74">
-        <v>27.36323508806871</v>
+        <v>27.00447793651411</v>
       </c>
       <c r="P74">
-        <v>191.542645616481</v>
+        <v>189.0313455555988</v>
       </c>
       <c r="Q74">
-        <v>218.242645616481</v>
+        <v>215.7313455555988</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2091664539098519</v>
+        <v>0.2149843475676102</v>
       </c>
       <c r="T74">
-        <v>3.184316260523773</v>
+        <v>3.297717836753252</v>
       </c>
       <c r="U74">
         <v>0.0817366166625341</v>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.05933757733298</v>
+        <v>2.031127473533898</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,22 +7404,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1102550377364484</v>
+        <v>0.1104493998807418</v>
       </c>
       <c r="C75">
-        <v>644.7468633756775</v>
+        <v>602.9911721689346</v>
       </c>
       <c r="D75">
-        <v>3055.031044477866</v>
+        <v>3048.388835204029</v>
       </c>
       <c r="E75">
-        <v>855.9359878115195</v>
+        <v>891.0494697444262</v>
       </c>
       <c r="F75">
-        <v>2563.284181102188</v>
+        <v>2598.397663035095</v>
       </c>
       <c r="G75">
         <v>153</v>
@@ -7440,28 +7440,28 @@
         <v>425.55</v>
       </c>
       <c r="M75">
-        <v>209.5141765078872</v>
+        <v>212.384233720324</v>
       </c>
       <c r="N75">
-        <v>216.0358234921129</v>
+        <v>213.165766279676</v>
       </c>
       <c r="O75">
-        <v>27.00447793651411</v>
+        <v>26.6457207849595</v>
       </c>
       <c r="P75">
-        <v>189.0313455555988</v>
+        <v>186.5200454947165</v>
       </c>
       <c r="Q75">
-        <v>215.7313455555988</v>
+        <v>213.2200454947165</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2149843475676102</v>
+        <v>0.2212497715067345</v>
       </c>
       <c r="T75">
-        <v>3.297717836753252</v>
+        <v>3.419842611154229</v>
       </c>
       <c r="U75">
         <v>0.0817366166625341</v>
@@ -7478,7 +7478,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.031127473533898</v>
+        <v>2.003679804972629</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,22 +7486,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1104493998807418</v>
+        <v>0.1199625120250352</v>
       </c>
       <c r="C76">
-        <v>602.9911721689346</v>
+        <v>274.6805791800762</v>
       </c>
       <c r="D76">
-        <v>3048.388835204029</v>
+        <v>2755.191724148078</v>
       </c>
       <c r="E76">
-        <v>891.0494697444262</v>
+        <v>926.162951677333</v>
       </c>
       <c r="F76">
-        <v>2598.397663035095</v>
+        <v>2633.511144968002</v>
       </c>
       <c r="G76">
         <v>153</v>
@@ -7522,45 +7522,45 @@
         <v>425.55</v>
       </c>
       <c r="M76">
-        <v>212.384233720324</v>
+        <v>252.6501491913064</v>
       </c>
       <c r="N76">
-        <v>213.165766279676</v>
+        <v>172.8998508086936</v>
       </c>
       <c r="O76">
-        <v>26.6457207849595</v>
+        <v>21.6124813510867</v>
       </c>
       <c r="P76">
-        <v>186.5200454947165</v>
+        <v>151.2873694576069</v>
       </c>
       <c r="Q76">
-        <v>213.2200454947165</v>
+        <v>177.9873694576069</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2212497715067345</v>
+        <v>0.2280164293609887</v>
       </c>
       <c r="T76">
-        <v>3.419842611154229</v>
+        <v>3.551737367507285</v>
       </c>
       <c r="U76">
-        <v>0.0817366166625341</v>
+        <v>0.0959366166625341</v>
       </c>
       <c r="V76">
         <v>0.125</v>
       </c>
       <c r="W76">
-        <v>0.07151953957971734</v>
+        <v>0.08394453957971734</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.003679804972629</v>
+        <v>1.684344938493482</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,22 +7568,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1199625120250352</v>
+        <v>0.1202811241693286</v>
       </c>
       <c r="C77">
-        <v>274.6805791800762</v>
+        <v>230.7203397808607</v>
       </c>
       <c r="D77">
-        <v>2755.191724148078</v>
+        <v>2746.344966681769</v>
       </c>
       <c r="E77">
-        <v>926.162951677333</v>
+        <v>961.2764336102398</v>
       </c>
       <c r="F77">
-        <v>2633.511144968002</v>
+        <v>2668.624626900908</v>
       </c>
       <c r="G77">
         <v>153</v>
@@ -7604,28 +7604,28 @@
         <v>425.55</v>
       </c>
       <c r="M77">
-        <v>252.6501491913064</v>
+        <v>256.0188178471905</v>
       </c>
       <c r="N77">
-        <v>172.8998508086936</v>
+        <v>169.5311821528095</v>
       </c>
       <c r="O77">
-        <v>21.6124813510867</v>
+        <v>21.19139776910119</v>
       </c>
       <c r="P77">
-        <v>151.2873694576069</v>
+        <v>148.3397843837083</v>
       </c>
       <c r="Q77">
-        <v>177.9873694576069</v>
+        <v>175.0397843837083</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2280164293609887</v>
+        <v>0.2353469753697641</v>
       </c>
       <c r="T77">
-        <v>3.551737367507285</v>
+        <v>3.694623353556429</v>
       </c>
       <c r="U77">
         <v>0.0959366166625341</v>
@@ -7642,7 +7642,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.684344938493482</v>
+        <v>1.662182505092252</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,22 +7650,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1202811241693286</v>
+        <v>0.120599736313622</v>
       </c>
       <c r="C78">
-        <v>230.7203397808607</v>
+        <v>186.8167313715448</v>
       </c>
       <c r="D78">
-        <v>2746.344966681769</v>
+        <v>2737.55484020536</v>
       </c>
       <c r="E78">
-        <v>961.2764336102398</v>
+        <v>996.3899155431466</v>
       </c>
       <c r="F78">
-        <v>2668.624626900908</v>
+        <v>2703.738108833815</v>
       </c>
       <c r="G78">
         <v>153</v>
@@ -7686,28 +7686,28 @@
         <v>425.55</v>
       </c>
       <c r="M78">
-        <v>256.0188178471905</v>
+        <v>259.3874865030746</v>
       </c>
       <c r="N78">
-        <v>169.5311821528095</v>
+        <v>166.1625134969254</v>
       </c>
       <c r="O78">
-        <v>21.19139776910119</v>
+        <v>20.77031418711567</v>
       </c>
       <c r="P78">
-        <v>148.3397843837083</v>
+        <v>145.3921993098097</v>
       </c>
       <c r="Q78">
-        <v>175.0397843837083</v>
+        <v>172.0921993098097</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2353469753697641</v>
+        <v>0.2433149601619113</v>
       </c>
       <c r="T78">
-        <v>3.694623353556429</v>
+        <v>3.849934207957672</v>
       </c>
       <c r="U78">
         <v>0.0959366166625341</v>
@@ -7724,7 +7724,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.662182505092252</v>
+        <v>1.640595719311833</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,22 +7732,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.120599736313622</v>
+        <v>0.1209183484579153</v>
       </c>
       <c r="C79">
-        <v>186.8167313715448</v>
+        <v>142.9692119167521</v>
       </c>
       <c r="D79">
-        <v>2737.55484020536</v>
+        <v>2728.820802683474</v>
       </c>
       <c r="E79">
-        <v>996.3899155431466</v>
+        <v>1031.503397476053</v>
       </c>
       <c r="F79">
-        <v>2703.738108833815</v>
+        <v>2738.851590766722</v>
       </c>
       <c r="G79">
         <v>153</v>
@@ -7768,28 +7768,28 @@
         <v>425.55</v>
       </c>
       <c r="M79">
-        <v>259.3874865030746</v>
+        <v>262.7561551589587</v>
       </c>
       <c r="N79">
-        <v>166.1625134969254</v>
+        <v>162.7938448410413</v>
       </c>
       <c r="O79">
-        <v>20.77031418711567</v>
+        <v>20.34923060513016</v>
       </c>
       <c r="P79">
-        <v>145.3921993098097</v>
+        <v>142.4446142359111</v>
       </c>
       <c r="Q79">
-        <v>172.0921993098097</v>
+        <v>169.1446142359111</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2433149601619113</v>
+        <v>0.2520073072078901</v>
       </c>
       <c r="T79">
-        <v>3.849934207957672</v>
+        <v>4.019364230940846</v>
       </c>
       <c r="U79">
         <v>0.0959366166625341</v>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.640595719311833</v>
+        <v>1.619562440859117</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,22 +7814,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1209183484579153</v>
+        <v>0.1212369606022087</v>
       </c>
       <c r="C80">
-        <v>142.9692119167521</v>
+        <v>99.17724627645521</v>
       </c>
       <c r="D80">
-        <v>2728.820802683474</v>
+        <v>2720.142318976084</v>
       </c>
       <c r="E80">
-        <v>1031.503397476053</v>
+        <v>1066.61687940896</v>
       </c>
       <c r="F80">
-        <v>2738.851590766722</v>
+        <v>2773.965072699628</v>
       </c>
       <c r="G80">
         <v>153</v>
@@ -7850,28 +7850,28 @@
         <v>425.55</v>
       </c>
       <c r="M80">
-        <v>262.7561551589587</v>
+        <v>266.1248238148428</v>
       </c>
       <c r="N80">
-        <v>162.7938448410413</v>
+        <v>159.4251761851572</v>
       </c>
       <c r="O80">
-        <v>20.34923060513016</v>
+        <v>19.92814702314465</v>
       </c>
       <c r="P80">
-        <v>142.4446142359111</v>
+        <v>139.4970291620126</v>
       </c>
       <c r="Q80">
-        <v>169.1446142359111</v>
+        <v>166.1970291620126</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2520073072078901</v>
+        <v>0.2615274968296764</v>
       </c>
       <c r="T80">
-        <v>4.019364230940846</v>
+        <v>4.204930446589086</v>
       </c>
       <c r="U80">
         <v>0.0959366166625341</v>
@@ -7888,7 +7888,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.619562440859117</v>
+        <v>1.599061650468495</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,22 +7896,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1212369606022087</v>
+        <v>0.1215555727465021</v>
       </c>
       <c r="C81">
-        <v>99.17724627645521</v>
+        <v>55.44030609668334</v>
       </c>
       <c r="D81">
-        <v>2720.142318976084</v>
+        <v>2711.518860729218</v>
       </c>
       <c r="E81">
-        <v>1066.61687940896</v>
+        <v>1101.730361341866</v>
       </c>
       <c r="F81">
-        <v>2773.965072699628</v>
+        <v>2809.078554632535</v>
       </c>
       <c r="G81">
         <v>153</v>
@@ -7932,28 +7932,28 @@
         <v>425.55</v>
       </c>
       <c r="M81">
-        <v>266.1248238148428</v>
+        <v>269.4934924707269</v>
       </c>
       <c r="N81">
-        <v>159.4251761851572</v>
+        <v>156.0565075292731</v>
       </c>
       <c r="O81">
-        <v>19.92814702314465</v>
+        <v>19.50706344115914</v>
       </c>
       <c r="P81">
-        <v>139.4970291620126</v>
+        <v>136.549444088114</v>
       </c>
       <c r="Q81">
-        <v>166.1970291620126</v>
+        <v>163.249444088114</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2615274968296764</v>
+        <v>0.2719997054136412</v>
       </c>
       <c r="T81">
-        <v>4.204930446589086</v>
+        <v>4.409053283802148</v>
       </c>
       <c r="U81">
         <v>0.0959366166625341</v>
@@ -7970,7 +7970,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.599061650468495</v>
+        <v>1.579073379837639</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,22 +7978,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1215555727465021</v>
+        <v>0.1218741848907955</v>
       </c>
       <c r="C82">
-        <v>55.44030609668334</v>
+        <v>11.75786970228955</v>
       </c>
       <c r="D82">
-        <v>2711.518860729218</v>
+        <v>2702.949906267731</v>
       </c>
       <c r="E82">
-        <v>1101.730361341866</v>
+        <v>1136.843843274773</v>
       </c>
       <c r="F82">
-        <v>2809.078554632535</v>
+        <v>2844.192036565442</v>
       </c>
       <c r="G82">
         <v>153</v>
@@ -8014,28 +8014,28 @@
         <v>425.55</v>
       </c>
       <c r="M82">
-        <v>269.4934924707269</v>
+        <v>272.8621611266109</v>
       </c>
       <c r="N82">
-        <v>156.0565075292731</v>
+        <v>152.6878388733891</v>
       </c>
       <c r="O82">
-        <v>19.50706344115914</v>
+        <v>19.08597985917363</v>
       </c>
       <c r="P82">
-        <v>136.549444088114</v>
+        <v>133.6018590142154</v>
       </c>
       <c r="Q82">
-        <v>163.249444088114</v>
+        <v>160.3018590142154</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2719997054136412</v>
+        <v>0.2835742517432866</v>
       </c>
       <c r="T82">
-        <v>4.409053283802148</v>
+        <v>4.634662735458691</v>
       </c>
       <c r="U82">
         <v>0.0959366166625341</v>
@@ -8052,7 +8052,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.579073379837639</v>
+        <v>1.559578646753224</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,22 +8060,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1218741848907955</v>
+        <v>0.1221927970350889</v>
       </c>
       <c r="C83">
-        <v>11.75786970228955</v>
+        <v>-31.87057800824368</v>
       </c>
       <c r="D83">
-        <v>2702.949906267731</v>
+        <v>2694.434940490105</v>
       </c>
       <c r="E83">
-        <v>1136.843843274773</v>
+        <v>1171.95732520768</v>
       </c>
       <c r="F83">
-        <v>2844.192036565442</v>
+        <v>2879.305518498349</v>
       </c>
       <c r="G83">
         <v>153</v>
@@ -8096,28 +8096,28 @@
         <v>425.55</v>
       </c>
       <c r="M83">
-        <v>272.8621611266109</v>
+        <v>276.2308297824951</v>
       </c>
       <c r="N83">
-        <v>152.6878388733891</v>
+        <v>149.319170217505</v>
       </c>
       <c r="O83">
-        <v>19.08597985917363</v>
+        <v>18.66489627718812</v>
       </c>
       <c r="P83">
-        <v>133.6018590142154</v>
+        <v>130.6542739403168</v>
       </c>
       <c r="Q83">
-        <v>160.3018590142154</v>
+        <v>157.3542739403168</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2835742517432866</v>
+        <v>0.2964348587762259</v>
       </c>
       <c r="T83">
-        <v>4.634662735458691</v>
+        <v>4.885339903965961</v>
       </c>
       <c r="U83">
         <v>0.0959366166625341</v>
@@ -8134,7 +8134,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.559578646753224</v>
+        <v>1.54055939496355</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,22 +8142,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1221927970350889</v>
+        <v>0.1225114091793823</v>
       </c>
       <c r="C84">
-        <v>-31.87057800824368</v>
+        <v>-75.4455456660271</v>
       </c>
       <c r="D84">
-        <v>2694.434940490105</v>
+        <v>2685.973454765228</v>
       </c>
       <c r="E84">
-        <v>1171.95732520768</v>
+        <v>1207.070807140587</v>
       </c>
       <c r="F84">
-        <v>2879.305518498349</v>
+        <v>2914.419000431255</v>
       </c>
       <c r="G84">
         <v>153</v>
@@ -8178,28 +8178,28 @@
         <v>425.55</v>
       </c>
       <c r="M84">
-        <v>276.2308297824951</v>
+        <v>279.5994984383792</v>
       </c>
       <c r="N84">
-        <v>149.319170217505</v>
+        <v>145.9505015616209</v>
       </c>
       <c r="O84">
-        <v>18.66489627718812</v>
+        <v>18.24381269520261</v>
       </c>
       <c r="P84">
-        <v>130.6542739403168</v>
+        <v>127.7066888664182</v>
       </c>
       <c r="Q84">
-        <v>157.3542739403168</v>
+        <v>154.4066888664182</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2964348587762259</v>
+        <v>0.3108084784012758</v>
       </c>
       <c r="T84">
-        <v>4.885339903965961</v>
+        <v>5.165508504062322</v>
       </c>
       <c r="U84">
         <v>0.0959366166625341</v>
@@ -8216,7 +8216,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.54055939496355</v>
+        <v>1.521998438397724</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,22 +8224,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1225114091793823</v>
+        <v>0.1228300213236757</v>
       </c>
       <c r="C85">
-        <v>-75.4455456660271</v>
+        <v>-118.9675355330382</v>
       </c>
       <c r="D85">
-        <v>2685.973454765228</v>
+        <v>2677.564946831124</v>
       </c>
       <c r="E85">
-        <v>1207.070807140587</v>
+        <v>1242.184289073494</v>
       </c>
       <c r="F85">
-        <v>2914.419000431255</v>
+        <v>2949.532482364162</v>
       </c>
       <c r="G85">
         <v>153</v>
@@ -8260,28 +8260,28 @@
         <v>425.55</v>
       </c>
       <c r="M85">
-        <v>279.5994984383792</v>
+        <v>282.9681670942633</v>
       </c>
       <c r="N85">
-        <v>145.9505015616209</v>
+        <v>142.5818329057367</v>
       </c>
       <c r="O85">
-        <v>18.24381269520261</v>
+        <v>17.82272911321709</v>
       </c>
       <c r="P85">
-        <v>127.7066888664182</v>
+        <v>124.7591037925197</v>
       </c>
       <c r="Q85">
-        <v>154.4066888664182</v>
+        <v>151.4591037925196</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3108084784012758</v>
+        <v>0.3269788004794569</v>
       </c>
       <c r="T85">
-        <v>5.165508504062322</v>
+        <v>5.480698179170728</v>
       </c>
       <c r="U85">
         <v>0.0959366166625341</v>
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>1.521998438397724</v>
+        <v>1.50387940936918</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,22 +8306,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1228300213236756</v>
+        <v>0.1668279649355852</v>
       </c>
       <c r="C86">
-        <v>-118.9675355330373</v>
+        <v>-962.2323281818885</v>
       </c>
       <c r="D86">
-        <v>2677.564946831124</v>
+        <v>1869.41363611518</v>
       </c>
       <c r="E86">
-        <v>1242.184289073493</v>
+        <v>1277.2977710064</v>
       </c>
       <c r="F86">
-        <v>2949.532482364162</v>
+        <v>2984.645964297069</v>
       </c>
       <c r="G86">
         <v>153</v>
@@ -8342,45 +8342,45 @@
         <v>425.55</v>
       </c>
       <c r="M86">
-        <v>282.9681670942632</v>
+        <v>455.8647265222208</v>
       </c>
       <c r="N86">
-        <v>142.5818329057368</v>
+        <v>-30.31472652222078</v>
       </c>
       <c r="O86">
-        <v>17.8227291132171</v>
+        <v>-3.789340815277598</v>
       </c>
       <c r="P86">
-        <v>124.7591037925197</v>
+        <v>-26.52538570694318</v>
       </c>
       <c r="Q86">
-        <v>151.4591037925197</v>
+        <v>0.1746142930568162</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3269788004794567</v>
+        <v>0.3476729101652054</v>
       </c>
       <c r="T86">
-        <v>5.480698179170724</v>
+        <v>5.884064894872069</v>
       </c>
       <c r="U86">
-        <v>0.0959366166625341</v>
+        <v>0.1527366166625341</v>
       </c>
       <c r="V86">
-        <v>0.125</v>
+        <v>0.1166875761715841</v>
       </c>
       <c r="W86">
-        <v>0.08394453957971734</v>
+        <v>0.1349141510715346</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y86">
-        <v>1.50387940936918</v>
+        <v>0.933500609372673</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,22 +8388,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1668279649355852</v>
+        <v>0.1678973311022106</v>
       </c>
       <c r="C87">
-        <v>-962.2323281818885</v>
+        <v>-1010.959563262421</v>
       </c>
       <c r="D87">
-        <v>1869.41363611518</v>
+        <v>1855.799882967554</v>
       </c>
       <c r="E87">
-        <v>1277.2977710064</v>
+        <v>1312.411252939307</v>
       </c>
       <c r="F87">
-        <v>2984.645964297069</v>
+        <v>3019.759446229975</v>
       </c>
       <c r="G87">
         <v>153</v>
@@ -8424,37 +8424,37 @@
         <v>425.55</v>
       </c>
       <c r="M87">
-        <v>455.8647265222208</v>
+        <v>461.227840951894</v>
       </c>
       <c r="N87">
-        <v>-30.31472652222078</v>
+        <v>-35.67784095189398</v>
       </c>
       <c r="O87">
-        <v>-3.789340815277598</v>
+        <v>-4.459730118986748</v>
       </c>
       <c r="P87">
-        <v>-26.52538570694318</v>
+        <v>-31.21811083290724</v>
       </c>
       <c r="Q87">
-        <v>0.1746142930568162</v>
+        <v>-4.518110832907237</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3476729101652054</v>
+        <v>0.3692352608912914</v>
       </c>
       <c r="T87">
-        <v>5.884064894872069</v>
+        <v>6.304355244505787</v>
       </c>
       <c r="U87">
         <v>0.1527366166625341</v>
       </c>
       <c r="V87">
-        <v>0.1166875761715841</v>
+        <v>0.1153307438905192</v>
       </c>
       <c r="W87">
-        <v>0.1349141510715346</v>
+        <v>0.135121389043523</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8462,7 +8462,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.933500609372673</v>
+        <v>0.9226459511241535</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,22 +8470,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1678973311022106</v>
+        <v>0.1689666972688359</v>
       </c>
       <c r="C88">
-        <v>-1010.959563262421</v>
+        <v>-1059.489951206455</v>
       </c>
       <c r="D88">
-        <v>1855.799882967554</v>
+        <v>1842.382976956427</v>
       </c>
       <c r="E88">
-        <v>1312.411252939307</v>
+        <v>1347.524734872213</v>
       </c>
       <c r="F88">
-        <v>3019.759446229975</v>
+        <v>3054.872928162882</v>
       </c>
       <c r="G88">
         <v>153</v>
@@ -8506,37 +8506,37 @@
         <v>425.55</v>
       </c>
       <c r="M88">
-        <v>461.227840951894</v>
+        <v>466.5909553815672</v>
       </c>
       <c r="N88">
-        <v>-35.67784095189398</v>
+        <v>-41.04095538156719</v>
       </c>
       <c r="O88">
-        <v>-4.459730118986748</v>
+        <v>-5.130119422695898</v>
       </c>
       <c r="P88">
-        <v>-31.21811083290724</v>
+        <v>-35.91083595887129</v>
       </c>
       <c r="Q88">
-        <v>-4.518110832907237</v>
+        <v>-9.210835958871289</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3692352608912914</v>
+        <v>0.3941148963444677</v>
       </c>
       <c r="T88">
-        <v>6.304355244505787</v>
+        <v>6.78930564792931</v>
       </c>
       <c r="U88">
         <v>0.1527366166625341</v>
       </c>
       <c r="V88">
-        <v>0.1153307438905192</v>
+        <v>0.1140051031561454</v>
       </c>
       <c r="W88">
-        <v>0.135121389043523</v>
+        <v>0.1353238629242013</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.9226459511241535</v>
+        <v>0.9120408252491632</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,22 +8552,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1689666972688359</v>
+        <v>0.1700360634354612</v>
       </c>
       <c r="C89">
-        <v>-1059.489951206455</v>
+        <v>-1107.827730815303</v>
       </c>
       <c r="D89">
-        <v>1842.382976956427</v>
+        <v>1829.158679280485</v>
       </c>
       <c r="E89">
-        <v>1347.524734872213</v>
+        <v>1382.63821680512</v>
       </c>
       <c r="F89">
-        <v>3054.872928162882</v>
+        <v>3089.986410095788</v>
       </c>
       <c r="G89">
         <v>153</v>
@@ -8588,37 +8588,37 @@
         <v>425.55</v>
       </c>
       <c r="M89">
-        <v>466.5909553815672</v>
+        <v>471.9540698112403</v>
       </c>
       <c r="N89">
-        <v>-41.04095538156719</v>
+        <v>-46.40406981124033</v>
       </c>
       <c r="O89">
-        <v>-5.130119422695898</v>
+        <v>-5.800508726405042</v>
       </c>
       <c r="P89">
-        <v>-35.91083595887129</v>
+        <v>-40.60356108483529</v>
       </c>
       <c r="Q89">
-        <v>-9.210835958871289</v>
+        <v>-13.90356108483529</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3941148963444677</v>
+        <v>0.4231411377065068</v>
       </c>
       <c r="T89">
-        <v>6.78930564792931</v>
+        <v>7.355081118590087</v>
       </c>
       <c r="U89">
         <v>0.1527366166625341</v>
       </c>
       <c r="V89">
-        <v>0.1140051031561454</v>
+        <v>0.1127095906202801</v>
       </c>
       <c r="W89">
-        <v>0.1353238629242013</v>
+        <v>0.1355217351257732</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8626,7 +8626,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.9120408252491632</v>
+        <v>0.9016767249622409</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,22 +8634,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1700360634354612</v>
+        <v>0.1711054296020866</v>
       </c>
       <c r="C90">
-        <v>-1107.827730815303</v>
+        <v>-1155.97702005616</v>
       </c>
       <c r="D90">
-        <v>1829.158679280485</v>
+        <v>1816.122871972535</v>
       </c>
       <c r="E90">
-        <v>1382.63821680512</v>
+        <v>1417.751698738027</v>
       </c>
       <c r="F90">
-        <v>3089.986410095788</v>
+        <v>3125.099892028695</v>
       </c>
       <c r="G90">
         <v>153</v>
@@ -8670,37 +8670,37 @@
         <v>425.55</v>
       </c>
       <c r="M90">
-        <v>471.9540698112403</v>
+        <v>477.3171842409135</v>
       </c>
       <c r="N90">
-        <v>-46.40406981124033</v>
+        <v>-51.76718424091354</v>
       </c>
       <c r="O90">
-        <v>-5.800508726405042</v>
+        <v>-6.470898030114192</v>
       </c>
       <c r="P90">
-        <v>-40.60356108483529</v>
+        <v>-45.29628621079934</v>
       </c>
       <c r="Q90">
-        <v>-13.90356108483529</v>
+        <v>-18.59628621079935</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4231411377065068</v>
+        <v>0.4574448774980074</v>
       </c>
       <c r="T90">
-        <v>7.355081118590087</v>
+        <v>8.023724856643732</v>
       </c>
       <c r="U90">
         <v>0.1527366166625341</v>
       </c>
       <c r="V90">
-        <v>0.1127095906202801</v>
+        <v>0.1114431907256702</v>
       </c>
       <c r="W90">
-        <v>0.1355217351257732</v>
+        <v>0.1357151607610177</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8708,7 +8708,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.9016767249622409</v>
+        <v>0.8915455258053617</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,22 +8716,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1711054296020866</v>
+        <v>0.1721747957687119</v>
       </c>
       <c r="C91">
-        <v>-1155.97702005616</v>
+        <v>-1203.941820337347</v>
       </c>
       <c r="D91">
-        <v>1816.122871972535</v>
+        <v>1803.271553624255</v>
       </c>
       <c r="E91">
-        <v>1417.751698738027</v>
+        <v>1452.865180670933</v>
       </c>
       <c r="F91">
-        <v>3125.099892028695</v>
+        <v>3160.213373961602</v>
       </c>
       <c r="G91">
         <v>153</v>
@@ -8752,37 +8752,37 @@
         <v>425.55</v>
       </c>
       <c r="M91">
-        <v>477.3171842409135</v>
+        <v>482.6802986705868</v>
       </c>
       <c r="N91">
-        <v>-51.76718424091354</v>
+        <v>-57.13029867058674</v>
       </c>
       <c r="O91">
-        <v>-6.470898030114192</v>
+        <v>-7.141287333823342</v>
       </c>
       <c r="P91">
-        <v>-45.29628621079934</v>
+        <v>-49.9890113367634</v>
       </c>
       <c r="Q91">
-        <v>-18.59628621079935</v>
+        <v>-23.2890113367634</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4574448774980074</v>
+        <v>0.4986093652478082</v>
       </c>
       <c r="T91">
-        <v>8.023724856643732</v>
+        <v>8.826097342308106</v>
       </c>
       <c r="U91">
         <v>0.1527366166625341</v>
       </c>
       <c r="V91">
-        <v>0.1114431907256702</v>
+        <v>0.1102049330509405</v>
       </c>
       <c r="W91">
-        <v>0.1357151607610177</v>
+        <v>0.1359042880488124</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8790,7 +8790,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8915455258053617</v>
+        <v>0.8816394644075244</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,22 +8798,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1721747957687119</v>
+        <v>0.1732441619353373</v>
       </c>
       <c r="C92">
-        <v>-1203.941820337347</v>
+        <v>-1251.726020603332</v>
       </c>
       <c r="D92">
-        <v>1803.271553624255</v>
+        <v>1790.600835291177</v>
       </c>
       <c r="E92">
-        <v>1452.865180670933</v>
+        <v>1487.97866260384</v>
       </c>
       <c r="F92">
-        <v>3160.213373961602</v>
+        <v>3195.326855894509</v>
       </c>
       <c r="G92">
         <v>153</v>
@@ -8834,37 +8834,37 @@
         <v>425.55</v>
       </c>
       <c r="M92">
-        <v>482.6802986705868</v>
+        <v>488.04341310026</v>
       </c>
       <c r="N92">
-        <v>-57.13029867058674</v>
+        <v>-62.49341310025994</v>
       </c>
       <c r="O92">
-        <v>-7.141287333823342</v>
+        <v>-7.811676637532493</v>
       </c>
       <c r="P92">
-        <v>-49.9890113367634</v>
+        <v>-54.68173646272745</v>
       </c>
       <c r="Q92">
-        <v>-23.2890113367634</v>
+        <v>-27.98173646272745</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4986093652478082</v>
+        <v>0.5489215169420091</v>
       </c>
       <c r="T92">
-        <v>8.826097342308106</v>
+        <v>9.806774824786785</v>
       </c>
       <c r="U92">
         <v>0.1527366166625341</v>
       </c>
       <c r="V92">
-        <v>0.1102049330509405</v>
+        <v>0.1089938898306005</v>
       </c>
       <c r="W92">
-        <v>0.1359042880488124</v>
+        <v>0.1360892586929192</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8872,7 +8872,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8816394644075244</v>
+        <v>0.8719511186448043</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,22 +8880,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1732441619353373</v>
+        <v>0.1743135281019626</v>
       </c>
       <c r="C93">
-        <v>-1251.726020603332</v>
+        <v>-1299.333401258302</v>
       </c>
       <c r="D93">
-        <v>1790.600835291177</v>
+        <v>1778.106936569114</v>
       </c>
       <c r="E93">
-        <v>1487.97866260384</v>
+        <v>1523.092144536747</v>
       </c>
       <c r="F93">
-        <v>3195.326855894509</v>
+        <v>3230.440337827416</v>
       </c>
       <c r="G93">
         <v>153</v>
@@ -8916,37 +8916,37 @@
         <v>425.55</v>
       </c>
       <c r="M93">
-        <v>488.04341310026</v>
+        <v>493.4065275299332</v>
       </c>
       <c r="N93">
-        <v>-62.49341310025994</v>
+        <v>-67.85652752993315</v>
       </c>
       <c r="O93">
-        <v>-7.811676637532493</v>
+        <v>-8.482065941241643</v>
       </c>
       <c r="P93">
-        <v>-54.68173646272745</v>
+        <v>-59.3744615886915</v>
       </c>
       <c r="Q93">
-        <v>-27.98173646272745</v>
+        <v>-32.6744615886915</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5489215169420091</v>
+        <v>0.6118117065597605</v>
       </c>
       <c r="T93">
-        <v>9.806774824786785</v>
+        <v>11.03262167788514</v>
       </c>
       <c r="U93">
         <v>0.1527366166625341</v>
       </c>
       <c r="V93">
-        <v>0.1089938898306005</v>
+        <v>0.1078091736367897</v>
       </c>
       <c r="W93">
-        <v>0.1360892586929192</v>
+        <v>0.1362702082360672</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8719511186448043</v>
+        <v>0.8624733890943173</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,22 +8962,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1743135281019626</v>
+        <v>0.175382894268588</v>
       </c>
       <c r="C94">
-        <v>-1299.333401258302</v>
+        <v>-1346.767637926622</v>
       </c>
       <c r="D94">
-        <v>1778.106936569114</v>
+        <v>1765.7861818337</v>
       </c>
       <c r="E94">
-        <v>1523.092144536747</v>
+        <v>1558.205626469654</v>
       </c>
       <c r="F94">
-        <v>3230.440337827416</v>
+        <v>3265.553819760322</v>
       </c>
       <c r="G94">
         <v>153</v>
@@ -8998,37 +8998,37 @@
         <v>425.55</v>
       </c>
       <c r="M94">
-        <v>493.4065275299332</v>
+        <v>498.7696419596063</v>
       </c>
       <c r="N94">
-        <v>-67.85652752993315</v>
+        <v>-73.21964195960629</v>
       </c>
       <c r="O94">
-        <v>-8.482065941241643</v>
+        <v>-9.152455244950787</v>
       </c>
       <c r="P94">
-        <v>-59.3744615886915</v>
+        <v>-64.06718671465551</v>
       </c>
       <c r="Q94">
-        <v>-32.6744615886915</v>
+        <v>-37.3671867146555</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6118117065597605</v>
+        <v>0.6926705217825834</v>
       </c>
       <c r="T94">
-        <v>11.03262167788514</v>
+        <v>12.60871048901159</v>
       </c>
       <c r="U94">
         <v>0.1527366166625341</v>
       </c>
       <c r="V94">
-        <v>0.1078091736367897</v>
+        <v>0.1066499352105876</v>
       </c>
       <c r="W94">
-        <v>0.1362702082360672</v>
+        <v>0.1364472663911905</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9036,7 +9036,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8624733890943173</v>
+        <v>0.8531994816847011</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,22 +9044,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.175382894268588</v>
+        <v>0.1764522604352133</v>
       </c>
       <c r="C95">
-        <v>-1346.767637926622</v>
+        <v>-1394.032305058024</v>
       </c>
       <c r="D95">
-        <v>1765.7861818337</v>
+        <v>1753.634996635205</v>
       </c>
       <c r="E95">
-        <v>1558.205626469654</v>
+        <v>1593.31910840256</v>
       </c>
       <c r="F95">
-        <v>3265.553819760322</v>
+        <v>3300.667301693229</v>
       </c>
       <c r="G95">
         <v>153</v>
@@ -9080,37 +9080,37 @@
         <v>425.55</v>
       </c>
       <c r="M95">
-        <v>498.7696419596063</v>
+        <v>504.1327563892795</v>
       </c>
       <c r="N95">
-        <v>-73.21964195960629</v>
+        <v>-78.5827563892795</v>
       </c>
       <c r="O95">
-        <v>-9.152455244950787</v>
+        <v>-9.822844548659937</v>
       </c>
       <c r="P95">
-        <v>-64.06718671465551</v>
+        <v>-68.75991184061957</v>
       </c>
       <c r="Q95">
-        <v>-37.3671867146555</v>
+        <v>-42.05991184061956</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6926705217825834</v>
+        <v>0.8004822754130142</v>
       </c>
       <c r="T95">
-        <v>12.60871048901159</v>
+        <v>14.71016223718019</v>
       </c>
       <c r="U95">
         <v>0.1527366166625341</v>
       </c>
       <c r="V95">
-        <v>0.1066499352105876</v>
+        <v>0.1055153614317516</v>
       </c>
       <c r="W95">
-        <v>0.1364472663911905</v>
+        <v>0.1366205573515239</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8531994816847011</v>
+        <v>0.8441228914540126</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,22 +9126,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1764522604352133</v>
+        <v>0.1775216266018387</v>
       </c>
       <c r="C96">
-        <v>-1394.032305058024</v>
+        <v>-1441.130879384959</v>
       </c>
       <c r="D96">
-        <v>1753.634996635205</v>
+        <v>1741.649904241177</v>
       </c>
       <c r="E96">
-        <v>1593.31910840256</v>
+        <v>1628.432590335467</v>
       </c>
       <c r="F96">
-        <v>3300.667301693229</v>
+        <v>3335.780783626136</v>
       </c>
       <c r="G96">
         <v>153</v>
@@ -9162,37 +9162,37 @@
         <v>425.55</v>
       </c>
       <c r="M96">
-        <v>504.1327563892795</v>
+        <v>509.4958708189527</v>
       </c>
       <c r="N96">
-        <v>-78.5827563892795</v>
+        <v>-83.9458708189527</v>
       </c>
       <c r="O96">
-        <v>-9.822844548659937</v>
+        <v>-10.49323385236909</v>
       </c>
       <c r="P96">
-        <v>-68.75991184061957</v>
+        <v>-73.45263696658361</v>
       </c>
       <c r="Q96">
-        <v>-42.05991184061956</v>
+        <v>-46.75263696658361</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8004822754130142</v>
+        <v>0.9514187304956175</v>
       </c>
       <c r="T96">
-        <v>14.71016223718019</v>
+        <v>17.65219468461623</v>
       </c>
       <c r="U96">
         <v>0.1527366166625341</v>
       </c>
       <c r="V96">
-        <v>0.1055153614317516</v>
+        <v>0.1044046734166805</v>
       </c>
       <c r="W96">
-        <v>0.1366205573515239</v>
+        <v>0.1367902000811135</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9200,7 +9200,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8441228914540126</v>
+        <v>0.8352373873334441</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,22 +9208,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1775216266018387</v>
+        <v>0.178590992768464</v>
       </c>
       <c r="C97">
-        <v>-1441.130879384959</v>
+        <v>-1488.066743239141</v>
       </c>
       <c r="D97">
-        <v>1741.649904241177</v>
+        <v>1729.827522319901</v>
       </c>
       <c r="E97">
-        <v>1628.432590335467</v>
+        <v>1663.546072268374</v>
       </c>
       <c r="F97">
-        <v>3335.780783626136</v>
+        <v>3370.894265559042</v>
       </c>
       <c r="G97">
         <v>153</v>
@@ -9244,37 +9244,37 @@
         <v>425.55</v>
       </c>
       <c r="M97">
-        <v>509.4958708189527</v>
+        <v>514.8589852486259</v>
       </c>
       <c r="N97">
-        <v>-83.9458708189527</v>
+        <v>-89.3089852486259</v>
       </c>
       <c r="O97">
-        <v>-10.49323385236909</v>
+        <v>-11.16362315607824</v>
       </c>
       <c r="P97">
-        <v>-73.45263696658361</v>
+        <v>-78.14536209254766</v>
       </c>
       <c r="Q97">
-        <v>-46.75263696658361</v>
+        <v>-51.44536209254765</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9514187304956175</v>
+        <v>1.177823413119522</v>
       </c>
       <c r="T97">
-        <v>17.65219468461623</v>
+        <v>22.0652433557703</v>
       </c>
       <c r="U97">
         <v>0.1527366166625341</v>
       </c>
       <c r="V97">
-        <v>0.1044046734166805</v>
+        <v>0.1033171247352568</v>
       </c>
       <c r="W97">
-        <v>0.1367902000811135</v>
+        <v>0.13695630858717</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9282,7 +9282,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8352373873334441</v>
+        <v>0.826536997882054</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,22 +9290,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.178590992768464</v>
+        <v>0.1796603589350893</v>
       </c>
       <c r="C98">
-        <v>-1488.066743239141</v>
+        <v>-1534.843187733924</v>
       </c>
       <c r="D98">
-        <v>1729.827522319901</v>
+        <v>1718.164559758024</v>
       </c>
       <c r="E98">
-        <v>1663.546072268374</v>
+        <v>1698.65955420128</v>
       </c>
       <c r="F98">
-        <v>3370.894265559042</v>
+        <v>3406.007747491949</v>
       </c>
       <c r="G98">
         <v>153</v>
@@ -9326,37 +9326,37 @@
         <v>425.55</v>
       </c>
       <c r="M98">
-        <v>514.8589852486259</v>
+        <v>520.2220996782989</v>
       </c>
       <c r="N98">
-        <v>-89.3089852486259</v>
+        <v>-94.67209967829893</v>
       </c>
       <c r="O98">
-        <v>-11.16362315607824</v>
+        <v>-11.83401245978737</v>
       </c>
       <c r="P98">
-        <v>-78.14536209254766</v>
+        <v>-82.83808721851156</v>
       </c>
       <c r="Q98">
-        <v>-51.44536209254765</v>
+        <v>-56.13808721851156</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.177823413119519</v>
+        <v>1.555164550826026</v>
       </c>
       <c r="T98">
-        <v>22.06524335577024</v>
+        <v>29.42032447436032</v>
       </c>
       <c r="U98">
         <v>0.1527366166625341</v>
       </c>
       <c r="V98">
-        <v>0.1033171247352568</v>
+        <v>0.1022519997379861</v>
       </c>
       <c r="W98">
-        <v>0.13695630858717</v>
+        <v>0.1371189921755758</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.826536997882054</v>
+        <v>0.8180159979038888</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,22 +9372,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1796603589350893</v>
+        <v>0.1807297251017146</v>
       </c>
       <c r="C99">
-        <v>-1534.843187733924</v>
+        <v>-1581.463415818798</v>
       </c>
       <c r="D99">
-        <v>1718.164559758024</v>
+        <v>1706.657813606058</v>
       </c>
       <c r="E99">
-        <v>1698.65955420128</v>
+        <v>1733.773036134187</v>
       </c>
       <c r="F99">
-        <v>3406.007747491949</v>
+        <v>3441.121229424855</v>
       </c>
       <c r="G99">
         <v>153</v>
@@ -9408,37 +9408,37 @@
         <v>425.55</v>
       </c>
       <c r="M99">
-        <v>520.2220996782989</v>
+        <v>525.5852141079722</v>
       </c>
       <c r="N99">
-        <v>-94.67209967829893</v>
+        <v>-100.0352141079722</v>
       </c>
       <c r="O99">
-        <v>-11.83401245978737</v>
+        <v>-12.50440176349652</v>
       </c>
       <c r="P99">
-        <v>-82.83808721851156</v>
+        <v>-87.53081234447566</v>
       </c>
       <c r="Q99">
-        <v>-56.13808721851156</v>
+        <v>-60.83081234447566</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.555164550826026</v>
+        <v>2.309846826239038</v>
       </c>
       <c r="T99">
-        <v>29.42032447436032</v>
+        <v>44.13048671154048</v>
       </c>
       <c r="U99">
         <v>0.1527366166625341</v>
       </c>
       <c r="V99">
-        <v>0.1022519997379861</v>
+        <v>0.1012086119855577</v>
       </c>
       <c r="W99">
-        <v>0.1371189921755758</v>
+        <v>0.1372783556907488</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8180159979038888</v>
+        <v>0.8096688958844612</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,22 +9454,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1807297251017146</v>
+        <v>0.18179909126834</v>
       </c>
       <c r="C100">
-        <v>-1581.463415818798</v>
+        <v>-1627.930545211969</v>
       </c>
       <c r="D100">
-        <v>1706.657813606058</v>
+        <v>1695.304166145793</v>
       </c>
       <c r="E100">
-        <v>1733.773036134187</v>
+        <v>1768.886518067093</v>
       </c>
       <c r="F100">
-        <v>3441.121229424855</v>
+        <v>3476.234711357762</v>
       </c>
       <c r="G100">
         <v>153</v>
@@ -9490,37 +9490,37 @@
         <v>425.55</v>
       </c>
       <c r="M100">
-        <v>525.5852141079722</v>
+        <v>530.9483285376454</v>
       </c>
       <c r="N100">
-        <v>-100.0352141079722</v>
+        <v>-105.3983285376453</v>
       </c>
       <c r="O100">
-        <v>-12.50440176349652</v>
+        <v>-13.17479106720567</v>
       </c>
       <c r="P100">
-        <v>-87.53081234447566</v>
+        <v>-92.22353747043968</v>
       </c>
       <c r="Q100">
-        <v>-60.83081234447566</v>
+        <v>-65.52353747043968</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.309846826239038</v>
+        <v>4.573893652478077</v>
       </c>
       <c r="T100">
-        <v>44.13048671154048</v>
+        <v>88.26097342308096</v>
       </c>
       <c r="U100">
         <v>0.1527366166625341</v>
       </c>
       <c r="V100">
-        <v>0.1012086119855577</v>
+        <v>0.1001863027735823</v>
       </c>
       <c r="W100">
-        <v>0.1372783556907488</v>
+        <v>0.1374344997409689</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9528,91 +9528,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8096688958844612</v>
+        <v>0.8014904221886586</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.18179909126834</v>
-      </c>
-      <c r="C101">
-        <v>-1627.930545211969</v>
-      </c>
-      <c r="D101">
-        <v>1695.304166145793</v>
-      </c>
-      <c r="E101">
-        <v>1768.886518067093</v>
-      </c>
-      <c r="F101">
-        <v>3476.234711357762</v>
-      </c>
-      <c r="G101">
-        <v>153</v>
-      </c>
-      <c r="H101">
-        <v>1804</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>452.25</v>
-      </c>
-      <c r="K101">
-        <v>26.7</v>
-      </c>
-      <c r="L101">
-        <v>425.55</v>
-      </c>
-      <c r="M101">
-        <v>530.9483285376454</v>
-      </c>
-      <c r="N101">
-        <v>-105.3983285376453</v>
-      </c>
-      <c r="O101">
-        <v>-13.17479106720567</v>
-      </c>
-      <c r="P101">
-        <v>-92.22353747043968</v>
-      </c>
-      <c r="Q101">
-        <v>-65.52353747043968</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.573893652478077</v>
-      </c>
-      <c r="T101">
-        <v>88.26097342308096</v>
-      </c>
-      <c r="U101">
-        <v>0.1527366166625341</v>
-      </c>
-      <c r="V101">
-        <v>0.1001863027735823</v>
-      </c>
-      <c r="W101">
-        <v>0.1374344997409689</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8014904221886586</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
